--- a/Business Analysis/checkupp_product_backlog.xlsx
+++ b/Business Analysis/checkupp_product_backlog.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34550AD7-EA1C-44F2-8B37-D1E9B7DFAAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E11AF35-D9A5-4EBD-8DD3-E7EE2CBE1164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Tanvi_Immunisation_User_Stories" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$1:$I$32</definedName>
@@ -178,7 +179,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="374">
   <si>
     <t>Epic #</t>
   </si>
@@ -5299,12 +5300,1410 @@
 11. Zero Network Dependency (Privacy): Because scanning runs strictly via on-device ML Kit, the extraction feature must operate flawlessly when the device is fully offline, ensuring no visual data is transmitted over the internet.
 12. Lighting/Contrast Pre-Processing (Technical AC): Because floor scales are often highly reflective or backlit, the camera feed passed to ML Kit must utilize a threshold/contrast filter to isolate the glowing LCD numbers from the background glare.</t>
   </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>As a...</t>
+  </si>
+  <si>
+    <t>I want to...</t>
+  </si>
+  <si>
+    <t>So that...</t>
+  </si>
+  <si>
+    <t>Logged-in user navigating to the Immunisations screen</t>
+  </si>
+  <si>
+    <t>See the immunisation category relevant to my age bracket</t>
+  </si>
+  <si>
+    <t>I can easily identify vaccinations relevant to my current age group</t>
+  </si>
+  <si>
+    <t>Logged-in user whose profile indicates female gender and confirmed pregnancy</t>
+  </si>
+  <si>
+    <t>See pregnancy-specific immunisation recommendations</t>
+  </si>
+  <si>
+    <t>I can view vaccinations relevant to pregnancy</t>
+  </si>
+  <si>
+    <t>See vaccination recommendations personalised to my applicable age/life stage</t>
+  </si>
+  <si>
+    <t>I am not presented with irrelevant recommendations</t>
+  </si>
+  <si>
+    <t>Access the Travel immunisation category</t>
+  </si>
+  <si>
+    <t>I can view travel vaccination information regardless of my age or gender</t>
+  </si>
+  <si>
+    <t>Logged-in user who is at or above the defined legal parenting age</t>
+  </si>
+  <si>
+    <t>Access the Children immunisation category</t>
+  </si>
+  <si>
+    <t>I can view vaccination information relevant to children</t>
+  </si>
+  <si>
+    <t>Logged-in user browsing the Immunisations screen</t>
+  </si>
+  <si>
+    <t>Browse other applicable immunisation categories</t>
+  </si>
+  <si>
+    <t>I can access useful vaccination information beyond my personalised recommendations</t>
+  </si>
+  <si>
+    <t>Logged-in user selecting an immunisation category</t>
+  </si>
+  <si>
+    <t>View the vaccinations associated with that specific age group or life stage</t>
+  </si>
+  <si>
+    <t>I can understand which vaccinations belong to that category</t>
+  </si>
+  <si>
+    <t>Logged-in user viewing an immunisation category</t>
+  </si>
+  <si>
+    <t>View more information about an available vaccination</t>
+  </si>
+  <si>
+    <t>I can understand the vaccination recommendation presented to me</t>
+  </si>
+  <si>
+    <t>Logged-in user with incomplete or invalid profile information</t>
+  </si>
+  <si>
+    <t>See an appropriate Immunisations screen state</t>
+  </si>
+  <si>
+    <t>The interface does not provide incorrect personalised recommendations</t>
+  </si>
+  <si>
+    <t>Logged-in user using the Immunisations screen</t>
+  </si>
+  <si>
+    <t>See a consistent and usable immunisation interface</t>
+  </si>
+  <si>
+    <t>I can navigate recommendations and categories without confusion</t>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The frontend must determine the applicable age bracket using the user's configured age/test profile data.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The corresponding age-group card must be displayed in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommended for You.
+3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Age-group labels and ranges must match the approved wireframe, e.g. Children, Adolescent, Adult, 50+ Years, 65+ Years and 70+ Years where applicable.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Age-group cards that are not applicable to the user must not appear in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommended for You</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Boundary ages must map to the correct group according to the defined age ranges.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If age data is unavailable or invalid, age-specific recommendations must not be displayed and an appropriate frontend fallback message/state must be shown.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pregnancy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> card must be displayed when the configured user profile indicates both female gender </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> confirmed pregnancy.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The Pregnancy card must not be displayed as a personalised recommendation when either condition is not satisfied.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pregnancy recommendations must appear alongside any applicable age-based recommendation rather than replacing it.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting the Pregnancy card must display the vaccination information configured for the pregnancy life stage.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The displayed Pregnancy card must follow the approved wireframe styling and interaction behaviour.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommended for You</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> must contain only cards applicable to the configured user profile.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The applicable age-based card must be displayed when valid age information is available.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A qualifying pregnant user must see both the applicable age-based recommendation and Pregnancy recommendation where both apply.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Non-applicable age/life-stage cards must not appear in this section.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Travel and other general browsing categories must not appear in Recommended for You unless separately defined as recommendations in the approved design.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The layout must correctly handle one or multiple recommendation cards without overlap, clipping, or broken spacing.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Travel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> card must always be displayed under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for every configured user profile.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Travel card visibility must not depend on age, gender, or pregnancy status.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting the Travel card must display the configured travel vaccination information/list.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The Travel card must remain visible when testing different valid user profile combinations.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The card's label, description, icon and interaction must follow the approved wireframe.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Children (0–4 years)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> card must be displayed under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when the configured user's age is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16 years or older</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The Children card must not be displayed when the configured user's age is below 16.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The boundary value of exactly 16 years must result in the Children card being displayed.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Visibility of the Children card must not depend on gender or pregnancy status.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting the card must display the vaccination information configured for children aged 0–4 years.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> must be displayed separately from Recommended for You.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cards within Other Categories must follow their defined frontend visibility rules.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Travel must be available to all users.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Children (0–4 years) must follow the 16+ visibility rule.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pregnancy must follow its approved visibility rule for this section, if the product design includes Pregnancy under Other Categories.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Age/life-stage categories shown for general browsing must appear in the order specified by the approved wireframe.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Changes to the configured test profile must result in the appropriate category visibility changes when the screen is re-rendered.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Each category card must be associated with its approved vaccination list.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting a card must display only the vaccination information configured for that category.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Vaccine names and accompanying frontend content must match the approved content source supplied to the development team.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Vaccines belonging exclusively to another category must not incorrectly appear in the selected category.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Categories containing multiple vaccines must display all configured vaccines without clipping or inaccessible content.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Empty or missing mock vaccination data must produce an appropriate frontend empty state rather than a blank or broken component.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Each displayed vaccination must be selectable where interaction is defined in the design.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting a vaccination must display the corresponding configured details using the approved frontend component/screen.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The displayed vaccine information must correspond to the vaccination selected by the user.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The user must be able to return to the relevant immunisation category without breaking the screen state/navigation flow.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Missing optional information must not cause the component to crash or display malformed UI.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Missing/invalid age data must not result in an arbitrary age-specific recommendation being shown.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Missing pregnancy information must not cause the Pregnancy card to be treated as a personalised recommendation.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> General categories that do not depend on missing information, such as Travel, must remain accessible.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The frontend must display the defined fallback/empty state where personalised recommendations cannot be determined.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The screen must remain functional and must not crash because profile values are null, undefined, malformed, or otherwise unavailable.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommended for You</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quick Actions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> must appear in the order defined in the approved wireframe.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cards must use consistent spacing, typography, icons, borders and interaction states according to the approved frontend design.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Conditional removal of a card must not leave unintended blank spaces or broken alignment.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Multiple Recommended for You cards must render correctly when more than one condition applies.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> All visible interactive cards must respond to user selection and navigate/open the expected frontend content.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The screen must remain scrollable and all rendered content must be reachable on supported mobile screen sizes.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5426,6 +6825,13 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="19">
@@ -5624,7 +7030,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5797,6 +7203,72 @@
     <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5818,9 +7290,6 @@
     <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5836,68 +7305,14 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6116,50 +7531,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L94"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="64.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="72.5546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" style="3" customWidth="1"/>
-    <col min="10" max="12" width="8.88671875" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="5.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.90625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="64.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="72.54296875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.6328125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.36328125" style="3" customWidth="1"/>
+    <col min="10" max="12" width="8.90625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
       <c r="G1" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="74" t="s">
+      <c r="H1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="74" t="s">
+      <c r="I1" s="71" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="65"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -6170,10 +7585,10 @@
         <v>9</v>
       </c>
       <c r="G2" s="75"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-    </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+    </row>
+    <row r="3" spans="1:9" s="5" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="76">
         <v>1</v>
       </c>
@@ -6202,7 +7617,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="6" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" s="6" customFormat="1" ht="124.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="76"/>
       <c r="B4" s="78"/>
       <c r="C4" s="16">
@@ -6223,7 +7638,7 @@
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
     </row>
-    <row r="5" spans="1:9" s="6" customFormat="1" ht="160.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="6" customFormat="1" ht="160.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="76"/>
       <c r="B5" s="78"/>
       <c r="C5" s="16">
@@ -6244,7 +7659,7 @@
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
     </row>
-    <row r="6" spans="1:9" s="6" customFormat="1" ht="154.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="6" customFormat="1" ht="154.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="76"/>
       <c r="B6" s="78"/>
       <c r="C6" s="16">
@@ -6265,7 +7680,7 @@
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
     </row>
-    <row r="7" spans="1:9" s="6" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="6" customFormat="1" ht="116" x14ac:dyDescent="0.35">
       <c r="A7" s="76"/>
       <c r="B7" s="78"/>
       <c r="C7" s="16">
@@ -6286,7 +7701,7 @@
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
     </row>
-    <row r="8" spans="1:9" s="6" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="6" customFormat="1" ht="124.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="50"/>
       <c r="B8" s="78"/>
       <c r="C8" s="16">
@@ -6307,7 +7722,7 @@
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
     </row>
-    <row r="9" spans="1:9" s="6" customFormat="1" ht="152.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="6" customFormat="1" ht="152.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="50"/>
       <c r="B9" s="78"/>
       <c r="C9" s="16">
@@ -6328,7 +7743,7 @@
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
     </row>
-    <row r="10" spans="1:9" s="6" customFormat="1" ht="295.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="6" customFormat="1" ht="295.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="50"/>
       <c r="B10" s="79"/>
       <c r="C10" s="16">
@@ -6349,11 +7764,11 @@
       <c r="H10" s="16"/>
       <c r="I10" s="51"/>
     </row>
-    <row r="11" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="71">
+    <row r="11" spans="1:9" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="72">
         <v>5</v>
       </c>
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="72" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="18">
@@ -6378,9 +7793,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="72"/>
-      <c r="B12" s="72"/>
+    <row r="12" spans="1:9" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="73"/>
+      <c r="B12" s="73"/>
       <c r="C12" s="18">
         <v>5.2</v>
       </c>
@@ -6399,9 +7814,9 @@
       <c r="H12" s="20"/>
       <c r="I12" s="18"/>
     </row>
-    <row r="13" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="72"/>
-      <c r="B13" s="72"/>
+    <row r="13" spans="1:9" s="6" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+      <c r="A13" s="73"/>
+      <c r="B13" s="73"/>
       <c r="C13" s="18">
         <v>5.3</v>
       </c>
@@ -6420,9 +7835,9 @@
       <c r="H13" s="20"/>
       <c r="I13" s="18"/>
     </row>
-    <row r="14" spans="1:9" s="14" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="72"/>
-      <c r="B14" s="72"/>
+    <row r="14" spans="1:9" s="14" customFormat="1" ht="232" x14ac:dyDescent="0.35">
+      <c r="A14" s="73"/>
+      <c r="B14" s="73"/>
       <c r="C14" s="21">
         <v>5.4</v>
       </c>
@@ -6441,9 +7856,9 @@
       <c r="H14" s="23"/>
       <c r="I14" s="21"/>
     </row>
-    <row r="15" spans="1:9" s="14" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="73"/>
-      <c r="B15" s="73"/>
+    <row r="15" spans="1:9" s="14" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+      <c r="A15" s="74"/>
+      <c r="B15" s="74"/>
       <c r="C15" s="21">
         <v>5.5</v>
       </c>
@@ -6462,11 +7877,11 @@
       <c r="H15" s="23"/>
       <c r="I15" s="21"/>
     </row>
-    <row r="16" spans="1:9" s="14" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="80">
+    <row r="16" spans="1:9" s="14" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+      <c r="A16" s="58">
         <v>6</v>
       </c>
-      <c r="B16" s="80" t="s">
+      <c r="B16" s="58" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="24">
@@ -6491,9 +7906,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="81"/>
-      <c r="B17" s="81"/>
+    <row r="17" spans="1:9" s="6" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+      <c r="A17" s="59"/>
+      <c r="B17" s="59"/>
       <c r="C17" s="24">
         <v>6.2</v>
       </c>
@@ -6512,9 +7927,9 @@
       <c r="H17" s="26"/>
       <c r="I17" s="24"/>
     </row>
-    <row r="18" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="81"/>
-      <c r="B18" s="81"/>
+    <row r="18" spans="1:9" s="6" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+      <c r="A18" s="59"/>
+      <c r="B18" s="59"/>
       <c r="C18" s="24">
         <v>6.3</v>
       </c>
@@ -6533,9 +7948,9 @@
       <c r="H18" s="26"/>
       <c r="I18" s="24"/>
     </row>
-    <row r="19" spans="1:9" s="6" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="81"/>
-      <c r="B19" s="81"/>
+    <row r="19" spans="1:9" s="6" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="59"/>
+      <c r="B19" s="59"/>
       <c r="C19" s="27">
         <v>6.4</v>
       </c>
@@ -6558,9 +7973,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A20" s="52"/>
-      <c r="B20" s="81"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="24">
         <v>6.5</v>
       </c>
@@ -6579,9 +7994,9 @@
       <c r="H20" s="26"/>
       <c r="I20" s="24"/>
     </row>
-    <row r="21" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A21" s="52"/>
-      <c r="B21" s="91"/>
+      <c r="B21" s="70"/>
       <c r="C21" s="24">
         <v>6.6</v>
       </c>
@@ -6600,11 +8015,11 @@
       <c r="H21" s="26"/>
       <c r="I21" s="24"/>
     </row>
-    <row r="22" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A22" s="82">
+    <row r="22" spans="1:9" s="6" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+      <c r="A22" s="60">
         <v>7</v>
       </c>
-      <c r="B22" s="80" t="s">
+      <c r="B22" s="58" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="24">
@@ -6629,9 +8044,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A23" s="83"/>
-      <c r="B23" s="81"/>
+    <row r="23" spans="1:9" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="61"/>
+      <c r="B23" s="59"/>
       <c r="C23" s="24">
         <v>7.2</v>
       </c>
@@ -6652,9 +8067,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="83"/>
-      <c r="B24" s="81"/>
+    <row r="24" spans="1:9" s="6" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="61"/>
+      <c r="B24" s="59"/>
       <c r="C24" s="24">
         <v>7.3</v>
       </c>
@@ -6673,9 +8088,9 @@
       <c r="H24" s="26"/>
       <c r="I24" s="24"/>
     </row>
-    <row r="25" spans="1:9" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="84"/>
-      <c r="B25" s="81"/>
+    <row r="25" spans="1:9" s="6" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="62"/>
+      <c r="B25" s="59"/>
       <c r="C25" s="24">
         <v>7.4</v>
       </c>
@@ -6694,9 +8109,9 @@
       <c r="H25" s="26"/>
       <c r="I25" s="24"/>
     </row>
-    <row r="26" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A26" s="52"/>
-      <c r="B26" s="91"/>
+      <c r="B26" s="70"/>
       <c r="C26" s="24">
         <v>7.5</v>
       </c>
@@ -6715,11 +8130,11 @@
       <c r="H26" s="26"/>
       <c r="I26" s="24"/>
     </row>
-    <row r="27" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="88">
+    <row r="27" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="67">
         <v>8</v>
       </c>
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="67" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="28">
@@ -6742,9 +8157,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="89"/>
-      <c r="B28" s="89"/>
+    <row r="28" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="68"/>
+      <c r="B28" s="68"/>
       <c r="C28" s="28">
         <v>9.3000000000000007</v>
       </c>
@@ -6765,9 +8180,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="90"/>
-      <c r="B29" s="90"/>
+    <row r="29" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="69"/>
+      <c r="B29" s="69"/>
       <c r="C29" s="28">
         <v>9.4</v>
       </c>
@@ -6788,11 +8203,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="86">
+    <row r="30" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A30" s="65">
         <v>12</v>
       </c>
-      <c r="B30" s="86" t="s">
+      <c r="B30" s="65" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="30">
@@ -6817,9 +8232,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="86"/>
-      <c r="B31" s="86"/>
+    <row r="31" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A31" s="65"/>
+      <c r="B31" s="65"/>
       <c r="C31" s="30">
         <v>12.2</v>
       </c>
@@ -6842,9 +8257,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="86"/>
-      <c r="B32" s="86"/>
+    <row r="32" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A32" s="65"/>
+      <c r="B32" s="65"/>
       <c r="C32" s="30">
         <v>12.3</v>
       </c>
@@ -6867,9 +8282,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="86"/>
-      <c r="B33" s="86"/>
+    <row r="33" spans="1:9" s="6" customFormat="1" ht="123.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="65"/>
+      <c r="B33" s="65"/>
       <c r="C33" s="30">
         <v>12.4</v>
       </c>
@@ -6892,9 +8307,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="86"/>
-      <c r="B34" s="86"/>
+    <row r="34" spans="1:9" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="65"/>
+      <c r="B34" s="65"/>
       <c r="C34" s="30">
         <v>12.5</v>
       </c>
@@ -6917,11 +8332,11 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="87">
+    <row r="35" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="66">
         <v>14</v>
       </c>
-      <c r="B35" s="87" t="s">
+      <c r="B35" s="66" t="s">
         <v>70</v>
       </c>
       <c r="C35" s="34">
@@ -6946,9 +8361,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="87"/>
-      <c r="B36" s="87"/>
+    <row r="36" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="66"/>
+      <c r="B36" s="66"/>
       <c r="C36" s="34">
         <v>14.2</v>
       </c>
@@ -6971,9 +8386,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="87"/>
-      <c r="B37" s="87"/>
+    <row r="37" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="66"/>
+      <c r="B37" s="66"/>
       <c r="C37" s="34">
         <v>14.3</v>
       </c>
@@ -6996,9 +8411,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="87"/>
-      <c r="B38" s="87"/>
+    <row r="38" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A38" s="66"/>
+      <c r="B38" s="66"/>
       <c r="C38" s="34">
         <v>14.4</v>
       </c>
@@ -7021,9 +8436,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="87"/>
-      <c r="B39" s="87"/>
+    <row r="39" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="66"/>
+      <c r="B39" s="66"/>
       <c r="C39" s="34">
         <v>14.5</v>
       </c>
@@ -7046,9 +8461,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="87"/>
-      <c r="B40" s="87"/>
+    <row r="40" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="66"/>
+      <c r="B40" s="66"/>
       <c r="C40" s="34">
         <v>14.6</v>
       </c>
@@ -7071,9 +8486,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="87"/>
-      <c r="B41" s="87"/>
+    <row r="41" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="66"/>
+      <c r="B41" s="66"/>
       <c r="C41" s="34">
         <v>14.7</v>
       </c>
@@ -7096,9 +8511,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="87"/>
-      <c r="B42" s="87"/>
+    <row r="42" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="66"/>
+      <c r="B42" s="66"/>
       <c r="C42" s="34">
         <v>14.8</v>
       </c>
@@ -7121,9 +8536,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="87"/>
-      <c r="B43" s="87"/>
+    <row r="43" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="66"/>
+      <c r="B43" s="66"/>
       <c r="C43" s="34">
         <v>14.9</v>
       </c>
@@ -7146,9 +8561,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="87"/>
-      <c r="B44" s="87"/>
+    <row r="44" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A44" s="66"/>
+      <c r="B44" s="66"/>
       <c r="C44" s="34">
         <v>14.1</v>
       </c>
@@ -7171,9 +8586,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="87"/>
-      <c r="B45" s="87"/>
+    <row r="45" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="66"/>
+      <c r="B45" s="66"/>
       <c r="C45" s="34">
         <v>14.11</v>
       </c>
@@ -7196,11 +8611,11 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="85">
+    <row r="46" spans="1:9" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A46" s="63">
         <v>15</v>
       </c>
-      <c r="B46" s="85" t="s">
+      <c r="B46" s="63" t="s">
         <v>74</v>
       </c>
       <c r="C46" s="37">
@@ -7225,9 +8640,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="65"/>
-      <c r="B47" s="65"/>
+    <row r="47" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A47" s="64"/>
+      <c r="B47" s="64"/>
       <c r="C47" s="37">
         <v>15.2</v>
       </c>
@@ -7250,9 +8665,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="65"/>
-      <c r="B48" s="65"/>
+    <row r="48" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A48" s="64"/>
+      <c r="B48" s="64"/>
       <c r="C48" s="37">
         <v>15.3</v>
       </c>
@@ -7275,9 +8690,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="65"/>
-      <c r="B49" s="65"/>
+    <row r="49" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="64"/>
+      <c r="B49" s="64"/>
       <c r="C49" s="37">
         <v>15.4</v>
       </c>
@@ -7300,9 +8715,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="65"/>
-      <c r="B50" s="65"/>
+    <row r="50" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A50" s="64"/>
+      <c r="B50" s="64"/>
       <c r="C50" s="37">
         <v>15.5</v>
       </c>
@@ -7325,9 +8740,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="65"/>
-      <c r="B51" s="65"/>
+    <row r="51" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A51" s="64"/>
+      <c r="B51" s="64"/>
       <c r="C51" s="37">
         <v>15.6</v>
       </c>
@@ -7350,9 +8765,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="65"/>
-      <c r="B52" s="65"/>
+    <row r="52" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="64"/>
+      <c r="B52" s="64"/>
       <c r="C52" s="37">
         <v>15.7</v>
       </c>
@@ -7375,9 +8790,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="65"/>
-      <c r="B53" s="65"/>
+    <row r="53" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A53" s="64"/>
+      <c r="B53" s="64"/>
       <c r="C53" s="37">
         <v>15.8</v>
       </c>
@@ -7400,11 +8815,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="64">
+    <row r="54" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="86">
         <v>16</v>
       </c>
-      <c r="B54" s="64" t="s">
+      <c r="B54" s="86" t="s">
         <v>89</v>
       </c>
       <c r="C54" s="39">
@@ -7429,9 +8844,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="64"/>
-      <c r="B55" s="64"/>
+    <row r="55" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="86"/>
+      <c r="B55" s="86"/>
       <c r="C55" s="39">
         <v>16.2</v>
       </c>
@@ -7454,9 +8869,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="64"/>
-      <c r="B56" s="64"/>
+    <row r="56" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="86"/>
+      <c r="B56" s="86"/>
       <c r="C56" s="39">
         <v>16.3</v>
       </c>
@@ -7479,9 +8894,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="64"/>
-      <c r="B57" s="64"/>
+    <row r="57" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A57" s="86"/>
+      <c r="B57" s="86"/>
       <c r="C57" s="39">
         <v>16.399999999999999</v>
       </c>
@@ -7504,9 +8919,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="64"/>
-      <c r="B58" s="64"/>
+    <row r="58" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="86"/>
+      <c r="B58" s="86"/>
       <c r="C58" s="39">
         <v>16.5</v>
       </c>
@@ -7529,9 +8944,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="65"/>
-      <c r="B59" s="65"/>
+    <row r="59" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="64"/>
+      <c r="B59" s="64"/>
       <c r="C59" s="39">
         <v>16.600000000000001</v>
       </c>
@@ -7554,11 +8969,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="66">
+    <row r="60" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="87">
         <v>17</v>
       </c>
-      <c r="B60" s="69" t="s">
+      <c r="B60" s="90" t="s">
         <v>105</v>
       </c>
       <c r="C60" s="42">
@@ -7583,9 +8998,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="67"/>
-      <c r="B61" s="69"/>
+    <row r="61" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="88"/>
+      <c r="B61" s="90"/>
       <c r="C61" s="42">
         <v>17.2</v>
       </c>
@@ -7608,9 +9023,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="67"/>
-      <c r="B62" s="69"/>
+    <row r="62" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="88"/>
+      <c r="B62" s="90"/>
       <c r="C62" s="42">
         <v>17.3</v>
       </c>
@@ -7633,9 +9048,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="67"/>
-      <c r="B63" s="69"/>
+    <row r="63" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="88"/>
+      <c r="B63" s="90"/>
       <c r="C63" s="42">
         <v>17.399999999999999</v>
       </c>
@@ -7658,9 +9073,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="68"/>
-      <c r="B64" s="69"/>
+    <row r="64" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="89"/>
+      <c r="B64" s="90"/>
       <c r="C64" s="42">
         <v>17.5</v>
       </c>
@@ -7683,11 +9098,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="65" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="70">
+    <row r="65" spans="1:12" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A65" s="91">
         <v>18</v>
       </c>
-      <c r="B65" s="71" t="s">
+      <c r="B65" s="72" t="s">
         <v>279</v>
       </c>
       <c r="C65" s="18">
@@ -7712,9 +9127,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="66" spans="1:12" s="6" customFormat="1" ht="250.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="65"/>
-      <c r="B66" s="72"/>
+    <row r="66" spans="1:12" s="6" customFormat="1" ht="250.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="64"/>
+      <c r="B66" s="73"/>
       <c r="C66" s="18">
         <v>18.2</v>
       </c>
@@ -7737,9 +9152,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="67" spans="1:12" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="65"/>
-      <c r="B67" s="72"/>
+    <row r="67" spans="1:12" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="64"/>
+      <c r="B67" s="73"/>
       <c r="C67" s="18">
         <v>18.3</v>
       </c>
@@ -7762,9 +9177,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="1:12" s="6" customFormat="1" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="65"/>
-      <c r="B68" s="72"/>
+    <row r="68" spans="1:12" s="6" customFormat="1" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="64"/>
+      <c r="B68" s="73"/>
       <c r="C68" s="18">
         <v>18.399999999999999</v>
       </c>
@@ -7787,9 +9202,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:12" s="6" customFormat="1" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" s="6" customFormat="1" ht="216" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="48"/>
-      <c r="B69" s="73"/>
+      <c r="B69" s="74"/>
       <c r="C69" s="18">
         <v>18.5</v>
       </c>
@@ -7808,11 +9223,11 @@
       <c r="H69" s="18"/>
       <c r="I69" s="18"/>
     </row>
-    <row r="70" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="58">
+    <row r="70" spans="1:12" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A70" s="80">
         <v>19</v>
       </c>
-      <c r="B70" s="61" t="s">
+      <c r="B70" s="83" t="s">
         <v>120</v>
       </c>
       <c r="C70" s="44">
@@ -7833,9 +9248,9 @@
       <c r="H70" s="44"/>
       <c r="I70" s="47"/>
     </row>
-    <row r="71" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="59"/>
-      <c r="B71" s="62"/>
+    <row r="71" spans="1:12" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="81"/>
+      <c r="B71" s="84"/>
       <c r="C71" s="15">
         <v>19.2</v>
       </c>
@@ -7854,9 +9269,9 @@
       <c r="H71" s="44"/>
       <c r="I71" s="47"/>
     </row>
-    <row r="72" spans="1:12" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="60"/>
-      <c r="B72" s="63"/>
+    <row r="72" spans="1:12" s="6" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="82"/>
+      <c r="B72" s="85"/>
       <c r="C72" s="53">
         <v>19.3</v>
       </c>
@@ -7877,11 +9292,11 @@
         <v>313</v>
       </c>
     </row>
-    <row r="73" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="58">
+    <row r="73" spans="1:12" s="6" customFormat="1" ht="203" x14ac:dyDescent="0.35">
+      <c r="A73" s="80">
         <v>20</v>
       </c>
-      <c r="B73" s="61" t="s">
+      <c r="B73" s="83" t="s">
         <v>126</v>
       </c>
       <c r="C73" s="44">
@@ -7902,9 +9317,9 @@
       <c r="H73" s="44"/>
       <c r="I73" s="47"/>
     </row>
-    <row r="74" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A74" s="59"/>
-      <c r="B74" s="62"/>
+    <row r="74" spans="1:12" s="6" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="81"/>
+      <c r="B74" s="84"/>
       <c r="C74" s="15">
         <v>20.2</v>
       </c>
@@ -7926,9 +9341,9 @@
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
     </row>
-    <row r="75" spans="1:12" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="60"/>
-      <c r="B75" s="62"/>
+    <row r="75" spans="1:12" s="6" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="82"/>
+      <c r="B75" s="84"/>
       <c r="C75" s="56">
         <v>20.3</v>
       </c>
@@ -7952,9 +9367,9 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
     </row>
-    <row r="76" spans="1:12" s="6" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" s="6" customFormat="1" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A76" s="49"/>
-      <c r="B76" s="63"/>
+      <c r="B76" s="85"/>
       <c r="C76" s="56">
         <v>20.399999999999999</v>
       </c>
@@ -7978,11 +9393,11 @@
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
     </row>
-    <row r="77" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="58">
+    <row r="77" spans="1:12" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A77" s="80">
         <v>21</v>
       </c>
-      <c r="B77" s="61" t="s">
+      <c r="B77" s="83" t="s">
         <v>129</v>
       </c>
       <c r="C77" s="44">
@@ -8003,9 +9418,9 @@
       <c r="H77" s="44"/>
       <c r="I77" s="47"/>
     </row>
-    <row r="78" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="59"/>
-      <c r="B78" s="62"/>
+    <row r="78" spans="1:12" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="81"/>
+      <c r="B78" s="84"/>
       <c r="C78" s="15">
         <v>21.2</v>
       </c>
@@ -8024,9 +9439,9 @@
       <c r="H78" s="44"/>
       <c r="I78" s="47"/>
     </row>
-    <row r="79" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A79" s="60"/>
-      <c r="B79" s="63"/>
+    <row r="79" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="82"/>
+      <c r="B79" s="85"/>
       <c r="C79" s="32">
         <v>21.3</v>
       </c>
@@ -8041,11 +9456,11 @@
       <c r="H79" s="32"/>
       <c r="I79" s="33"/>
     </row>
-    <row r="80" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="58">
+    <row r="80" spans="1:12" ht="261" x14ac:dyDescent="0.35">
+      <c r="A80" s="80">
         <v>22</v>
       </c>
-      <c r="B80" s="61" t="s">
+      <c r="B80" s="83" t="s">
         <v>133</v>
       </c>
       <c r="C80" s="44">
@@ -8066,9 +9481,9 @@
       <c r="H80" s="44"/>
       <c r="I80" s="47"/>
     </row>
-    <row r="81" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A81" s="59"/>
-      <c r="B81" s="62"/>
+    <row r="81" spans="1:9" ht="261" x14ac:dyDescent="0.35">
+      <c r="A81" s="81"/>
+      <c r="B81" s="84"/>
       <c r="C81" s="15">
         <v>22.2</v>
       </c>
@@ -8087,9 +9502,9 @@
       <c r="H81" s="44"/>
       <c r="I81" s="47"/>
     </row>
-    <row r="82" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A82" s="60"/>
-      <c r="B82" s="63"/>
+    <row r="82" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A82" s="82"/>
+      <c r="B82" s="85"/>
       <c r="C82" s="32">
         <v>22.3</v>
       </c>
@@ -8104,26 +9519,26 @@
       <c r="H82" s="32"/>
       <c r="I82" s="33"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="E83" s="11"/>
       <c r="H83" s="3"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="I84" s="2"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="I85" s="2"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -8134,7 +9549,7 @@
       <c r="H86" s="7"/>
       <c r="I86" s="7"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -8145,7 +9560,7 @@
       <c r="H87" s="10"/>
       <c r="I87" s="10"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D88" s="10"/>
       <c r="E88" s="10"/>
       <c r="F88" s="10"/>
@@ -8153,7 +9568,7 @@
       <c r="H88" s="10"/>
       <c r="I88" s="10"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B89" s="3"/>
       <c r="D89" s="10"/>
       <c r="E89" s="10"/>
@@ -8162,7 +9577,7 @@
       <c r="H89" s="10"/>
       <c r="I89" s="10"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D90" s="10"/>
       <c r="E90" s="10"/>
       <c r="F90" s="10"/>
@@ -8170,7 +9585,7 @@
       <c r="H90" s="10"/>
       <c r="I90" s="10"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D91" s="10"/>
       <c r="E91" s="10"/>
       <c r="F91" s="10"/>
@@ -8178,7 +9593,7 @@
       <c r="H91" s="10"/>
       <c r="I91" s="10"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D92" s="10"/>
       <c r="E92" s="10"/>
       <c r="F92" s="10"/>
@@ -8186,7 +9601,7 @@
       <c r="H92" s="10"/>
       <c r="I92" s="10"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D93" s="10"/>
       <c r="E93" s="10"/>
       <c r="F93" s="10"/>
@@ -8194,7 +9609,7 @@
       <c r="H93" s="10"/>
       <c r="I93" s="10"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D94" s="10"/>
       <c r="E94" s="10"/>
       <c r="F94" s="10"/>
@@ -8205,29 +9620,6 @@
   </sheetData>
   <autoFilter ref="I1:I32" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A46:A53"/>
-    <mergeCell ref="B46:B53"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="A35:A45"/>
-    <mergeCell ref="B35:B45"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B10"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="A80:A82"/>
@@ -8242,6 +9634,29 @@
     <mergeCell ref="A73:A75"/>
     <mergeCell ref="B73:B76"/>
     <mergeCell ref="B65:B69"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B10"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A46:A53"/>
+    <mergeCell ref="B46:B53"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="A35:A45"/>
+    <mergeCell ref="B35:B45"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="B22:B26"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8253,15 +9668,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="18.21875" customWidth="1"/>
-    <col min="5" max="5" width="24.88671875" customWidth="1"/>
-    <col min="6" max="6" width="27.33203125" customWidth="1"/>
-    <col min="7" max="7" width="36.21875" customWidth="1"/>
+    <col min="4" max="4" width="18.1796875" customWidth="1"/>
+    <col min="5" max="5" width="24.90625" customWidth="1"/>
+    <col min="6" max="6" width="27.36328125" customWidth="1"/>
+    <col min="7" max="7" width="36.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -8273,7 +9688,7 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -8285,7 +9700,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -8309,7 +9724,7 @@
       </c>
       <c r="J3" s="9"/>
     </row>
-    <row r="4" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="348" x14ac:dyDescent="0.35">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -8333,7 +9748,7 @@
       </c>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -8357,7 +9772,7 @@
       </c>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="348" x14ac:dyDescent="0.35">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -8381,7 +9796,7 @@
       </c>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="406" x14ac:dyDescent="0.35">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -8405,7 +9820,7 @@
       </c>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -8429,7 +9844,7 @@
       </c>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:10" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -8453,7 +9868,7 @@
       </c>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="348" x14ac:dyDescent="0.35">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -8477,7 +9892,7 @@
       </c>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="319" x14ac:dyDescent="0.35">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -8501,7 +9916,7 @@
       </c>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:10" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -8525,7 +9940,7 @@
       </c>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:10" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -8549,7 +9964,7 @@
       </c>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:10" ht="288" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="290" x14ac:dyDescent="0.35">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -8573,7 +9988,7 @@
       </c>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -8585,7 +10000,7 @@
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -8597,7 +10012,7 @@
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -8609,7 +10024,7 @@
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -8621,7 +10036,7 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -8633,7 +10048,7 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -8645,7 +10060,7 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -8657,7 +10072,7 @@
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -8669,7 +10084,7 @@
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -8681,7 +10096,7 @@
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -8693,7 +10108,7 @@
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -8705,7 +10120,7 @@
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -8717,7 +10132,7 @@
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -8729,7 +10144,7 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -8741,7 +10156,7 @@
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -8753,7 +10168,7 @@
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -8765,7 +10180,7 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -8777,7 +10192,7 @@
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -8789,63 +10204,63 @@
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -8856,4 +10271,208 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0802363A-09BC-4F89-B136-783D2DDEAFD1}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.7265625" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" customWidth="1"/>
+    <col min="3" max="3" width="55.1796875" customWidth="1"/>
+    <col min="4" max="4" width="70.26953125" customWidth="1"/>
+    <col min="5" max="5" width="89.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="92" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1" s="92" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1" s="92" t="s">
+        <v>334</v>
+      </c>
+      <c r="D1" s="92" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" s="92" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="203" x14ac:dyDescent="0.35">
+      <c r="A2" s="93">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="E2" s="93" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="145" x14ac:dyDescent="0.35">
+      <c r="A3" s="93">
+        <v>5.2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="E3" s="93" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="174" x14ac:dyDescent="0.35">
+      <c r="A4" s="93">
+        <v>5.3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="E4" s="93" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="93">
+        <v>5.4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="E5" s="93" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="93">
+        <v>5.5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="E6" s="93" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="174" x14ac:dyDescent="0.35">
+      <c r="A7" s="93">
+        <v>5.6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="E7" s="93" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="93">
+        <v>5.7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>353</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="E8" s="93" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="145" x14ac:dyDescent="0.35">
+      <c r="A9" s="93">
+        <v>5.8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="E9" s="93" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="145" x14ac:dyDescent="0.35">
+      <c r="A10" s="93">
+        <v>5.9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="E10" s="93" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="145" x14ac:dyDescent="0.35">
+      <c r="A11" s="94">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="E11" s="93" t="s">
+        <v>373</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Business Analysis/checkupp_product_backlog.xlsx
+++ b/Business Analysis/checkupp_product_backlog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CheckUpp\Business Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E11AF35-D9A5-4EBD-8DD3-E7EE2CBE1164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CAF1AC-1AFC-4D00-884A-F47A2BAA0FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -178,6 +178,90 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>HP</author>
+  </authors>
+  <commentList>
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{BBA4420A-0271-44D0-A3EB-03CC607498CE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Sayan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+WILL BE BUILT BUT WON'T BE SHOWN TO THE USER</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{EF9259EC-0289-41C7-8C3D-2B6EEFD57174}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Sayan:
+Children will be hidden and other categories might only contain Travel for now.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{DB4BA10A-3EEC-432C-84DE-6EF56322DA85}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Sayan:
+Have to confirm from client whether other categories will be shown </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="374">
   <si>
@@ -5367,9 +5451,6 @@
     <t>View the vaccinations associated with that specific age group or life stage</t>
   </si>
   <si>
-    <t>I can understand which vaccinations belong to that category</t>
-  </si>
-  <si>
     <t>Logged-in user viewing an immunisation category</t>
   </si>
   <si>
@@ -5395,6 +5476,608 @@
   </si>
   <si>
     <t>I can navigate recommendations and categories without confusion</t>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Travel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> card must always be displayed under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for every configured user profile.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Travel card visibility must not depend on age, gender, or pregnancy status.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting the Travel card must display the configured travel vaccination information/list.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The Travel card must remain visible when testing different valid user profile combinations.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The card's label, description, icon and interaction must follow the approved wireframe.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Each category card must be associated with its approved vaccination list.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting a card must display only the vaccination information configured for that category.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Vaccine names and accompanying frontend content must match the approved content source supplied to the development team.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Vaccines belonging exclusively to another category must not incorrectly appear in the selected category.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Categories containing multiple vaccines must display all configured vaccines without clipping or inaccessible content.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Empty or missing mock vaccination data must produce an appropriate frontend empty state rather than a blank or broken component.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Each displayed vaccination must be selectable where interaction is defined in the design.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting a vaccination must display the corresponding configured details using the approved frontend component/screen.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The displayed vaccine information must correspond to the vaccination selected by the user.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The user must be able to return to the relevant immunisation category without breaking the screen state/navigation flow.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Missing optional information must not cause the component to crash or display malformed UI.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Missing/invalid age data must not result in an arbitrary age-specific recommendation being shown.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Missing pregnancy information must not cause the Pregnancy card to be treated as a personalised recommendation.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> General categories that do not depend on missing information, such as Travel, must remain accessible.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The frontend must display the defined fallback/empty state where personalised recommendations cannot be determined.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The screen must remain functional and must not crash because profile values are null, undefined, malformed, or otherwise unavailable.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommended for You</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quick Actions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> must appear in the order defined in the approved wireframe.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cards must use consistent spacing, typography, icons, borders and interaction states according to the approved frontend design.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Conditional removal of a card must not leave unintended blank spaces or broken alignment.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Multiple Recommended for You cards must render correctly when more than one condition applies.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> All visible interactive cards must respond to user selection and navigate/open the expected frontend content.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The screen must remain scrollable and all rendered content must be reachable on supported mobile screen sizes.</t>
+    </r>
   </si>
   <si>
     <r>
@@ -5447,7 +6130,45 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Age-group labels and ranges must match the approved wireframe, e.g. Children, Adolescent, Adult, 50+ Years, 65+ Years and 70+ Years where applicable.
+      <t xml:space="preserve"> Age-group labels and ranges must match the approved wireframe, e.g. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Children</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Adolescent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, Adult (18-49), 50+ Years, 65+ Years and 70+ Years where applicable.
 </t>
     </r>
     <r>
@@ -5477,7 +6198,444 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve">Recommended for You </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Boundary ages must map to the correct group according to the defined age ranges.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> If age data is unavailable or invalid, age-specific recommendations must not be displayed and an appropriate frontend fallback message/state must be shown.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pregnancy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> card must be displayed when the configured user profile indicates both female gender </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> confirmed pregnancy in the app (calculated LMP date).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The Pregnancy card must not be displayed as a personalised recommendation when either condition is not satisfied.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pregnancy recommendations must appear alongside any applicable age-based recommendation rather than replacing it, under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Recommended for You</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting the Pregnancy card must display the vaccination information configured for the pregnancy life stage.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The displayed Pregnancy card must follow the approved wireframe styling and interaction behaviour.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommended for You</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> must contain only cards applicable to the configured user profile.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The applicable age-based card must be displayed when valid age information is available.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A qualifying pregnant user must see both the applicable age-based recommendation and Pregnancy recommendation where both apply.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Non-applicable age/life-stage cards must not appear in this section.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Travel and other general browsing categories must not appear in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommended for You</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The layout must correctly handle one or multiple recommendation cards without overlap, clipping, or broken spacing.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Children (0–4 years)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> card must be displayed under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when the configured user's age is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16 years or older</t>
     </r>
     <r>
       <rPr>
@@ -5497,521 +6655,17 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Boundary ages must map to the correct group according to the defined age ranges.
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The Children card must not be displayed when the configured user's age is below 16.
 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> If age data is unavailable or invalid, age-specific recommendations must not be displayed and an appropriate frontend fallback message/state must be shown.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pregnancy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> card must be displayed when the configured user profile indicates both female gender </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>and</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> confirmed pregnancy.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The Pregnancy card must not be displayed as a personalised recommendation when either condition is not satisfied.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pregnancy recommendations must appear alongside any applicable age-based recommendation rather than replacing it.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Selecting the Pregnancy card must display the vaccination information configured for the pregnancy life stage.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The displayed Pregnancy card must follow the approved wireframe styling and interaction behaviour.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Recommended for You</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> must contain only cards applicable to the configured user profile.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The applicable age-based card must be displayed when valid age information is available.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> A qualifying pregnant user must see both the applicable age-based recommendation and Pregnancy recommendation where both apply.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Non-applicable age/life-stage cards must not appear in this section.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Travel and other general browsing categories must not appear in Recommended for You unless separately defined as recommendations in the approved design.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The layout must correctly handle one or multiple recommendation cards without overlap, clipping, or broken spacing.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Travel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> card must always be displayed under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Categories</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for every configured user profile.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Travel card visibility must not depend on age, gender, or pregnancy status.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Selecting the Travel card must display the configured travel vaccination information/list.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The Travel card must remain visible when testing different valid user profile combinations.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The card's label, description, icon and interaction must follow the approved wireframe.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Children (0–4 years)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> card must be displayed under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Categories</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> when the configured user's age is </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>16 years or older</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The Children card must not be displayed when the configured user's age is below 16.</t>
     </r>
     <r>
       <rPr>
@@ -6150,8 +6804,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>4.</t>
@@ -6159,19 +6814,30 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Children (0–4 years) must follow the 16+ visibility rule.
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Children (0–4 years) must follow the 16+ visibility rule.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>5.</t>
@@ -6179,28 +6845,9 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pregnancy must follow its approved visibility rule for this section, if the product design includes Pregnancy under Other Categories.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Age/life-stage categories shown for general browsing must appear in the order specified by the approved wireframe.
@@ -6210,504 +6857,44 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>7.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Changes to the configured test profile must result in the appropriate category visibility changes when the screen is re-rendered.</t>
     </r>
   </si>
   <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Each category card must be associated with its approved vaccination list.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Selecting a card must display only the vaccination information configured for that category.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Vaccine names and accompanying frontend content must match the approved content source supplied to the development team.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Vaccines belonging exclusively to another category must not incorrectly appear in the selected category.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Categories containing multiple vaccines must display all configured vaccines without clipping or inaccessible content.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Empty or missing mock vaccination data must produce an appropriate frontend empty state rather than a blank or broken component.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Each displayed vaccination must be selectable where interaction is defined in the design.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Selecting a vaccination must display the corresponding configured details using the approved frontend component/screen.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The displayed vaccine information must correspond to the vaccination selected by the user.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The user must be able to return to the relevant immunisation category without breaking the screen state/navigation flow.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Missing optional information must not cause the component to crash or display malformed UI.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Missing/invalid age data must not result in an arbitrary age-specific recommendation being shown.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Missing pregnancy information must not cause the Pregnancy card to be treated as a personalised recommendation.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> General categories that do not depend on missing information, such as Travel, must remain accessible.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The frontend must display the defined fallback/empty state where personalised recommendations cannot be determined.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The screen must remain functional and must not crash because profile values are null, undefined, malformed, or otherwise unavailable.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Recommended for You</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Quick Actions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Categories</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> must appear in the order defined in the approved wireframe.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Cards must use consistent spacing, typography, icons, borders and interaction states according to the approved frontend design.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Conditional removal of a card must not leave unintended blank spaces or broken alignment.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Multiple Recommended for You cards must render correctly when more than one condition applies.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> All visible interactive cards must respond to user selection and navigate/open the expected frontend content.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The screen must remain scrollable and all rendered content must be reachable on supported mobile screen sizes.</t>
-    </r>
+    <t>I can access which vaccinations belong to that category</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6833,8 +7020,51 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6933,6 +7163,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -7028,9 +7270,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7041,10 +7283,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -7062,257 +7304,281 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7531,50 +7797,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L94"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.90625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="64.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="72.54296875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.6328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.36328125" style="3" customWidth="1"/>
-    <col min="10" max="12" width="8.90625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="64.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="72.5546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" style="3" customWidth="1"/>
+    <col min="10" max="12" width="8.88671875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="71" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="C1" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="71" t="s">
+      <c r="D1" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="75" t="s">
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="71" t="s">
+      <c r="H1" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="71" t="s">
+      <c r="I1" s="82" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="64"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="75"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -7584,15 +7850,15 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-    </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="76">
+      <c r="G2" s="86"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+    </row>
+    <row r="3" spans="1:9" s="5" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="87">
         <v>1</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="88" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="16">
@@ -7617,9 +7883,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="6" customFormat="1" ht="124.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="76"/>
-      <c r="B4" s="78"/>
+    <row r="4" spans="1:9" s="6" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="87"/>
+      <c r="B4" s="89"/>
       <c r="C4" s="16">
         <v>1.2</v>
       </c>
@@ -7638,9 +7904,9 @@
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
     </row>
-    <row r="5" spans="1:9" s="6" customFormat="1" ht="160.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="76"/>
-      <c r="B5" s="78"/>
+    <row r="5" spans="1:9" s="6" customFormat="1" ht="160.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="87"/>
+      <c r="B5" s="89"/>
       <c r="C5" s="16">
         <v>1.3</v>
       </c>
@@ -7659,9 +7925,9 @@
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
     </row>
-    <row r="6" spans="1:9" s="6" customFormat="1" ht="154.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="76"/>
-      <c r="B6" s="78"/>
+    <row r="6" spans="1:9" s="6" customFormat="1" ht="154.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="87"/>
+      <c r="B6" s="89"/>
       <c r="C6" s="16">
         <v>1.4</v>
       </c>
@@ -7680,9 +7946,9 @@
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
     </row>
-    <row r="7" spans="1:9" s="6" customFormat="1" ht="116" x14ac:dyDescent="0.35">
-      <c r="A7" s="76"/>
-      <c r="B7" s="78"/>
+    <row r="7" spans="1:9" s="6" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="87"/>
+      <c r="B7" s="89"/>
       <c r="C7" s="16">
         <v>1.5</v>
       </c>
@@ -7701,9 +7967,9 @@
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
     </row>
-    <row r="8" spans="1:9" s="6" customFormat="1" ht="124.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" s="6" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50"/>
-      <c r="B8" s="78"/>
+      <c r="B8" s="89"/>
       <c r="C8" s="16">
         <v>1.6</v>
       </c>
@@ -7722,9 +7988,9 @@
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
     </row>
-    <row r="9" spans="1:9" s="6" customFormat="1" ht="152.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" s="6" customFormat="1" ht="152.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="50"/>
-      <c r="B9" s="78"/>
+      <c r="B9" s="89"/>
       <c r="C9" s="16">
         <v>1.7</v>
       </c>
@@ -7743,9 +8009,9 @@
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
     </row>
-    <row r="10" spans="1:9" s="6" customFormat="1" ht="295.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" s="6" customFormat="1" ht="295.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="50"/>
-      <c r="B10" s="79"/>
+      <c r="B10" s="90"/>
       <c r="C10" s="16">
         <v>1.8</v>
       </c>
@@ -7764,11 +8030,11 @@
       <c r="H10" s="16"/>
       <c r="I10" s="51"/>
     </row>
-    <row r="11" spans="1:9" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="72">
+    <row r="11" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="83">
         <v>5</v>
       </c>
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="83" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="18">
@@ -7793,9 +8059,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="73"/>
-      <c r="B12" s="73"/>
+    <row r="12" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="84"/>
+      <c r="B12" s="84"/>
       <c r="C12" s="18">
         <v>5.2</v>
       </c>
@@ -7814,9 +8080,9 @@
       <c r="H12" s="20"/>
       <c r="I12" s="18"/>
     </row>
-    <row r="13" spans="1:9" s="6" customFormat="1" ht="174" x14ac:dyDescent="0.35">
-      <c r="A13" s="73"/>
-      <c r="B13" s="73"/>
+    <row r="13" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="84"/>
+      <c r="B13" s="84"/>
       <c r="C13" s="18">
         <v>5.3</v>
       </c>
@@ -7835,9 +8101,9 @@
       <c r="H13" s="20"/>
       <c r="I13" s="18"/>
     </row>
-    <row r="14" spans="1:9" s="14" customFormat="1" ht="232" x14ac:dyDescent="0.35">
-      <c r="A14" s="73"/>
-      <c r="B14" s="73"/>
+    <row r="14" spans="1:9" s="14" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="84"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="21">
         <v>5.4</v>
       </c>
@@ -7856,9 +8122,9 @@
       <c r="H14" s="23"/>
       <c r="I14" s="21"/>
     </row>
-    <row r="15" spans="1:9" s="14" customFormat="1" ht="174" x14ac:dyDescent="0.35">
-      <c r="A15" s="74"/>
-      <c r="B15" s="74"/>
+    <row r="15" spans="1:9" s="14" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="85"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="21">
         <v>5.5</v>
       </c>
@@ -7877,11 +8143,11 @@
       <c r="H15" s="23"/>
       <c r="I15" s="21"/>
     </row>
-    <row r="16" spans="1:9" s="14" customFormat="1" ht="174" x14ac:dyDescent="0.35">
-      <c r="A16" s="58">
+    <row r="16" spans="1:9" s="14" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="69">
         <v>6</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="69" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="24">
@@ -7906,9 +8172,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="6" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A17" s="59"/>
-      <c r="B17" s="59"/>
+    <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A17" s="70"/>
+      <c r="B17" s="70"/>
       <c r="C17" s="24">
         <v>6.2</v>
       </c>
@@ -7927,9 +8193,9 @@
       <c r="H17" s="26"/>
       <c r="I17" s="24"/>
     </row>
-    <row r="18" spans="1:9" s="6" customFormat="1" ht="174" x14ac:dyDescent="0.35">
-      <c r="A18" s="59"/>
-      <c r="B18" s="59"/>
+    <row r="18" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="70"/>
+      <c r="B18" s="70"/>
       <c r="C18" s="24">
         <v>6.3</v>
       </c>
@@ -7948,9 +8214,9 @@
       <c r="H18" s="26"/>
       <c r="I18" s="24"/>
     </row>
-    <row r="19" spans="1:9" s="6" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="59"/>
-      <c r="B19" s="59"/>
+    <row r="19" spans="1:9" s="6" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="70"/>
+      <c r="B19" s="70"/>
       <c r="C19" s="27">
         <v>6.4</v>
       </c>
@@ -7973,9 +8239,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A20" s="52"/>
-      <c r="B20" s="59"/>
+      <c r="B20" s="70"/>
       <c r="C20" s="24">
         <v>6.5</v>
       </c>
@@ -7994,9 +8260,9 @@
       <c r="H20" s="26"/>
       <c r="I20" s="24"/>
     </row>
-    <row r="21" spans="1:9" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="52"/>
-      <c r="B21" s="70"/>
+      <c r="B21" s="81"/>
       <c r="C21" s="24">
         <v>6.6</v>
       </c>
@@ -8015,11 +8281,11 @@
       <c r="H21" s="26"/>
       <c r="I21" s="24"/>
     </row>
-    <row r="22" spans="1:9" s="6" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A22" s="60">
+    <row r="22" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A22" s="71">
         <v>7</v>
       </c>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="69" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="24">
@@ -8044,9 +8310,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="61"/>
-      <c r="B23" s="59"/>
+    <row r="23" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A23" s="72"/>
+      <c r="B23" s="70"/>
       <c r="C23" s="24">
         <v>7.2</v>
       </c>
@@ -8067,9 +8333,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="6" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="61"/>
-      <c r="B24" s="59"/>
+    <row r="24" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="72"/>
+      <c r="B24" s="70"/>
       <c r="C24" s="24">
         <v>7.3</v>
       </c>
@@ -8088,9 +8354,9 @@
       <c r="H24" s="26"/>
       <c r="I24" s="24"/>
     </row>
-    <row r="25" spans="1:9" s="6" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="62"/>
-      <c r="B25" s="59"/>
+    <row r="25" spans="1:9" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="73"/>
+      <c r="B25" s="70"/>
       <c r="C25" s="24">
         <v>7.4</v>
       </c>
@@ -8109,9 +8375,9 @@
       <c r="H25" s="26"/>
       <c r="I25" s="24"/>
     </row>
-    <row r="26" spans="1:9" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A26" s="52"/>
-      <c r="B26" s="70"/>
+      <c r="B26" s="81"/>
       <c r="C26" s="24">
         <v>7.5</v>
       </c>
@@ -8130,11 +8396,11 @@
       <c r="H26" s="26"/>
       <c r="I26" s="24"/>
     </row>
-    <row r="27" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="67">
+    <row r="27" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="78">
         <v>8</v>
       </c>
-      <c r="B27" s="67" t="s">
+      <c r="B27" s="78" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="28">
@@ -8157,9 +8423,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="68"/>
-      <c r="B28" s="68"/>
+    <row r="28" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="79"/>
+      <c r="B28" s="79"/>
       <c r="C28" s="28">
         <v>9.3000000000000007</v>
       </c>
@@ -8180,9 +8446,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="69"/>
-      <c r="B29" s="69"/>
+    <row r="29" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="80"/>
+      <c r="B29" s="80"/>
       <c r="C29" s="28">
         <v>9.4</v>
       </c>
@@ -8203,11 +8469,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A30" s="65">
+    <row r="30" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="76">
         <v>12</v>
       </c>
-      <c r="B30" s="65" t="s">
+      <c r="B30" s="76" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="30">
@@ -8232,9 +8498,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A31" s="65"/>
-      <c r="B31" s="65"/>
+    <row r="31" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="76"/>
+      <c r="B31" s="76"/>
       <c r="C31" s="30">
         <v>12.2</v>
       </c>
@@ -8257,9 +8523,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A32" s="65"/>
-      <c r="B32" s="65"/>
+    <row r="32" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="76"/>
+      <c r="B32" s="76"/>
       <c r="C32" s="30">
         <v>12.3</v>
       </c>
@@ -8282,9 +8548,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="6" customFormat="1" ht="123.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="65"/>
-      <c r="B33" s="65"/>
+    <row r="33" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="76"/>
+      <c r="B33" s="76"/>
       <c r="C33" s="30">
         <v>12.4</v>
       </c>
@@ -8307,9 +8573,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="65"/>
-      <c r="B34" s="65"/>
+    <row r="34" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="76"/>
+      <c r="B34" s="76"/>
       <c r="C34" s="30">
         <v>12.5</v>
       </c>
@@ -8332,11 +8598,11 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="66">
+    <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="77">
         <v>14</v>
       </c>
-      <c r="B35" s="66" t="s">
+      <c r="B35" s="77" t="s">
         <v>70</v>
       </c>
       <c r="C35" s="34">
@@ -8361,9 +8627,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="66"/>
-      <c r="B36" s="66"/>
+    <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="77"/>
+      <c r="B36" s="77"/>
       <c r="C36" s="34">
         <v>14.2</v>
       </c>
@@ -8386,9 +8652,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="66"/>
-      <c r="B37" s="66"/>
+    <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="77"/>
+      <c r="B37" s="77"/>
       <c r="C37" s="34">
         <v>14.3</v>
       </c>
@@ -8411,9 +8677,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A38" s="66"/>
-      <c r="B38" s="66"/>
+    <row r="38" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="77"/>
+      <c r="B38" s="77"/>
       <c r="C38" s="34">
         <v>14.4</v>
       </c>
@@ -8436,9 +8702,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="66"/>
-      <c r="B39" s="66"/>
+    <row r="39" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="77"/>
+      <c r="B39" s="77"/>
       <c r="C39" s="34">
         <v>14.5</v>
       </c>
@@ -8461,9 +8727,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="66"/>
-      <c r="B40" s="66"/>
+    <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="77"/>
+      <c r="B40" s="77"/>
       <c r="C40" s="34">
         <v>14.6</v>
       </c>
@@ -8486,9 +8752,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="66"/>
-      <c r="B41" s="66"/>
+    <row r="41" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="77"/>
+      <c r="B41" s="77"/>
       <c r="C41" s="34">
         <v>14.7</v>
       </c>
@@ -8511,9 +8777,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="66"/>
-      <c r="B42" s="66"/>
+    <row r="42" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="77"/>
+      <c r="B42" s="77"/>
       <c r="C42" s="34">
         <v>14.8</v>
       </c>
@@ -8536,9 +8802,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="66"/>
-      <c r="B43" s="66"/>
+    <row r="43" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="77"/>
+      <c r="B43" s="77"/>
       <c r="C43" s="34">
         <v>14.9</v>
       </c>
@@ -8561,9 +8827,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A44" s="66"/>
-      <c r="B44" s="66"/>
+    <row r="44" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="77"/>
+      <c r="B44" s="77"/>
       <c r="C44" s="34">
         <v>14.1</v>
       </c>
@@ -8586,9 +8852,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="66"/>
-      <c r="B45" s="66"/>
+    <row r="45" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="77"/>
+      <c r="B45" s="77"/>
       <c r="C45" s="34">
         <v>14.11</v>
       </c>
@@ -8611,11 +8877,11 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A46" s="63">
+    <row r="46" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A46" s="74">
         <v>15</v>
       </c>
-      <c r="B46" s="63" t="s">
+      <c r="B46" s="74" t="s">
         <v>74</v>
       </c>
       <c r="C46" s="37">
@@ -8640,9 +8906,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A47" s="64"/>
-      <c r="B47" s="64"/>
+    <row r="47" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="75"/>
+      <c r="B47" s="75"/>
       <c r="C47" s="37">
         <v>15.2</v>
       </c>
@@ -8665,9 +8931,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A48" s="64"/>
-      <c r="B48" s="64"/>
+    <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="75"/>
+      <c r="B48" s="75"/>
       <c r="C48" s="37">
         <v>15.3</v>
       </c>
@@ -8690,9 +8956,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="64"/>
-      <c r="B49" s="64"/>
+    <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="75"/>
+      <c r="B49" s="75"/>
       <c r="C49" s="37">
         <v>15.4</v>
       </c>
@@ -8715,9 +8981,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A50" s="64"/>
-      <c r="B50" s="64"/>
+    <row r="50" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="75"/>
+      <c r="B50" s="75"/>
       <c r="C50" s="37">
         <v>15.5</v>
       </c>
@@ -8740,9 +9006,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A51" s="64"/>
-      <c r="B51" s="64"/>
+    <row r="51" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="75"/>
+      <c r="B51" s="75"/>
       <c r="C51" s="37">
         <v>15.6</v>
       </c>
@@ -8765,9 +9031,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="64"/>
-      <c r="B52" s="64"/>
+    <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="75"/>
+      <c r="B52" s="75"/>
       <c r="C52" s="37">
         <v>15.7</v>
       </c>
@@ -8790,9 +9056,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A53" s="64"/>
-      <c r="B53" s="64"/>
+    <row r="53" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="75"/>
+      <c r="B53" s="75"/>
       <c r="C53" s="37">
         <v>15.8</v>
       </c>
@@ -8815,11 +9081,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="54" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="86">
+    <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="97">
         <v>16</v>
       </c>
-      <c r="B54" s="86" t="s">
+      <c r="B54" s="97" t="s">
         <v>89</v>
       </c>
       <c r="C54" s="39">
@@ -8844,9 +9110,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="86"/>
-      <c r="B55" s="86"/>
+    <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="97"/>
+      <c r="B55" s="97"/>
       <c r="C55" s="39">
         <v>16.2</v>
       </c>
@@ -8869,9 +9135,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="56" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="86"/>
-      <c r="B56" s="86"/>
+    <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A56" s="97"/>
+      <c r="B56" s="97"/>
       <c r="C56" s="39">
         <v>16.3</v>
       </c>
@@ -8894,9 +9160,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="57" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A57" s="86"/>
-      <c r="B57" s="86"/>
+    <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A57" s="97"/>
+      <c r="B57" s="97"/>
       <c r="C57" s="39">
         <v>16.399999999999999</v>
       </c>
@@ -8919,9 +9185,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="86"/>
-      <c r="B58" s="86"/>
+    <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A58" s="97"/>
+      <c r="B58" s="97"/>
       <c r="C58" s="39">
         <v>16.5</v>
       </c>
@@ -8944,9 +9210,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="64"/>
-      <c r="B59" s="64"/>
+    <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A59" s="75"/>
+      <c r="B59" s="75"/>
       <c r="C59" s="39">
         <v>16.600000000000001</v>
       </c>
@@ -8969,11 +9235,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="87">
+    <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A60" s="98">
         <v>17</v>
       </c>
-      <c r="B60" s="90" t="s">
+      <c r="B60" s="101" t="s">
         <v>105</v>
       </c>
       <c r="C60" s="42">
@@ -8998,9 +9264,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="61" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="88"/>
-      <c r="B61" s="90"/>
+    <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="99"/>
+      <c r="B61" s="101"/>
       <c r="C61" s="42">
         <v>17.2</v>
       </c>
@@ -9023,9 +9289,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A62" s="88"/>
-      <c r="B62" s="90"/>
+    <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A62" s="99"/>
+      <c r="B62" s="101"/>
       <c r="C62" s="42">
         <v>17.3</v>
       </c>
@@ -9048,9 +9314,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="88"/>
-      <c r="B63" s="90"/>
+    <row r="63" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A63" s="99"/>
+      <c r="B63" s="101"/>
       <c r="C63" s="42">
         <v>17.399999999999999</v>
       </c>
@@ -9073,9 +9339,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A64" s="89"/>
-      <c r="B64" s="90"/>
+    <row r="64" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A64" s="100"/>
+      <c r="B64" s="101"/>
       <c r="C64" s="42">
         <v>17.5</v>
       </c>
@@ -9098,11 +9364,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="65" spans="1:12" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A65" s="91">
+    <row r="65" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A65" s="102">
         <v>18</v>
       </c>
-      <c r="B65" s="72" t="s">
+      <c r="B65" s="83" t="s">
         <v>279</v>
       </c>
       <c r="C65" s="18">
@@ -9127,9 +9393,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="66" spans="1:12" s="6" customFormat="1" ht="250.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="64"/>
-      <c r="B66" s="73"/>
+    <row r="66" spans="1:12" s="6" customFormat="1" ht="250.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="75"/>
+      <c r="B66" s="84"/>
       <c r="C66" s="18">
         <v>18.2</v>
       </c>
@@ -9152,9 +9418,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="67" spans="1:12" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="64"/>
-      <c r="B67" s="73"/>
+    <row r="67" spans="1:12" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="75"/>
+      <c r="B67" s="84"/>
       <c r="C67" s="18">
         <v>18.3</v>
       </c>
@@ -9177,9 +9443,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="1:12" s="6" customFormat="1" ht="246.5" x14ac:dyDescent="0.35">
-      <c r="A68" s="64"/>
-      <c r="B68" s="73"/>
+    <row r="68" spans="1:12" s="6" customFormat="1" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="75"/>
+      <c r="B68" s="84"/>
       <c r="C68" s="18">
         <v>18.399999999999999</v>
       </c>
@@ -9202,9 +9468,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:12" s="6" customFormat="1" ht="216" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" s="6" customFormat="1" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="48"/>
-      <c r="B69" s="74"/>
+      <c r="B69" s="85"/>
       <c r="C69" s="18">
         <v>18.5</v>
       </c>
@@ -9223,11 +9489,11 @@
       <c r="H69" s="18"/>
       <c r="I69" s="18"/>
     </row>
-    <row r="70" spans="1:12" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A70" s="80">
+    <row r="70" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A70" s="91">
         <v>19</v>
       </c>
-      <c r="B70" s="83" t="s">
+      <c r="B70" s="94" t="s">
         <v>120</v>
       </c>
       <c r="C70" s="44">
@@ -9248,9 +9514,9 @@
       <c r="H70" s="44"/>
       <c r="I70" s="47"/>
     </row>
-    <row r="71" spans="1:12" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="81"/>
-      <c r="B71" s="84"/>
+    <row r="71" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="92"/>
+      <c r="B71" s="95"/>
       <c r="C71" s="15">
         <v>19.2</v>
       </c>
@@ -9269,9 +9535,9 @@
       <c r="H71" s="44"/>
       <c r="I71" s="47"/>
     </row>
-    <row r="72" spans="1:12" s="6" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="82"/>
-      <c r="B72" s="85"/>
+    <row r="72" spans="1:12" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="93"/>
+      <c r="B72" s="96"/>
       <c r="C72" s="53">
         <v>19.3</v>
       </c>
@@ -9292,11 +9558,11 @@
         <v>313</v>
       </c>
     </row>
-    <row r="73" spans="1:12" s="6" customFormat="1" ht="203" x14ac:dyDescent="0.35">
-      <c r="A73" s="80">
+    <row r="73" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="91">
         <v>20</v>
       </c>
-      <c r="B73" s="83" t="s">
+      <c r="B73" s="94" t="s">
         <v>126</v>
       </c>
       <c r="C73" s="44">
@@ -9317,9 +9583,9 @@
       <c r="H73" s="44"/>
       <c r="I73" s="47"/>
     </row>
-    <row r="74" spans="1:12" s="6" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A74" s="81"/>
-      <c r="B74" s="84"/>
+    <row r="74" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A74" s="92"/>
+      <c r="B74" s="95"/>
       <c r="C74" s="15">
         <v>20.2</v>
       </c>
@@ -9341,9 +9607,9 @@
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
     </row>
-    <row r="75" spans="1:12" s="6" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A75" s="82"/>
-      <c r="B75" s="84"/>
+    <row r="75" spans="1:12" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="93"/>
+      <c r="B75" s="95"/>
       <c r="C75" s="56">
         <v>20.3</v>
       </c>
@@ -9367,9 +9633,9 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
     </row>
-    <row r="76" spans="1:12" s="6" customFormat="1" ht="333.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" s="6" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A76" s="49"/>
-      <c r="B76" s="85"/>
+      <c r="B76" s="96"/>
       <c r="C76" s="56">
         <v>20.399999999999999</v>
       </c>
@@ -9393,11 +9659,11 @@
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
     </row>
-    <row r="77" spans="1:12" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A77" s="80">
+    <row r="77" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A77" s="91">
         <v>21</v>
       </c>
-      <c r="B77" s="83" t="s">
+      <c r="B77" s="94" t="s">
         <v>129</v>
       </c>
       <c r="C77" s="44">
@@ -9418,9 +9684,9 @@
       <c r="H77" s="44"/>
       <c r="I77" s="47"/>
     </row>
-    <row r="78" spans="1:12" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A78" s="81"/>
-      <c r="B78" s="84"/>
+    <row r="78" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="92"/>
+      <c r="B78" s="95"/>
       <c r="C78" s="15">
         <v>21.2</v>
       </c>
@@ -9439,9 +9705,9 @@
       <c r="H78" s="44"/>
       <c r="I78" s="47"/>
     </row>
-    <row r="79" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="82"/>
-      <c r="B79" s="85"/>
+    <row r="79" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A79" s="93"/>
+      <c r="B79" s="96"/>
       <c r="C79" s="32">
         <v>21.3</v>
       </c>
@@ -9456,11 +9722,11 @@
       <c r="H79" s="32"/>
       <c r="I79" s="33"/>
     </row>
-    <row r="80" spans="1:12" ht="261" x14ac:dyDescent="0.35">
-      <c r="A80" s="80">
+    <row r="80" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A80" s="91">
         <v>22</v>
       </c>
-      <c r="B80" s="83" t="s">
+      <c r="B80" s="94" t="s">
         <v>133</v>
       </c>
       <c r="C80" s="44">
@@ -9481,9 +9747,9 @@
       <c r="H80" s="44"/>
       <c r="I80" s="47"/>
     </row>
-    <row r="81" spans="1:9" ht="261" x14ac:dyDescent="0.35">
-      <c r="A81" s="81"/>
-      <c r="B81" s="84"/>
+    <row r="81" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A81" s="92"/>
+      <c r="B81" s="95"/>
       <c r="C81" s="15">
         <v>22.2</v>
       </c>
@@ -9502,9 +9768,9 @@
       <c r="H81" s="44"/>
       <c r="I81" s="47"/>
     </row>
-    <row r="82" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A82" s="82"/>
-      <c r="B82" s="85"/>
+    <row r="82" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A82" s="93"/>
+      <c r="B82" s="96"/>
       <c r="C82" s="32">
         <v>22.3</v>
       </c>
@@ -9519,26 +9785,26 @@
       <c r="H82" s="32"/>
       <c r="I82" s="33"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="E83" s="11"/>
       <c r="H83" s="3"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="I84" s="2"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="I85" s="2"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -9549,7 +9815,7 @@
       <c r="H86" s="7"/>
       <c r="I86" s="7"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -9560,7 +9826,7 @@
       <c r="H87" s="10"/>
       <c r="I87" s="10"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D88" s="10"/>
       <c r="E88" s="10"/>
       <c r="F88" s="10"/>
@@ -9568,7 +9834,7 @@
       <c r="H88" s="10"/>
       <c r="I88" s="10"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B89" s="3"/>
       <c r="D89" s="10"/>
       <c r="E89" s="10"/>
@@ -9577,7 +9843,7 @@
       <c r="H89" s="10"/>
       <c r="I89" s="10"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D90" s="10"/>
       <c r="E90" s="10"/>
       <c r="F90" s="10"/>
@@ -9585,7 +9851,7 @@
       <c r="H90" s="10"/>
       <c r="I90" s="10"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D91" s="10"/>
       <c r="E91" s="10"/>
       <c r="F91" s="10"/>
@@ -9593,7 +9859,7 @@
       <c r="H91" s="10"/>
       <c r="I91" s="10"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D92" s="10"/>
       <c r="E92" s="10"/>
       <c r="F92" s="10"/>
@@ -9601,7 +9867,7 @@
       <c r="H92" s="10"/>
       <c r="I92" s="10"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D93" s="10"/>
       <c r="E93" s="10"/>
       <c r="F93" s="10"/>
@@ -9609,7 +9875,7 @@
       <c r="H93" s="10"/>
       <c r="I93" s="10"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D94" s="10"/>
       <c r="E94" s="10"/>
       <c r="F94" s="10"/>
@@ -9658,7 +9924,7 @@
     <mergeCell ref="B16:B21"/>
     <mergeCell ref="B22:B26"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -9668,15 +9934,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="18.1796875" customWidth="1"/>
-    <col min="5" max="5" width="24.90625" customWidth="1"/>
-    <col min="6" max="6" width="27.36328125" customWidth="1"/>
-    <col min="7" max="7" width="36.1796875" customWidth="1"/>
+    <col min="4" max="4" width="18.21875" customWidth="1"/>
+    <col min="5" max="5" width="24.88671875" customWidth="1"/>
+    <col min="6" max="6" width="27.33203125" customWidth="1"/>
+    <col min="7" max="7" width="36.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -9688,7 +9954,7 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -9700,7 +9966,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -9724,7 +9990,7 @@
       </c>
       <c r="J3" s="9"/>
     </row>
-    <row r="4" spans="1:10" ht="348" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -9748,7 +10014,7 @@
       </c>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" ht="362.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -9772,7 +10038,7 @@
       </c>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10" ht="348" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -9796,7 +10062,7 @@
       </c>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10" ht="406" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -9820,7 +10086,7 @@
       </c>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10" ht="333.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -9844,7 +10110,7 @@
       </c>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -9868,7 +10134,7 @@
       </c>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10" ht="348" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -9892,7 +10158,7 @@
       </c>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:10" ht="319" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -9916,7 +10182,7 @@
       </c>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:10" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -9940,7 +10206,7 @@
       </c>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:10" ht="391.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="388.8" x14ac:dyDescent="0.3">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -9964,7 +10230,7 @@
       </c>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:10" ht="290" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="288" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -9988,7 +10254,7 @@
       </c>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -10000,7 +10266,7 @@
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -10012,7 +10278,7 @@
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -10024,7 +10290,7 @@
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -10036,7 +10302,7 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -10048,7 +10314,7 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -10060,7 +10326,7 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -10072,7 +10338,7 @@
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -10084,7 +10350,7 @@
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -10096,7 +10362,7 @@
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -10108,7 +10374,7 @@
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -10120,7 +10386,7 @@
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -10132,7 +10398,7 @@
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -10144,7 +10410,7 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -10156,7 +10422,7 @@
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -10168,7 +10434,7 @@
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -10180,7 +10446,7 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -10192,7 +10458,7 @@
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -10204,63 +10470,63 @@
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -10274,205 +10540,206 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0802363A-09BC-4F89-B136-783D2DDEAFD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0802363A-09BC-4F89-B136-783D2DDEAFD1}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.7265625" customWidth="1"/>
-    <col min="2" max="2" width="43.54296875" customWidth="1"/>
-    <col min="3" max="3" width="55.1796875" customWidth="1"/>
-    <col min="4" max="4" width="70.26953125" customWidth="1"/>
-    <col min="5" max="5" width="89.81640625" customWidth="1"/>
+    <col min="1" max="1" width="21.77734375" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" customWidth="1"/>
+    <col min="3" max="3" width="55.21875" customWidth="1"/>
+    <col min="4" max="4" width="70.21875" customWidth="1"/>
+    <col min="5" max="5" width="89.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:5" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="68" t="s">
         <v>332</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="68" t="s">
         <v>333</v>
       </c>
-      <c r="C1" s="92" t="s">
+      <c r="C1" s="68" t="s">
         <v>334</v>
       </c>
-      <c r="D1" s="92" t="s">
+      <c r="D1" s="68" t="s">
         <v>335</v>
       </c>
-      <c r="E1" s="92" t="s">
+      <c r="E1" s="68" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="203" x14ac:dyDescent="0.35">
-      <c r="A2" s="93">
+    <row r="2" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A2" s="58">
         <v>5.0999999999999996</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="59" t="s">
         <v>336</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="59" t="s">
         <v>337</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="59" t="s">
         <v>338</v>
       </c>
-      <c r="E2" s="93" t="s">
+      <c r="E2" s="60" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="58">
+        <v>5.2</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>339</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>340</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>341</v>
+      </c>
+      <c r="E3" s="60" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="58">
+        <v>5.3</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>342</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>343</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="58">
+        <v>5.4</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>336</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>344</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>345</v>
+      </c>
+      <c r="E5" s="58" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="61">
+        <v>5.5</v>
+      </c>
+      <c r="B6" s="62" t="s">
+        <v>346</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>347</v>
+      </c>
+      <c r="D6" s="62" t="s">
+        <v>348</v>
+      </c>
+      <c r="E6" s="63" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="58">
+        <v>5.6</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>349</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>350</v>
+      </c>
+      <c r="D7" s="59" t="s">
+        <v>351</v>
+      </c>
+      <c r="E7" s="60" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="64">
+        <v>5.7</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>352</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>353</v>
+      </c>
+      <c r="D8" s="66" t="s">
+        <v>373</v>
+      </c>
+      <c r="E8" s="64" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="145" x14ac:dyDescent="0.35">
-      <c r="A3" s="93">
-        <v>5.2</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="E3" s="93" t="s">
+    <row r="9" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="58">
+        <v>5.8</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>354</v>
+      </c>
+      <c r="C9" s="59" t="s">
+        <v>355</v>
+      </c>
+      <c r="D9" s="59" t="s">
+        <v>356</v>
+      </c>
+      <c r="E9" s="58" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="174" x14ac:dyDescent="0.35">
-      <c r="A4" s="93">
-        <v>5.3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="E4" s="93" t="s">
+    <row r="10" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="58">
+        <v>5.9</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>357</v>
+      </c>
+      <c r="C10" s="59" t="s">
+        <v>358</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>359</v>
+      </c>
+      <c r="E10" s="58" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="93">
-        <v>5.4</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="E5" s="93" t="s">
+    <row r="11" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A11" s="67">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B11" s="59" t="s">
+        <v>360</v>
+      </c>
+      <c r="C11" s="59" t="s">
+        <v>361</v>
+      </c>
+      <c r="D11" s="59" t="s">
+        <v>362</v>
+      </c>
+      <c r="E11" s="58" t="s">
         <v>367</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="93">
-        <v>5.5</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="E6" s="93" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="174" x14ac:dyDescent="0.35">
-      <c r="A7" s="93">
-        <v>5.6</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="E7" s="93" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="93">
-        <v>5.7</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>353</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="E8" s="93" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="145" x14ac:dyDescent="0.35">
-      <c r="A9" s="93">
-        <v>5.8</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="E9" s="93" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="145" x14ac:dyDescent="0.35">
-      <c r="A10" s="93">
-        <v>5.9</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>358</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>360</v>
-      </c>
-      <c r="E10" s="93" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="145" x14ac:dyDescent="0.35">
-      <c r="A11" s="94">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="E11" s="93" t="s">
-        <v>373</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Business Analysis/checkupp_product_backlog.xlsx
+++ b/Business Analysis/checkupp_product_backlog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CAF1AC-1AFC-4D00-884A-F47A2BAA0FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443E0692-E891-49C3-BE56-000C29AAC3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6577,14 +6577,18 @@
     </r>
   </si>
   <si>
+    <t>I can access which vaccinations belong to that category</t>
+  </si>
+  <si>
     <r>
       <t>1.</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> The </t>
@@ -6593,8 +6597,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Children (0–4 years)</t>
@@ -6602,8 +6607,9 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> card must be displayed under </t>
@@ -6612,8 +6618,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Other Categories</t>
@@ -6621,8 +6628,9 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> when the configured user's age is </t>
@@ -6631,8 +6639,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>16 years or older</t>
@@ -6640,8 +6649,9 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">.
@@ -6651,8 +6661,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2.</t>
@@ -6660,8 +6671,9 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> The Children card must not be displayed when the configured user's age is below 16.
@@ -6671,8 +6683,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3.</t>
@@ -6680,8 +6693,9 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> The boundary value of exactly 16 years must result in the Children card being displayed.
@@ -6691,8 +6705,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>4.</t>
@@ -6700,8 +6715,9 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Visibility of the Children card must not depend on gender or pregnancy status.
@@ -6711,8 +6727,9 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>5.</t>
@@ -6720,11 +6737,45 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Selecting the card must display the vaccination information configured for children aged 0–4 years.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Must be obscured in MVP.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
     </r>
   </si>
   <si>
@@ -6819,7 +6870,18 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Children (0–4 years) must follow the 16+ visibility rule.</t>
+      <t xml:space="preserve"> Children (0–4 years) must follow the 16+ visibility rule</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. (Must be obscured in MVP)</t>
     </r>
     <r>
       <rPr>
@@ -6874,16 +6936,13 @@
       </rPr>
       <t xml:space="preserve"> Changes to the configured test profile must result in the appropriate category visibility changes when the screen is re-rendered.</t>
     </r>
-  </si>
-  <si>
-    <t>I can access which vaccinations belong to that category</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7062,6 +7121,28 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-9.9978637043366805E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="21">
@@ -7460,9 +7541,6 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -7476,72 +7554,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7565,6 +7577,9 @@
     <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7579,6 +7594,72 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7797,47 +7878,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L94"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="64.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="72.5546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" style="3" customWidth="1"/>
-    <col min="10" max="12" width="8.88671875" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="5.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.90625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="64.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="72.54296875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.6328125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.36328125" style="3" customWidth="1"/>
+    <col min="10" max="12" width="8.90625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="84" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="82" t="s">
+      <c r="D1" s="84" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="75"/>
       <c r="F1" s="75"/>
-      <c r="G1" s="86" t="s">
+      <c r="G1" s="85" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="82" t="s">
+      <c r="H1" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="82" t="s">
+      <c r="I1" s="84" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="75"/>
       <c r="B2" s="75"/>
       <c r="C2" s="75"/>
@@ -7850,15 +7931,15 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="86"/>
+      <c r="G2" s="85"/>
       <c r="H2" s="75"/>
       <c r="I2" s="75"/>
     </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="87">
+    <row r="3" spans="1:9" s="5" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="86">
         <v>1</v>
       </c>
-      <c r="B3" s="88" t="s">
+      <c r="B3" s="87" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="16">
@@ -7883,9 +7964,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="6" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="87"/>
-      <c r="B4" s="89"/>
+    <row r="4" spans="1:9" s="6" customFormat="1" ht="124.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="86"/>
+      <c r="B4" s="88"/>
       <c r="C4" s="16">
         <v>1.2</v>
       </c>
@@ -7904,9 +7985,9 @@
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
     </row>
-    <row r="5" spans="1:9" s="6" customFormat="1" ht="160.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="87"/>
-      <c r="B5" s="89"/>
+    <row r="5" spans="1:9" s="6" customFormat="1" ht="160.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="86"/>
+      <c r="B5" s="88"/>
       <c r="C5" s="16">
         <v>1.3</v>
       </c>
@@ -7925,9 +8006,9 @@
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
     </row>
-    <row r="6" spans="1:9" s="6" customFormat="1" ht="154.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="87"/>
-      <c r="B6" s="89"/>
+    <row r="6" spans="1:9" s="6" customFormat="1" ht="154.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="86"/>
+      <c r="B6" s="88"/>
       <c r="C6" s="16">
         <v>1.4</v>
       </c>
@@ -7946,9 +8027,9 @@
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
     </row>
-    <row r="7" spans="1:9" s="6" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="87"/>
-      <c r="B7" s="89"/>
+    <row r="7" spans="1:9" s="6" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+      <c r="A7" s="86"/>
+      <c r="B7" s="88"/>
       <c r="C7" s="16">
         <v>1.5</v>
       </c>
@@ -7967,9 +8048,9 @@
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
     </row>
-    <row r="8" spans="1:9" s="6" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="6" customFormat="1" ht="124.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="50"/>
-      <c r="B8" s="89"/>
+      <c r="B8" s="88"/>
       <c r="C8" s="16">
         <v>1.6</v>
       </c>
@@ -7988,9 +8069,9 @@
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
     </row>
-    <row r="9" spans="1:9" s="6" customFormat="1" ht="152.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="6" customFormat="1" ht="152.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="50"/>
-      <c r="B9" s="89"/>
+      <c r="B9" s="88"/>
       <c r="C9" s="16">
         <v>1.7</v>
       </c>
@@ -8009,9 +8090,9 @@
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
     </row>
-    <row r="10" spans="1:9" s="6" customFormat="1" ht="295.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="6" customFormat="1" ht="295.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="50"/>
-      <c r="B10" s="90"/>
+      <c r="B10" s="89"/>
       <c r="C10" s="16">
         <v>1.8</v>
       </c>
@@ -8030,11 +8111,11 @@
       <c r="H10" s="16"/>
       <c r="I10" s="51"/>
     </row>
-    <row r="11" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="83">
+    <row r="11" spans="1:9" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="81">
         <v>5</v>
       </c>
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="81" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="18">
@@ -8059,9 +8140,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="84"/>
-      <c r="B12" s="84"/>
+    <row r="12" spans="1:9" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="82"/>
+      <c r="B12" s="82"/>
       <c r="C12" s="18">
         <v>5.2</v>
       </c>
@@ -8080,9 +8161,9 @@
       <c r="H12" s="20"/>
       <c r="I12" s="18"/>
     </row>
-    <row r="13" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="84"/>
-      <c r="B13" s="84"/>
+    <row r="13" spans="1:9" s="6" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+      <c r="A13" s="82"/>
+      <c r="B13" s="82"/>
       <c r="C13" s="18">
         <v>5.3</v>
       </c>
@@ -8101,9 +8182,9 @@
       <c r="H13" s="20"/>
       <c r="I13" s="18"/>
     </row>
-    <row r="14" spans="1:9" s="14" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="84"/>
-      <c r="B14" s="84"/>
+    <row r="14" spans="1:9" s="14" customFormat="1" ht="232" x14ac:dyDescent="0.35">
+      <c r="A14" s="82"/>
+      <c r="B14" s="82"/>
       <c r="C14" s="21">
         <v>5.4</v>
       </c>
@@ -8122,9 +8203,9 @@
       <c r="H14" s="23"/>
       <c r="I14" s="21"/>
     </row>
-    <row r="15" spans="1:9" s="14" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="85"/>
-      <c r="B15" s="85"/>
+    <row r="15" spans="1:9" s="14" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+      <c r="A15" s="83"/>
+      <c r="B15" s="83"/>
       <c r="C15" s="21">
         <v>5.5</v>
       </c>
@@ -8143,11 +8224,11 @@
       <c r="H15" s="23"/>
       <c r="I15" s="21"/>
     </row>
-    <row r="16" spans="1:9" s="14" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="69">
+    <row r="16" spans="1:9" s="14" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+      <c r="A16" s="90">
         <v>6</v>
       </c>
-      <c r="B16" s="69" t="s">
+      <c r="B16" s="90" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="24">
@@ -8172,9 +8253,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="70"/>
-      <c r="B17" s="70"/>
+    <row r="17" spans="1:9" s="6" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+      <c r="A17" s="91"/>
+      <c r="B17" s="91"/>
       <c r="C17" s="24">
         <v>6.2</v>
       </c>
@@ -8193,9 +8274,9 @@
       <c r="H17" s="26"/>
       <c r="I17" s="24"/>
     </row>
-    <row r="18" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="70"/>
-      <c r="B18" s="70"/>
+    <row r="18" spans="1:9" s="6" customFormat="1" ht="174" x14ac:dyDescent="0.35">
+      <c r="A18" s="91"/>
+      <c r="B18" s="91"/>
       <c r="C18" s="24">
         <v>6.3</v>
       </c>
@@ -8214,9 +8295,9 @@
       <c r="H18" s="26"/>
       <c r="I18" s="24"/>
     </row>
-    <row r="19" spans="1:9" s="6" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="70"/>
-      <c r="B19" s="70"/>
+    <row r="19" spans="1:9" s="6" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="91"/>
+      <c r="B19" s="91"/>
       <c r="C19" s="27">
         <v>6.4</v>
       </c>
@@ -8239,9 +8320,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
       <c r="A20" s="52"/>
-      <c r="B20" s="70"/>
+      <c r="B20" s="91"/>
       <c r="C20" s="24">
         <v>6.5</v>
       </c>
@@ -8260,9 +8341,9 @@
       <c r="H20" s="26"/>
       <c r="I20" s="24"/>
     </row>
-    <row r="21" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A21" s="52"/>
-      <c r="B21" s="81"/>
+      <c r="B21" s="101"/>
       <c r="C21" s="24">
         <v>6.6</v>
       </c>
@@ -8281,11 +8362,11 @@
       <c r="H21" s="26"/>
       <c r="I21" s="24"/>
     </row>
-    <row r="22" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A22" s="71">
+    <row r="22" spans="1:9" s="6" customFormat="1" ht="145" x14ac:dyDescent="0.35">
+      <c r="A22" s="92">
         <v>7</v>
       </c>
-      <c r="B22" s="69" t="s">
+      <c r="B22" s="90" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="24">
@@ -8310,9 +8391,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A23" s="72"/>
-      <c r="B23" s="70"/>
+    <row r="23" spans="1:9" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="93"/>
+      <c r="B23" s="91"/>
       <c r="C23" s="24">
         <v>7.2</v>
       </c>
@@ -8333,9 +8414,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="72"/>
-      <c r="B24" s="70"/>
+    <row r="24" spans="1:9" s="6" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="93"/>
+      <c r="B24" s="91"/>
       <c r="C24" s="24">
         <v>7.3</v>
       </c>
@@ -8354,9 +8435,9 @@
       <c r="H24" s="26"/>
       <c r="I24" s="24"/>
     </row>
-    <row r="25" spans="1:9" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="73"/>
-      <c r="B25" s="70"/>
+    <row r="25" spans="1:9" s="6" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="94"/>
+      <c r="B25" s="91"/>
       <c r="C25" s="24">
         <v>7.4</v>
       </c>
@@ -8375,9 +8456,9 @@
       <c r="H25" s="26"/>
       <c r="I25" s="24"/>
     </row>
-    <row r="26" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A26" s="52"/>
-      <c r="B26" s="81"/>
+      <c r="B26" s="101"/>
       <c r="C26" s="24">
         <v>7.5</v>
       </c>
@@ -8396,11 +8477,11 @@
       <c r="H26" s="26"/>
       <c r="I26" s="24"/>
     </row>
-    <row r="27" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="78">
+    <row r="27" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="98">
         <v>8</v>
       </c>
-      <c r="B27" s="78" t="s">
+      <c r="B27" s="98" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="28">
@@ -8423,9 +8504,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="79"/>
-      <c r="B28" s="79"/>
+    <row r="28" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="99"/>
+      <c r="B28" s="99"/>
       <c r="C28" s="28">
         <v>9.3000000000000007</v>
       </c>
@@ -8446,9 +8527,9 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="80"/>
-      <c r="B29" s="80"/>
+    <row r="29" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="100"/>
+      <c r="B29" s="100"/>
       <c r="C29" s="28">
         <v>9.4</v>
       </c>
@@ -8469,11 +8550,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="76">
+    <row r="30" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A30" s="96">
         <v>12</v>
       </c>
-      <c r="B30" s="76" t="s">
+      <c r="B30" s="96" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="30">
@@ -8498,9 +8579,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="76"/>
-      <c r="B31" s="76"/>
+    <row r="31" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A31" s="96"/>
+      <c r="B31" s="96"/>
       <c r="C31" s="30">
         <v>12.2</v>
       </c>
@@ -8523,9 +8604,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="76"/>
-      <c r="B32" s="76"/>
+    <row r="32" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A32" s="96"/>
+      <c r="B32" s="96"/>
       <c r="C32" s="30">
         <v>12.3</v>
       </c>
@@ -8548,9 +8629,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="76"/>
-      <c r="B33" s="76"/>
+    <row r="33" spans="1:9" s="6" customFormat="1" ht="123.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="96"/>
+      <c r="B33" s="96"/>
       <c r="C33" s="30">
         <v>12.4</v>
       </c>
@@ -8573,9 +8654,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="76"/>
-      <c r="B34" s="76"/>
+    <row r="34" spans="1:9" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="96"/>
+      <c r="B34" s="96"/>
       <c r="C34" s="30">
         <v>12.5</v>
       </c>
@@ -8598,11 +8679,11 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="77">
+    <row r="35" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="97">
         <v>14</v>
       </c>
-      <c r="B35" s="77" t="s">
+      <c r="B35" s="97" t="s">
         <v>70</v>
       </c>
       <c r="C35" s="34">
@@ -8627,9 +8708,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="77"/>
-      <c r="B36" s="77"/>
+    <row r="36" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="97"/>
+      <c r="B36" s="97"/>
       <c r="C36" s="34">
         <v>14.2</v>
       </c>
@@ -8652,9 +8733,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="77"/>
-      <c r="B37" s="77"/>
+    <row r="37" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="97"/>
+      <c r="B37" s="97"/>
       <c r="C37" s="34">
         <v>14.3</v>
       </c>
@@ -8677,9 +8758,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="77"/>
-      <c r="B38" s="77"/>
+    <row r="38" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A38" s="97"/>
+      <c r="B38" s="97"/>
       <c r="C38" s="34">
         <v>14.4</v>
       </c>
@@ -8702,9 +8783,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="77"/>
-      <c r="B39" s="77"/>
+    <row r="39" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="97"/>
+      <c r="B39" s="97"/>
       <c r="C39" s="34">
         <v>14.5</v>
       </c>
@@ -8727,9 +8808,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="77"/>
-      <c r="B40" s="77"/>
+    <row r="40" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="97"/>
+      <c r="B40" s="97"/>
       <c r="C40" s="34">
         <v>14.6</v>
       </c>
@@ -8752,9 +8833,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="77"/>
-      <c r="B41" s="77"/>
+    <row r="41" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="97"/>
+      <c r="B41" s="97"/>
       <c r="C41" s="34">
         <v>14.7</v>
       </c>
@@ -8777,9 +8858,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="77"/>
-      <c r="B42" s="77"/>
+    <row r="42" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="97"/>
+      <c r="B42" s="97"/>
       <c r="C42" s="34">
         <v>14.8</v>
       </c>
@@ -8802,9 +8883,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="77"/>
-      <c r="B43" s="77"/>
+    <row r="43" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="97"/>
+      <c r="B43" s="97"/>
       <c r="C43" s="34">
         <v>14.9</v>
       </c>
@@ -8827,9 +8908,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="77"/>
-      <c r="B44" s="77"/>
+    <row r="44" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A44" s="97"/>
+      <c r="B44" s="97"/>
       <c r="C44" s="34">
         <v>14.1</v>
       </c>
@@ -8852,9 +8933,9 @@
         <v>72</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="77"/>
-      <c r="B45" s="77"/>
+    <row r="45" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="97"/>
+      <c r="B45" s="97"/>
       <c r="C45" s="34">
         <v>14.11</v>
       </c>
@@ -8877,11 +8958,11 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="74">
+    <row r="46" spans="1:9" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A46" s="95">
         <v>15</v>
       </c>
-      <c r="B46" s="74" t="s">
+      <c r="B46" s="95" t="s">
         <v>74</v>
       </c>
       <c r="C46" s="37">
@@ -8906,7 +8987,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A47" s="75"/>
       <c r="B47" s="75"/>
       <c r="C47" s="37">
@@ -8931,7 +9012,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A48" s="75"/>
       <c r="B48" s="75"/>
       <c r="C48" s="37">
@@ -8956,7 +9037,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A49" s="75"/>
       <c r="B49" s="75"/>
       <c r="C49" s="37">
@@ -8981,7 +9062,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A50" s="75"/>
       <c r="B50" s="75"/>
       <c r="C50" s="37">
@@ -9006,7 +9087,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A51" s="75"/>
       <c r="B51" s="75"/>
       <c r="C51" s="37">
@@ -9031,7 +9112,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="75"/>
       <c r="B52" s="75"/>
       <c r="C52" s="37">
@@ -9056,7 +9137,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A53" s="75"/>
       <c r="B53" s="75"/>
       <c r="C53" s="37">
@@ -9081,11 +9162,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="97">
+    <row r="54" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="74">
         <v>16</v>
       </c>
-      <c r="B54" s="97" t="s">
+      <c r="B54" s="74" t="s">
         <v>89</v>
       </c>
       <c r="C54" s="39">
@@ -9110,9 +9191,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="97"/>
-      <c r="B55" s="97"/>
+    <row r="55" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="74"/>
+      <c r="B55" s="74"/>
       <c r="C55" s="39">
         <v>16.2</v>
       </c>
@@ -9135,9 +9216,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="97"/>
-      <c r="B56" s="97"/>
+    <row r="56" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="74"/>
+      <c r="B56" s="74"/>
       <c r="C56" s="39">
         <v>16.3</v>
       </c>
@@ -9160,9 +9241,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="97"/>
-      <c r="B57" s="97"/>
+    <row r="57" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A57" s="74"/>
+      <c r="B57" s="74"/>
       <c r="C57" s="39">
         <v>16.399999999999999</v>
       </c>
@@ -9185,9 +9266,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="97"/>
-      <c r="B58" s="97"/>
+    <row r="58" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="74"/>
+      <c r="B58" s="74"/>
       <c r="C58" s="39">
         <v>16.5</v>
       </c>
@@ -9210,7 +9291,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A59" s="75"/>
       <c r="B59" s="75"/>
       <c r="C59" s="39">
@@ -9235,11 +9316,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="98">
+    <row r="60" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="76">
         <v>17</v>
       </c>
-      <c r="B60" s="101" t="s">
+      <c r="B60" s="79" t="s">
         <v>105</v>
       </c>
       <c r="C60" s="42">
@@ -9264,9 +9345,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="99"/>
-      <c r="B61" s="101"/>
+    <row r="61" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="77"/>
+      <c r="B61" s="79"/>
       <c r="C61" s="42">
         <v>17.2</v>
       </c>
@@ -9289,9 +9370,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="99"/>
-      <c r="B62" s="101"/>
+    <row r="62" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="77"/>
+      <c r="B62" s="79"/>
       <c r="C62" s="42">
         <v>17.3</v>
       </c>
@@ -9314,9 +9395,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="99"/>
-      <c r="B63" s="101"/>
+    <row r="63" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="77"/>
+      <c r="B63" s="79"/>
       <c r="C63" s="42">
         <v>17.399999999999999</v>
       </c>
@@ -9339,9 +9420,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="100"/>
-      <c r="B64" s="101"/>
+    <row r="64" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="78"/>
+      <c r="B64" s="79"/>
       <c r="C64" s="42">
         <v>17.5</v>
       </c>
@@ -9364,11 +9445,11 @@
         <v>94</v>
       </c>
     </row>
-    <row r="65" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="102">
+    <row r="65" spans="1:12" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A65" s="80">
         <v>18</v>
       </c>
-      <c r="B65" s="83" t="s">
+      <c r="B65" s="81" t="s">
         <v>279</v>
       </c>
       <c r="C65" s="18">
@@ -9393,9 +9474,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="66" spans="1:12" s="6" customFormat="1" ht="250.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" s="6" customFormat="1" ht="250.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="75"/>
-      <c r="B66" s="84"/>
+      <c r="B66" s="82"/>
       <c r="C66" s="18">
         <v>18.2</v>
       </c>
@@ -9418,9 +9499,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="67" spans="1:12" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="75"/>
-      <c r="B67" s="84"/>
+      <c r="B67" s="82"/>
       <c r="C67" s="18">
         <v>18.3</v>
       </c>
@@ -9443,9 +9524,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="68" spans="1:12" s="6" customFormat="1" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" s="6" customFormat="1" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A68" s="75"/>
-      <c r="B68" s="84"/>
+      <c r="B68" s="82"/>
       <c r="C68" s="18">
         <v>18.399999999999999</v>
       </c>
@@ -9468,9 +9549,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:12" s="6" customFormat="1" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" s="6" customFormat="1" ht="216" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="48"/>
-      <c r="B69" s="85"/>
+      <c r="B69" s="83"/>
       <c r="C69" s="18">
         <v>18.5</v>
       </c>
@@ -9489,11 +9570,11 @@
       <c r="H69" s="18"/>
       <c r="I69" s="18"/>
     </row>
-    <row r="70" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="91">
+    <row r="70" spans="1:12" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
+      <c r="A70" s="68">
         <v>19</v>
       </c>
-      <c r="B70" s="94" t="s">
+      <c r="B70" s="71" t="s">
         <v>120</v>
       </c>
       <c r="C70" s="44">
@@ -9514,9 +9595,9 @@
       <c r="H70" s="44"/>
       <c r="I70" s="47"/>
     </row>
-    <row r="71" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="92"/>
-      <c r="B71" s="95"/>
+    <row r="71" spans="1:12" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="69"/>
+      <c r="B71" s="72"/>
       <c r="C71" s="15">
         <v>19.2</v>
       </c>
@@ -9535,9 +9616,9 @@
       <c r="H71" s="44"/>
       <c r="I71" s="47"/>
     </row>
-    <row r="72" spans="1:12" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="93"/>
-      <c r="B72" s="96"/>
+    <row r="72" spans="1:12" s="6" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="70"/>
+      <c r="B72" s="73"/>
       <c r="C72" s="53">
         <v>19.3</v>
       </c>
@@ -9558,11 +9639,11 @@
         <v>313</v>
       </c>
     </row>
-    <row r="73" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="91">
+    <row r="73" spans="1:12" s="6" customFormat="1" ht="203" x14ac:dyDescent="0.35">
+      <c r="A73" s="68">
         <v>20</v>
       </c>
-      <c r="B73" s="94" t="s">
+      <c r="B73" s="71" t="s">
         <v>126</v>
       </c>
       <c r="C73" s="44">
@@ -9583,9 +9664,9 @@
       <c r="H73" s="44"/>
       <c r="I73" s="47"/>
     </row>
-    <row r="74" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A74" s="92"/>
-      <c r="B74" s="95"/>
+    <row r="74" spans="1:12" s="6" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="69"/>
+      <c r="B74" s="72"/>
       <c r="C74" s="15">
         <v>20.2</v>
       </c>
@@ -9607,9 +9688,9 @@
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
     </row>
-    <row r="75" spans="1:12" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="93"/>
-      <c r="B75" s="95"/>
+    <row r="75" spans="1:12" s="6" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="70"/>
+      <c r="B75" s="72"/>
       <c r="C75" s="56">
         <v>20.3</v>
       </c>
@@ -9633,9 +9714,9 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
     </row>
-    <row r="76" spans="1:12" s="6" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" s="6" customFormat="1" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A76" s="49"/>
-      <c r="B76" s="96"/>
+      <c r="B76" s="73"/>
       <c r="C76" s="56">
         <v>20.399999999999999</v>
       </c>
@@ -9659,11 +9740,11 @@
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
     </row>
-    <row r="77" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="91">
+    <row r="77" spans="1:12" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A77" s="68">
         <v>21</v>
       </c>
-      <c r="B77" s="94" t="s">
+      <c r="B77" s="71" t="s">
         <v>129</v>
       </c>
       <c r="C77" s="44">
@@ -9684,9 +9765,9 @@
       <c r="H77" s="44"/>
       <c r="I77" s="47"/>
     </row>
-    <row r="78" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="92"/>
-      <c r="B78" s="95"/>
+    <row r="78" spans="1:12" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="69"/>
+      <c r="B78" s="72"/>
       <c r="C78" s="15">
         <v>21.2</v>
       </c>
@@ -9705,9 +9786,9 @@
       <c r="H78" s="44"/>
       <c r="I78" s="47"/>
     </row>
-    <row r="79" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A79" s="93"/>
-      <c r="B79" s="96"/>
+    <row r="79" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="70"/>
+      <c r="B79" s="73"/>
       <c r="C79" s="32">
         <v>21.3</v>
       </c>
@@ -9722,11 +9803,11 @@
       <c r="H79" s="32"/>
       <c r="I79" s="33"/>
     </row>
-    <row r="80" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="91">
+    <row r="80" spans="1:12" ht="261" x14ac:dyDescent="0.35">
+      <c r="A80" s="68">
         <v>22</v>
       </c>
-      <c r="B80" s="94" t="s">
+      <c r="B80" s="71" t="s">
         <v>133</v>
       </c>
       <c r="C80" s="44">
@@ -9747,9 +9828,9 @@
       <c r="H80" s="44"/>
       <c r="I80" s="47"/>
     </row>
-    <row r="81" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A81" s="92"/>
-      <c r="B81" s="95"/>
+    <row r="81" spans="1:9" ht="261" x14ac:dyDescent="0.35">
+      <c r="A81" s="69"/>
+      <c r="B81" s="72"/>
       <c r="C81" s="15">
         <v>22.2</v>
       </c>
@@ -9768,9 +9849,9 @@
       <c r="H81" s="44"/>
       <c r="I81" s="47"/>
     </row>
-    <row r="82" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A82" s="93"/>
-      <c r="B82" s="96"/>
+    <row r="82" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A82" s="70"/>
+      <c r="B82" s="73"/>
       <c r="C82" s="32">
         <v>22.3</v>
       </c>
@@ -9785,26 +9866,26 @@
       <c r="H82" s="32"/>
       <c r="I82" s="33"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="E83" s="11"/>
       <c r="H83" s="3"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="I84" s="2"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="I85" s="2"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -9815,7 +9896,7 @@
       <c r="H86" s="7"/>
       <c r="I86" s="7"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -9826,7 +9907,7 @@
       <c r="H87" s="10"/>
       <c r="I87" s="10"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D88" s="10"/>
       <c r="E88" s="10"/>
       <c r="F88" s="10"/>
@@ -9834,7 +9915,7 @@
       <c r="H88" s="10"/>
       <c r="I88" s="10"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B89" s="3"/>
       <c r="D89" s="10"/>
       <c r="E89" s="10"/>
@@ -9843,7 +9924,7 @@
       <c r="H89" s="10"/>
       <c r="I89" s="10"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D90" s="10"/>
       <c r="E90" s="10"/>
       <c r="F90" s="10"/>
@@ -9851,7 +9932,7 @@
       <c r="H90" s="10"/>
       <c r="I90" s="10"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D91" s="10"/>
       <c r="E91" s="10"/>
       <c r="F91" s="10"/>
@@ -9859,7 +9940,7 @@
       <c r="H91" s="10"/>
       <c r="I91" s="10"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D92" s="10"/>
       <c r="E92" s="10"/>
       <c r="F92" s="10"/>
@@ -9867,7 +9948,7 @@
       <c r="H92" s="10"/>
       <c r="I92" s="10"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D93" s="10"/>
       <c r="E93" s="10"/>
       <c r="F93" s="10"/>
@@ -9875,7 +9956,7 @@
       <c r="H93" s="10"/>
       <c r="I93" s="10"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="D94" s="10"/>
       <c r="E94" s="10"/>
       <c r="F94" s="10"/>
@@ -9886,6 +9967,29 @@
   </sheetData>
   <autoFilter ref="I1:I32" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A46:A53"/>
+    <mergeCell ref="B46:B53"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="A35:A45"/>
+    <mergeCell ref="B35:B45"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B10"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="A80:A82"/>
@@ -9900,29 +10004,6 @@
     <mergeCell ref="A73:A75"/>
     <mergeCell ref="B73:B76"/>
     <mergeCell ref="B65:B69"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B10"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A46:A53"/>
-    <mergeCell ref="B46:B53"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="A35:A45"/>
-    <mergeCell ref="B35:B45"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="B22:B26"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9934,15 +10015,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="18.21875" customWidth="1"/>
-    <col min="5" max="5" width="24.88671875" customWidth="1"/>
-    <col min="6" max="6" width="27.33203125" customWidth="1"/>
-    <col min="7" max="7" width="36.21875" customWidth="1"/>
+    <col min="4" max="4" width="18.1796875" customWidth="1"/>
+    <col min="5" max="5" width="24.90625" customWidth="1"/>
+    <col min="6" max="6" width="27.36328125" customWidth="1"/>
+    <col min="7" max="7" width="36.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="9"/>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -9954,7 +10035,7 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -9966,7 +10047,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="9"/>
     </row>
-    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -9990,7 +10071,7 @@
       </c>
       <c r="J3" s="9"/>
     </row>
-    <row r="4" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="348" x14ac:dyDescent="0.35">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -10014,7 +10095,7 @@
       </c>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -10038,7 +10119,7 @@
       </c>
       <c r="J5" s="9"/>
     </row>
-    <row r="6" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="348" x14ac:dyDescent="0.35">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -10062,7 +10143,7 @@
       </c>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="406" x14ac:dyDescent="0.35">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -10086,7 +10167,7 @@
       </c>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="333.5" x14ac:dyDescent="0.35">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -10110,7 +10191,7 @@
       </c>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:10" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -10134,7 +10215,7 @@
       </c>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="348" x14ac:dyDescent="0.35">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
@@ -10158,7 +10239,7 @@
       </c>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="319" x14ac:dyDescent="0.35">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -10182,7 +10263,7 @@
       </c>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:10" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="304.5" x14ac:dyDescent="0.35">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -10206,7 +10287,7 @@
       </c>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:10" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="391.5" x14ac:dyDescent="0.35">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -10230,7 +10311,7 @@
       </c>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:10" ht="288" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="290" x14ac:dyDescent="0.35">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -10254,7 +10335,7 @@
       </c>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -10266,7 +10347,7 @@
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -10278,7 +10359,7 @@
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -10290,7 +10371,7 @@
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -10302,7 +10383,7 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -10314,7 +10395,7 @@
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -10326,7 +10407,7 @@
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -10338,7 +10419,7 @@
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -10350,7 +10431,7 @@
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -10362,7 +10443,7 @@
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -10374,7 +10455,7 @@
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -10386,7 +10467,7 @@
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="9"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -10398,7 +10479,7 @@
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -10410,7 +10491,7 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -10422,7 +10503,7 @@
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -10434,7 +10515,7 @@
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -10446,7 +10527,7 @@
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -10458,7 +10539,7 @@
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -10470,63 +10551,63 @@
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="9"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -10542,33 +10623,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0802363A-09BC-4F89-B136-783D2DDEAFD1}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.77734375" customWidth="1"/>
-    <col min="2" max="2" width="43.5546875" customWidth="1"/>
-    <col min="3" max="3" width="55.21875" customWidth="1"/>
-    <col min="4" max="4" width="70.21875" customWidth="1"/>
-    <col min="5" max="5" width="89.77734375" customWidth="1"/>
+    <col min="1" max="1" width="21.81640625" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" customWidth="1"/>
+    <col min="3" max="3" width="55.1796875" customWidth="1"/>
+    <col min="4" max="4" width="70.1796875" customWidth="1"/>
+    <col min="5" max="5" width="89.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
+    <row r="1" spans="1:5" ht="37.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="67" t="s">
         <v>332</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="67" t="s">
         <v>333</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="67" t="s">
         <v>334</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="67" t="s">
         <v>335</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="67" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="145" x14ac:dyDescent="0.35">
       <c r="A2" s="58">
         <v>5.0999999999999996</v>
       </c>
@@ -10585,7 +10666,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A3" s="58">
         <v>5.2</v>
       </c>
@@ -10602,7 +10683,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="116" x14ac:dyDescent="0.35">
       <c r="A4" s="58">
         <v>5.3</v>
       </c>
@@ -10619,7 +10700,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="58">
         <v>5.4</v>
       </c>
@@ -10636,7 +10717,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="116" x14ac:dyDescent="0.35">
       <c r="A6" s="61">
         <v>5.5</v>
       </c>
@@ -10649,11 +10730,11 @@
       <c r="D6" s="62" t="s">
         <v>348</v>
       </c>
-      <c r="E6" s="63" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="E6" s="102" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="116" x14ac:dyDescent="0.35">
       <c r="A7" s="58">
         <v>5.6</v>
       </c>
@@ -10667,27 +10748,27 @@
         <v>351</v>
       </c>
       <c r="E7" s="60" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="64">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="145" x14ac:dyDescent="0.35">
+      <c r="A8" s="63">
         <v>5.7</v>
       </c>
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="64" t="s">
         <v>352</v>
       </c>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="64" t="s">
         <v>353</v>
       </c>
-      <c r="D8" s="66" t="s">
-        <v>373</v>
-      </c>
-      <c r="E8" s="64" t="s">
+      <c r="D8" s="65" t="s">
+        <v>371</v>
+      </c>
+      <c r="E8" s="63" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A9" s="58">
         <v>5.8</v>
       </c>
@@ -10704,7 +10785,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A10" s="58">
         <v>5.9</v>
       </c>
@@ -10721,8 +10802,8 @@
         <v>366</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="144" x14ac:dyDescent="0.3">
-      <c r="A11" s="67">
+    <row r="11" spans="1:5" ht="145" x14ac:dyDescent="0.35">
+      <c r="A11" s="66">
         <v>5.0999999999999996</v>
       </c>
       <c r="B11" s="59" t="s">

--- a/Business Analysis/checkupp_product_backlog.xlsx
+++ b/Business Analysis/checkupp_product_backlog.xlsx
@@ -5,17 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CheckUpp\Business Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443E0692-E891-49C3-BE56-000C29AAC3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8CB6421-DABA-4057-AC9D-672152928404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Tanvi_Immunisation_User_Stories" sheetId="3" r:id="rId3"/>
+    <sheet name="Tanvi_Immunisation_User_Stories" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$1:$I$32</definedName>
@@ -184,7 +183,7 @@
     <author>HP</author>
   </authors>
   <commentList>
-    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{BBA4420A-0271-44D0-A3EB-03CC607498CE}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{BBA4420A-0271-44D0-A3EB-03CC607498CE}">
       <text>
         <r>
           <rPr>
@@ -204,11 +203,11 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-WILL BE BUILT BUT WON'T BE SHOWN TO THE USER</t>
+WILL BE BUILT BUT WON'T BE SHOWN TO THE USERS</t>
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{EF9259EC-0289-41C7-8C3D-2B6EEFD57174}">
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{EF9259EC-0289-41C7-8C3D-2B6EEFD57174}">
       <text>
         <r>
           <rPr>
@@ -233,37 +232,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{DB4BA10A-3EEC-432C-84DE-6EF56322DA85}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Sayan:
-Have to confirm from client whether other categories will be shown </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="341">
   <si>
     <t>Epic #</t>
   </si>
@@ -1155,1276 +1129,7 @@
 3. Users must be able to navigate between wellness categories.</t>
   </si>
   <si>
-    <t>So that</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">enter </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Appointment Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> while creating a custom health check on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Ailments</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <t>I can schedule a future health appointment before saving my custom health check</t>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to enter appointment date, time and location.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Appointment details must be linked to the health check.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Appointment information must be saved successfully.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Save Health Check</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Ailments</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can choose to sync my appointment on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add to Calendar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> App must display an </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add to Calendar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> prompt after saving.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to add or dismiss the prompt.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Appointment details must be retained regardless of the user's choice.</t>
-    </r>
-  </si>
-  <si>
     <t>First-time User</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Allow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Calendar Permission</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen after selecting </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add to Calendar</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">CheckUpp can access my device calendar and continue to the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Select Calendar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> App must request calendar permission before the first sync.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to allow or deny access.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Permission request should not appear again once a choice has been made.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">select my preferred calendar on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Select Calendar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <t>my health appointments are synced to my preferred calendar application</t>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to choose Google Calendar, Apple Calendar/iCal or Outlook (where supported).</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Selected calendar must be remembered for future syncs.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to change the selected calendar later.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">review my appointment details on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Event Preview</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <t>I can verify the appointment information before adding it to my calendar</t>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Event preview must display title, date, time, location and reminder.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to edit or cancel before syncing.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Calendar event must match the displayed details.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add to Calendar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Event Preview</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I receive confirmation that my appointment has been successfully added to my device calendar on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Success</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> App must display a success message after syncing.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to view the calendar event.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Appointment must exist in the selected calendar.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>View Upcoming Appointments</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Success</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can manage all my upcoming health appointments from the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Upcoming Appointments</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Upcoming Appointments screen must display all synced appointments.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Appointments must be grouped by date.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to open the device calendar from this screen.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Calendar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> icon on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Screenings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can open the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Calendar &amp; Sync Settings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen to manage my calendar preferences</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Tapping the calendar icon must open Calendar &amp; Sync Settings.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Settings must display current sync status.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to access settings at any time.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">enable or disable </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Calendar Sync</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Calendar &amp; Sync Settings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <t>I can control whether my health appointments are automatically synced to my device calendar</t>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to turn Calendar Sync on or off.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Preference must be saved across sessions.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Existing calendar events must remain unaffected when sync is disabled.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>14.10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(renumbered from the duplicate 14.1)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">select which health modules to sync on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Calendar &amp; Sync Settings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <t>only appointments from my selected health modules appear in my device calendar</t>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to enable or disable sync for individual modules.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Modules include Screenings, Pregnancy, Midlife Health, Menopause and Other Ailments.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Only enabled modules should sync appointments.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">configure reminder preferences on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Calendar &amp; Sync Settings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <t>I receive appointment reminders at my preferred time</t>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to choose reminder intervals.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Reminder settings must apply to newly synced appointments.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Default reminder must be configurable.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -5415,12 +4120,6 @@
     <t>I can view vaccinations relevant to pregnancy</t>
   </si>
   <si>
-    <t>See vaccination recommendations personalised to my applicable age/life stage</t>
-  </si>
-  <si>
-    <t>I am not presented with irrelevant recommendations</t>
-  </si>
-  <si>
     <t>Access the Travel immunisation category</t>
   </si>
   <si>
@@ -5458,18 +4157,6 @@
   </si>
   <si>
     <t>I can understand the vaccination recommendation presented to me</t>
-  </si>
-  <si>
-    <t>Logged-in user with incomplete or invalid profile information</t>
-  </si>
-  <si>
-    <t>See an appropriate Immunisations screen state</t>
-  </si>
-  <si>
-    <t>The interface does not provide incorrect personalised recommendations</t>
-  </si>
-  <si>
-    <t>Logged-in user using the Immunisations screen</t>
   </si>
   <si>
     <t>See a consistent and usable immunisation interface</t>
@@ -5826,6 +4513,383 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommended for You</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Quick Actions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> must appear in the order defined in the approved wireframe.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cards must use consistent spacing, typography, icons, borders and interaction states according to the approved frontend design.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Conditional removal of a card must not leave unintended blank spaces or broken alignment.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Multiple Recommended for You cards must render correctly when more than one condition applies.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> All visible interactive cards must respond to user selection and navigate/open the expected frontend content.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The screen must remain scrollable and all rendered content must be reachable on supported mobile screen sizes.</t>
+    </r>
+  </si>
+  <si>
+    <t>I can access which vaccinations belong to that category</t>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The frontend must determine the applicable age bracket using the user's configured age/test profile data.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The corresponding age-group card must be displayed in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommended for You.
+3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Age-group labels and ranges must match the approved wireframe, e.g. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Children</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Adolescent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, Adult (18-49), 50+ Years, 65+ Years and 70+ Years where applicable.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Age-group cards that are not applicable to the user must not appear in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Recommended for You </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Boundary ages must map to the correct group according to the defined age ranges.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+6. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The layout must correctly handle one or multiple recommendation cards without overlap, clipping, or broken spacing.</t>
+    </r>
+  </si>
+  <si>
+    <t>See an appropriate Immunisations screen state which guides me to set my age correctly</t>
+  </si>
+  <si>
+    <t>I do not get incorrect immunisation recommendations</t>
+  </si>
+  <si>
+    <t>Logged-in user with incomplete or invalid profile information about my age, gender</t>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve"> Missing/invalid age data must not result in an arbitrary age-specific recommendation being shown.
 </t>
     </r>
@@ -5846,7 +4910,7 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Missing pregnancy information must not cause the Pregnancy card to be treated as a personalised recommendation.
+      <t xml:space="preserve"> Missing pregnancy information or profile's gender, must not cause the Pregnancy card to be treated as a personalised recommendation.
 </t>
     </r>
     <r>
@@ -5886,7 +4950,8 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> The frontend must display the defined fallback/empty state where personalised recommendations cannot be determined.</t>
+      <t xml:space="preserve"> The frontend must display the defined fallback/empty state where personalised recommendations cannot be determined: A link to profile page that gives a gentle nudge to set age.
+</t>
     </r>
     <r>
       <rPr>
@@ -5919,307 +4984,96 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+      <t xml:space="preserve"> The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pregnancy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> card must be displayed when the configured user profile indicates both "female gender" </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "confirmed pregnancy in the app" (calculated LMP date).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The Pregnancy card must not be displayed as a personalised recommendation when either condition is not satisfied.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pregnancy recommendations must appear alongside any applicable age-based recommendation rather than replacing it, under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Recommended for You</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Quick Actions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Categories</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> must appear in the order defined in the approved wireframe.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Cards must use consistent spacing, typography, icons, borders and interaction states according to the approved frontend design.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Conditional removal of a card must not leave unintended blank spaces or broken alignment.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Multiple Recommended for You cards must render correctly when more than one condition applies.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> All visible interactive cards must respond to user selection and navigate/open the expected frontend content.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The screen must remain scrollable and all rendered content must be reachable on supported mobile screen sizes.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The frontend must determine the applicable age bracket using the user's configured age/test profile data.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The corresponding age-group card must be displayed in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Recommended for You.
-3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Age-group labels and ranges must match the approved wireframe, e.g. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Children</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Adolescent</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, Adult (18-49), 50+ Years, 65+ Years and 70+ Years where applicable.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Age-group cards that are not applicable to the user must not appear in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Recommended for You </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">or </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Categories</t>
     </r>
     <r>
       <rPr>
@@ -6239,6 +5093,26 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting the Pregnancy card must display the vaccination information configured for the pregnancy life stage.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>5.</t>
     </r>
     <r>
@@ -6248,7 +5122,219 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> Boundary ages must map to the correct group according to the defined age ranges.
+      <t xml:space="preserve"> The displayed Pregnancy card must follow the approved wireframe styling and interaction behaviour.</t>
+    </r>
+  </si>
+  <si>
+    <t>Logged-in user navigating the Immunisations screen</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>I can access the Immunisations tracking and listing feature of the app</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Screenings bottom nav tab's screen must display 3 top tabs in the following order:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> General, Cancer, Vaccine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Tapping the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vaccine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab must navigate the user to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Immunisation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Logged-in user navigating the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Screenings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">tap on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vaccine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab located at the top</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> must be displayed separately from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommended for You</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -6259,68 +5345,36 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
-      <t>6.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> If age data is unavailable or invalid, age-specific recommendations must not be displayed and an appropriate frontend fallback message/state must be shown.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pregnancy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> card must be displayed when the configured user profile indicates both female gender </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>and</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> confirmed pregnancy in the app (calculated LMP date).
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cards within </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> must follow their defined frontend visibility rules.
 </t>
     </r>
     <r>
@@ -6331,47 +5385,49 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The Pregnancy card must not be displayed as a personalised recommendation when either condition is not satisfied.
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Travel must be available to all users.
 </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pregnancy recommendations must appear alongside any applicable age-based recommendation rather than replacing it, under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Recommended for You</t>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Children (0–4 years) must follow the 16+ visibility rule</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. (Must be obscured in MVP)</t>
     </r>
     <r>
       <rPr>
@@ -6387,8 +5443,183 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Age/life-stage categories shown for general browsing must appear in the order specified by the approved wireframe.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Changes to the configured test/user profile must result in the appropriate category visibility changes when the screen is re-rendered.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Children (0–4 years)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> card must be displayed under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when the configured user's age is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16 years or older</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The Children card must not be displayed when the configured user's age is below 16.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The boundary value of exactly 16 years must result in the Children card being displayed.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>4.</t>
@@ -6398,9 +5629,10 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Selecting the Pregnancy card must display the vaccination information configured for the pregnancy life stage.
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Visibility of the Children card must not depend on gender or pregnancy status.
 </t>
     </r>
     <r>
@@ -6409,6 +5641,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>5.</t>
@@ -6418,139 +5651,18 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The displayed Pregnancy card must follow the approved wireframe styling and interaction behaviour.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Recommended for You</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> must contain only cards applicable to the configured user profile.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The applicable age-based card must be displayed when valid age information is available.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> A qualifying pregnant user must see both the applicable age-based recommendation and Pregnancy recommendation where both apply.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Non-applicable age/life-stage cards must not appear in this section.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Travel and other general browsing categories must not appear in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Recommended for You</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting the card must display the vaccination information configured for children aged 0–4 years.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
@@ -6560,381 +5672,22 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The layout must correctly handle one or multiple recommendation cards without overlap, clipping, or broken spacing.</t>
-    </r>
-  </si>
-  <si>
-    <t>I can access which vaccinations belong to that category</t>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Must be obscured in MVP.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="2" tint="-9.9978637043366805E-2"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Children (0–4 years)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> card must be displayed under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Categories</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> when the configured user's age is </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>16 years or older</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The Children card must not be displayed when the configured user's age is below 16.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The boundary value of exactly 16 years must result in the Children card being displayed.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Visibility of the Children card must not depend on gender or pregnancy status.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Selecting the card must display the vaccination information configured for children aged 0–4 years.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Must be obscured in MVP.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Categories</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> must be displayed separately from Recommended for You.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Cards within Other Categories must follow their defined frontend visibility rules.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Travel must be available to all users.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Children (0–4 years) must follow the 16+ visibility rule</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. (Must be obscured in MVP)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Age/life-stage categories shown for general browsing must appear in the order specified by the approved wireframe.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Changes to the configured test profile must result in the appropriate category visibility changes when the screen is re-rendered.</t>
     </r>
   </si>
 </sst>
@@ -6942,7 +5695,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7041,22 +5794,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -7131,13 +5868,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="2" tint="-9.9978637043366805E-2"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="2" tint="-9.9978637043366805E-2"/>
       <name val="Calibri"/>
@@ -7246,13 +5976,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FF7030A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
+        <fgColor rgb="FFFF6969"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -7353,7 +6083,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7380,72 +6110,63 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7454,43 +6175,43 @@
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7502,22 +6223,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7526,7 +6247,7 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -7535,25 +6256,73 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7574,11 +6343,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7589,76 +6355,43 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7668,6 +6401,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF6969"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -7878,50 +6616,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L94"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.90625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="64.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="72.54296875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.6328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.36328125" style="3" customWidth="1"/>
-    <col min="10" max="12" width="8.90625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="64.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="72.5546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" style="3" customWidth="1"/>
+    <col min="10" max="12" width="8.88671875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="84" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="84" t="s">
+      <c r="C1" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="84" t="s">
+      <c r="D1" s="72" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="85" t="s">
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="84" t="s">
+      <c r="H1" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="84" t="s">
+      <c r="I1" s="72" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="75"/>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -7931,1961 +6669,1961 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-    </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="86">
+      <c r="G2" s="76"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+    </row>
+    <row r="3" spans="1:9" s="5" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="77">
         <v>1</v>
       </c>
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="13">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="6" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="77"/>
+      <c r="B4" s="79"/>
+      <c r="C4" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="G4" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" spans="1:9" s="6" customFormat="1" ht="160.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="77"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="13">
+        <v>1.3</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G5" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+    </row>
+    <row r="6" spans="1:9" s="6" customFormat="1" ht="154.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="77"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+    </row>
+    <row r="7" spans="1:9" s="6" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="77"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="H3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="16" t="s">
+      <c r="F7" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+    </row>
+    <row r="8" spans="1:9" s="6" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="47"/>
+      <c r="B8" s="79"/>
+      <c r="C8" s="13">
+        <v>1.6</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+    </row>
+    <row r="9" spans="1:9" s="6" customFormat="1" ht="152.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="47"/>
+      <c r="B9" s="79"/>
+      <c r="C9" s="13">
+        <v>1.7</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" spans="1:9" s="6" customFormat="1" ht="295.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="47"/>
+      <c r="B10" s="80"/>
+      <c r="C10" s="13">
+        <v>1.8</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="H10" s="13"/>
+      <c r="I10" s="48"/>
+    </row>
+    <row r="11" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="73">
+        <v>5</v>
+      </c>
+      <c r="B11" s="73" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="15">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="74"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="15">
+        <v>5.2</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="17"/>
+      <c r="I12" s="15"/>
+    </row>
+    <row r="13" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="74"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="15">
+        <v>5.3</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="17"/>
+      <c r="I13" s="15"/>
+    </row>
+    <row r="14" spans="1:9" s="11" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="74"/>
+      <c r="B14" s="74"/>
+      <c r="C14" s="18">
+        <v>5.4</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="H14" s="20"/>
+      <c r="I14" s="18"/>
+    </row>
+    <row r="15" spans="1:9" s="11" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="75"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="18">
+        <v>5.5</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="H15" s="20"/>
+      <c r="I15" s="18"/>
+    </row>
+    <row r="16" spans="1:9" s="11" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="59">
+        <v>6</v>
+      </c>
+      <c r="B16" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="21">
+        <v>6.1</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A17" s="60"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="21">
+        <v>6.2</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="H17" s="23"/>
+      <c r="I17" s="21"/>
+    </row>
+    <row r="18" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="60"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="21">
+        <v>6.3</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="H18" s="23"/>
+      <c r="I18" s="21"/>
+    </row>
+    <row r="19" spans="1:9" s="6" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="60"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="24">
+        <v>6.4</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="49"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="21">
+        <v>6.5</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="H20" s="23"/>
+      <c r="I20" s="21"/>
+    </row>
+    <row r="21" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="49"/>
+      <c r="B21" s="71"/>
+      <c r="C21" s="21">
+        <v>6.6</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="H21" s="23"/>
+      <c r="I21" s="21"/>
+    </row>
+    <row r="22" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A22" s="61">
+        <v>7</v>
+      </c>
+      <c r="B22" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="21">
+        <v>7.1</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A23" s="62"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="21">
+        <v>7.2</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23" s="23"/>
+      <c r="I23" s="21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="62"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="21">
+        <v>7.3</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="23"/>
+      <c r="I24" s="21"/>
+    </row>
+    <row r="25" spans="1:9" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="63"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="21">
+        <v>7.4</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="H25" s="23"/>
+      <c r="I25" s="21"/>
+    </row>
+    <row r="26" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A26" s="49"/>
+      <c r="B26" s="71"/>
+      <c r="C26" s="21">
+        <v>7.5</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="G26" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="H26" s="23"/>
+      <c r="I26" s="21"/>
+    </row>
+    <row r="27" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="68">
+        <v>8</v>
+      </c>
+      <c r="B27" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="25">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="69"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="25">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="70"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="25">
+        <v>9.4</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="66">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" s="6" customFormat="1" ht="124.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="86"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="16">
-        <v>1.2</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E4" s="16" t="s">
+      <c r="B30" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="27">
+        <v>12.1</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="H30" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="I30" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="66"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="27">
+        <v>12.2</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="H31" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="I31" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="66"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="27">
+        <v>12.3</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="G32" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="H32" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="I32" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="66"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="27">
+        <v>12.4</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="F33" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="G33" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="H33" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="66"/>
+      <c r="B34" s="66"/>
+      <c r="C34" s="27">
+        <v>12.5</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="F34" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="G34" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="H34" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="I34" s="27" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="67">
+        <v>14</v>
+      </c>
+      <c r="B35" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="31">
+        <v>14.1</v>
+      </c>
+      <c r="D35" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="G35" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="H35" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="I35" s="31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="67"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="31">
+        <v>14.2</v>
+      </c>
+      <c r="D36" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="G36" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="H36" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="I36" s="31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="67"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="31">
+        <v>14.3</v>
+      </c>
+      <c r="D37" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="E37" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="F37" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="G37" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="I37" s="31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="67"/>
+      <c r="B38" s="67"/>
+      <c r="C38" s="31">
+        <v>14.4</v>
+      </c>
+      <c r="D38" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="F38" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="G38" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="H38" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="I38" s="31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="67"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="31">
+        <v>14.5</v>
+      </c>
+      <c r="D39" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="F39" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="G39" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="H39" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="I39" s="31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="67"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="31">
+        <v>14.6</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="F40" s="32" t="s">
+        <v>233</v>
+      </c>
+      <c r="G40" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="H40" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="I40" s="31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="67"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="31">
+        <v>14.7</v>
+      </c>
+      <c r="D41" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E41" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="G41" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="I41" s="31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="67"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="31">
+        <v>14.8</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="F42" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="G42" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="H42" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="I42" s="31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="67"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="31">
+        <v>14.9</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="F43" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="G43" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="H43" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="I43" s="31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="67"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="31">
+        <v>14.1</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E44" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="G44" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="H44" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="I44" s="31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="67"/>
+      <c r="B45" s="67"/>
+      <c r="C45" s="31">
+        <v>14.11</v>
+      </c>
+      <c r="D45" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="E45" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="F45" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="G45" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="H45" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="I45" s="31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A46" s="64">
+        <v>15</v>
+      </c>
+      <c r="B46" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="C46" s="34">
+        <v>15.1</v>
+      </c>
+      <c r="D46" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="34" t="s">
+        <v>76</v>
+      </c>
+      <c r="F46" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="G46" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="H46" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="I46" s="34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="65"/>
+      <c r="B47" s="65"/>
+      <c r="C47" s="34">
+        <v>15.2</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E47" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="F47" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="G47" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="H47" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="I47" s="34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="65"/>
+      <c r="B48" s="65"/>
+      <c r="C48" s="34">
+        <v>15.3</v>
+      </c>
+      <c r="D48" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E48" s="34" t="s">
+        <v>80</v>
+      </c>
+      <c r="F48" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="G48" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="H48" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="I48" s="34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="65"/>
+      <c r="B49" s="65"/>
+      <c r="C49" s="34">
+        <v>15.4</v>
+      </c>
+      <c r="D49" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="F49" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="H49" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="I49" s="34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="65"/>
+      <c r="B50" s="65"/>
+      <c r="C50" s="34">
+        <v>15.5</v>
+      </c>
+      <c r="D50" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E50" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="F50" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="G50" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="H50" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="I50" s="34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="65"/>
+      <c r="B51" s="65"/>
+      <c r="C51" s="34">
+        <v>15.6</v>
+      </c>
+      <c r="D51" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E51" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F51" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="G51" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="H51" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="I51" s="34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="65"/>
+      <c r="B52" s="65"/>
+      <c r="C52" s="34">
+        <v>15.7</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E52" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="F52" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="G52" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="H52" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="I52" s="34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="65"/>
+      <c r="B53" s="65"/>
+      <c r="C53" s="34">
+        <v>15.8</v>
+      </c>
+      <c r="D53" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="E53" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="F53" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="G53" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="H53" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="I53" s="34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="87">
+        <v>16</v>
+      </c>
+      <c r="B54" s="87" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" s="36">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D54" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E54" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="F54" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="G54" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="H54" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I54" s="37" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="87"/>
+      <c r="B55" s="87"/>
+      <c r="C55" s="36">
+        <v>16.2</v>
+      </c>
+      <c r="D55" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E55" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F55" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="G55" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="H55" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I55" s="37" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A56" s="87"/>
+      <c r="B56" s="87"/>
+      <c r="C56" s="36">
+        <v>16.3</v>
+      </c>
+      <c r="D56" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E56" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="F56" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="G56" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="H56" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I56" s="37" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A57" s="87"/>
+      <c r="B57" s="87"/>
+      <c r="C57" s="36">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="D57" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E57" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="F57" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G57" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="H57" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I57" s="37" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A58" s="87"/>
+      <c r="B58" s="87"/>
+      <c r="C58" s="36">
+        <v>16.5</v>
+      </c>
+      <c r="D58" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E58" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="F58" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="G58" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="H58" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I58" s="37" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A59" s="65"/>
+      <c r="B59" s="65"/>
+      <c r="C59" s="36">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="D59" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="F59" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="G59" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="H59" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="I59" s="37" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A60" s="88">
+        <v>17</v>
+      </c>
+      <c r="B60" s="91" t="s">
+        <v>105</v>
+      </c>
+      <c r="C60" s="39">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="D60" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="E60" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="F60" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="G60" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="H60" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="I60" s="39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="89"/>
+      <c r="B61" s="91"/>
+      <c r="C61" s="39">
+        <v>17.2</v>
+      </c>
+      <c r="D61" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="E61" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="F61" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="G61" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="H61" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="I61" s="39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A62" s="89"/>
+      <c r="B62" s="91"/>
+      <c r="C62" s="39">
+        <v>17.3</v>
+      </c>
+      <c r="D62" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="E62" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="F62" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="G62" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="H62" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="I62" s="39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A63" s="89"/>
+      <c r="B63" s="91"/>
+      <c r="C63" s="39">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="D63" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="E63" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="F63" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="G63" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="H63" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="I63" s="39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A64" s="90"/>
+      <c r="B64" s="91"/>
+      <c r="C64" s="39">
+        <v>17.5</v>
+      </c>
+      <c r="D64" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="E64" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="F64" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="G64" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="H64" s="39" t="s">
+        <v>109</v>
+      </c>
+      <c r="I64" s="39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A65" s="92">
+        <v>18</v>
+      </c>
+      <c r="B65" s="73" t="s">
+        <v>244</v>
+      </c>
+      <c r="C65" s="15">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E65" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="F65" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="G65" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="H65" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I65" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" s="6" customFormat="1" ht="250.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="65"/>
+      <c r="B66" s="74"/>
+      <c r="C66" s="15">
+        <v>18.2</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="F66" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="G66" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="H66" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I66" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="65"/>
+      <c r="B67" s="74"/>
+      <c r="C67" s="15">
+        <v>18.3</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="H67" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I67" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" s="6" customFormat="1" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="65"/>
+      <c r="B68" s="74"/>
+      <c r="C68" s="15">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="F68" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>299</v>
-      </c>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-    </row>
-    <row r="5" spans="1:9" s="6" customFormat="1" ht="160.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="86"/>
-      <c r="B5" s="88"/>
-      <c r="C5" s="16">
-        <v>1.3</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E5" s="16" t="s">
+      <c r="G68" s="16" t="s">
+        <v>269</v>
+      </c>
+      <c r="H68" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I68" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" s="6" customFormat="1" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="45"/>
+      <c r="B69" s="75"/>
+      <c r="C69" s="15">
+        <v>18.5</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E69" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="F69" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-    </row>
-    <row r="6" spans="1:9" s="6" customFormat="1" ht="154.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="86"/>
-      <c r="B6" s="88"/>
-      <c r="C6" s="16">
-        <v>1.4</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-    </row>
-    <row r="7" spans="1:9" s="6" customFormat="1" ht="116" x14ac:dyDescent="0.35">
-      <c r="A7" s="86"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="16">
-        <v>1.5</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="G7" s="17" t="s">
+      <c r="G69" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+    </row>
+    <row r="70" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A70" s="81">
+        <v>19</v>
+      </c>
+      <c r="B70" s="84" t="s">
+        <v>120</v>
+      </c>
+      <c r="C70" s="41">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="D70" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="E70" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="F70" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="G70" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="H70" s="41"/>
+      <c r="I70" s="44"/>
+    </row>
+    <row r="71" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="82"/>
+      <c r="B71" s="85"/>
+      <c r="C71" s="12">
+        <v>19.2</v>
+      </c>
+      <c r="D71" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="E71" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="F71" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="G71" s="43" t="s">
+        <v>124</v>
+      </c>
+      <c r="H71" s="41"/>
+      <c r="I71" s="44"/>
+    </row>
+    <row r="72" spans="1:12" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="83"/>
+      <c r="B72" s="86"/>
+      <c r="C72" s="50">
+        <v>19.3</v>
+      </c>
+      <c r="D72" s="51" t="s">
+        <v>121</v>
+      </c>
+      <c r="E72" s="51" t="s">
+        <v>272</v>
+      </c>
+      <c r="F72" s="51" t="s">
+        <v>273</v>
+      </c>
+      <c r="G72" s="52" t="s">
+        <v>296</v>
+      </c>
+      <c r="H72" s="53"/>
+      <c r="I72" s="54" t="s">
         <v>278</v>
       </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-    </row>
-    <row r="8" spans="1:9" s="6" customFormat="1" ht="124.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="50"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="16">
-        <v>1.6</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>293</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-    </row>
-    <row r="9" spans="1:9" s="6" customFormat="1" ht="152.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="50"/>
-      <c r="B9" s="88"/>
-      <c r="C9" s="16">
-        <v>1.7</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>294</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>296</v>
-      </c>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-    </row>
-    <row r="10" spans="1:9" s="6" customFormat="1" ht="295.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="50"/>
-      <c r="B10" s="89"/>
-      <c r="C10" s="16">
-        <v>1.8</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>297</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="H10" s="16"/>
-      <c r="I10" s="51"/>
-    </row>
-    <row r="11" spans="1:9" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="81">
-        <v>5</v>
-      </c>
-      <c r="B11" s="81" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="18">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="82"/>
-      <c r="B12" s="82"/>
-      <c r="C12" s="18">
-        <v>5.2</v>
-      </c>
-      <c r="D12" s="18" t="s">
+    </row>
+    <row r="73" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="81">
         <v>20</v>
       </c>
-      <c r="E12" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="20"/>
-      <c r="I12" s="18"/>
-    </row>
-    <row r="13" spans="1:9" s="6" customFormat="1" ht="174" x14ac:dyDescent="0.35">
-      <c r="A13" s="82"/>
-      <c r="B13" s="82"/>
-      <c r="C13" s="18">
-        <v>5.3</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="20"/>
-      <c r="I13" s="18"/>
-    </row>
-    <row r="14" spans="1:9" s="14" customFormat="1" ht="232" x14ac:dyDescent="0.35">
-      <c r="A14" s="82"/>
-      <c r="B14" s="82"/>
-      <c r="C14" s="21">
-        <v>5.4</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="H14" s="23"/>
-      <c r="I14" s="21"/>
-    </row>
-    <row r="15" spans="1:9" s="14" customFormat="1" ht="174" x14ac:dyDescent="0.35">
-      <c r="A15" s="83"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="21">
-        <v>5.5</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="H15" s="23"/>
-      <c r="I15" s="21"/>
-    </row>
-    <row r="16" spans="1:9" s="14" customFormat="1" ht="174" x14ac:dyDescent="0.35">
-      <c r="A16" s="90">
-        <v>6</v>
-      </c>
-      <c r="B16" s="90" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="24">
-        <v>6.1</v>
-      </c>
-      <c r="D16" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="25" t="s">
-        <v>321</v>
-      </c>
-      <c r="H16" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" s="6" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A17" s="91"/>
-      <c r="B17" s="91"/>
-      <c r="C17" s="24">
-        <v>6.2</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="H17" s="26"/>
-      <c r="I17" s="24"/>
-    </row>
-    <row r="18" spans="1:9" s="6" customFormat="1" ht="174" x14ac:dyDescent="0.35">
-      <c r="A18" s="91"/>
-      <c r="B18" s="91"/>
-      <c r="C18" s="24">
-        <v>6.3</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>322</v>
-      </c>
-      <c r="H18" s="26"/>
-      <c r="I18" s="24"/>
-    </row>
-    <row r="19" spans="1:9" s="6" customFormat="1" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="91"/>
-      <c r="B19" s="91"/>
-      <c r="C19" s="27">
-        <v>6.4</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>324</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>316</v>
-      </c>
-      <c r="H19" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A20" s="52"/>
-      <c r="B20" s="91"/>
-      <c r="C20" s="24">
-        <v>6.5</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>314</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="G20" s="25" t="s">
-        <v>323</v>
-      </c>
-      <c r="H20" s="26"/>
-      <c r="I20" s="24"/>
-    </row>
-    <row r="21" spans="1:9" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="52"/>
-      <c r="B21" s="101"/>
-      <c r="C21" s="24">
-        <v>6.6</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="G21" s="25" t="s">
-        <v>325</v>
-      </c>
-      <c r="H21" s="26"/>
-      <c r="I21" s="24"/>
-    </row>
-    <row r="22" spans="1:9" s="6" customFormat="1" ht="145" x14ac:dyDescent="0.35">
-      <c r="A22" s="92">
-        <v>7</v>
-      </c>
-      <c r="B22" s="90" t="s">
-        <v>34</v>
-      </c>
-      <c r="C22" s="24">
-        <v>7.1</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="25" t="s">
-        <v>326</v>
-      </c>
-      <c r="H22" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="93"/>
-      <c r="B23" s="91"/>
-      <c r="C23" s="24">
-        <v>7.2</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="H23" s="26"/>
-      <c r="I23" s="24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="6" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="93"/>
-      <c r="B24" s="91"/>
-      <c r="C24" s="24">
-        <v>7.3</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="H24" s="26"/>
-      <c r="I24" s="24"/>
-    </row>
-    <row r="25" spans="1:9" s="6" customFormat="1" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="94"/>
-      <c r="B25" s="91"/>
-      <c r="C25" s="24">
-        <v>7.4</v>
-      </c>
-      <c r="D25" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="G25" s="25" t="s">
-        <v>327</v>
-      </c>
-      <c r="H25" s="26"/>
-      <c r="I25" s="24"/>
-    </row>
-    <row r="26" spans="1:9" s="6" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="52"/>
-      <c r="B26" s="101"/>
-      <c r="C26" s="24">
-        <v>7.5</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>320</v>
-      </c>
-      <c r="G26" s="25" t="s">
-        <v>328</v>
-      </c>
-      <c r="H26" s="26"/>
-      <c r="I26" s="24"/>
-    </row>
-    <row r="27" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="98">
-        <v>8</v>
-      </c>
-      <c r="B27" s="98" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="28">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="G27" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="99"/>
-      <c r="B28" s="99"/>
-      <c r="C28" s="28">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="D28" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="F28" s="28" t="s">
-        <v>257</v>
-      </c>
-      <c r="G28" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="100"/>
-      <c r="B29" s="100"/>
-      <c r="C29" s="28">
-        <v>9.4</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="F29" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="G29" s="29" t="s">
-        <v>260</v>
-      </c>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A30" s="96">
-        <v>12</v>
-      </c>
-      <c r="B30" s="96" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="30">
-        <v>12.1</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="E30" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="F30" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="H30" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="I30" s="30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A31" s="96"/>
-      <c r="B31" s="96"/>
-      <c r="C31" s="30">
-        <v>12.2</v>
-      </c>
-      <c r="D31" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="H31" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="I31" s="30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A32" s="96"/>
-      <c r="B32" s="96"/>
-      <c r="C32" s="30">
-        <v>12.3</v>
-      </c>
-      <c r="D32" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="E32" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="F32" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="G32" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="H32" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="I32" s="30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="6" customFormat="1" ht="123.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="96"/>
-      <c r="B33" s="96"/>
-      <c r="C33" s="30">
-        <v>12.4</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="E33" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="F33" s="30" t="s">
-        <v>221</v>
-      </c>
-      <c r="G33" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="H33" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="I33" s="30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="96"/>
-      <c r="B34" s="96"/>
-      <c r="C34" s="30">
-        <v>12.5</v>
-      </c>
-      <c r="D34" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="E34" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="F34" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="G34" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="H34" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="I34" s="30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="97">
-        <v>14</v>
-      </c>
-      <c r="B35" s="97" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="34">
-        <v>14.1</v>
-      </c>
-      <c r="D35" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E35" s="35" t="s">
-        <v>261</v>
-      </c>
-      <c r="F35" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="G35" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="H35" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="I35" s="34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="97"/>
-      <c r="B36" s="97"/>
-      <c r="C36" s="34">
-        <v>14.2</v>
-      </c>
-      <c r="D36" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E36" s="35" t="s">
+      <c r="B73" s="84" t="s">
+        <v>126</v>
+      </c>
+      <c r="C73" s="41">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="D73" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="E73" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="F73" s="42" t="s">
         <v>202</v>
       </c>
-      <c r="F36" s="35" t="s">
-        <v>264</v>
-      </c>
-      <c r="G36" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="H36" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="I36" s="34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="97"/>
-      <c r="B37" s="97"/>
-      <c r="C37" s="34">
-        <v>14.3</v>
-      </c>
-      <c r="D37" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="E37" s="35" t="s">
+      <c r="G73" s="43" t="s">
         <v>203</v>
       </c>
-      <c r="F37" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="G37" s="36" t="s">
-        <v>212</v>
-      </c>
-      <c r="H37" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="I37" s="34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A38" s="97"/>
-      <c r="B38" s="97"/>
-      <c r="C38" s="34">
-        <v>14.4</v>
-      </c>
-      <c r="D38" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E38" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="F38" s="35" t="s">
-        <v>243</v>
-      </c>
-      <c r="G38" s="36" t="s">
-        <v>213</v>
-      </c>
-      <c r="H38" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="I38" s="34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="97"/>
-      <c r="B39" s="97"/>
-      <c r="C39" s="34">
-        <v>14.5</v>
-      </c>
-      <c r="D39" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E39" s="35" t="s">
-        <v>266</v>
-      </c>
-      <c r="F39" s="35" t="s">
-        <v>267</v>
-      </c>
-      <c r="G39" s="36" t="s">
-        <v>214</v>
-      </c>
-      <c r="H39" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="I39" s="34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="97"/>
-      <c r="B40" s="97"/>
-      <c r="C40" s="34">
-        <v>14.6</v>
-      </c>
-      <c r="D40" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E40" s="35" t="s">
-        <v>206</v>
-      </c>
-      <c r="F40" s="35" t="s">
-        <v>268</v>
-      </c>
-      <c r="G40" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="H40" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="I40" s="34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="97"/>
-      <c r="B41" s="97"/>
-      <c r="C41" s="34">
-        <v>14.7</v>
-      </c>
-      <c r="D41" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E41" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="F41" s="35" t="s">
-        <v>245</v>
-      </c>
-      <c r="G41" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="H41" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="I41" s="34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="97"/>
-      <c r="B42" s="97"/>
-      <c r="C42" s="34">
-        <v>14.8</v>
-      </c>
-      <c r="D42" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E42" s="35" t="s">
-        <v>207</v>
-      </c>
-      <c r="F42" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="G42" s="36" t="s">
-        <v>215</v>
-      </c>
-      <c r="H42" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="I42" s="34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="97"/>
-      <c r="B43" s="97"/>
-      <c r="C43" s="34">
-        <v>14.9</v>
-      </c>
-      <c r="D43" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E43" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="F43" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="G43" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="H43" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="I43" s="34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A44" s="97"/>
-      <c r="B44" s="97"/>
-      <c r="C44" s="34">
-        <v>14.1</v>
-      </c>
-      <c r="D44" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E44" s="35" t="s">
-        <v>210</v>
-      </c>
-      <c r="F44" s="35" t="s">
-        <v>248</v>
-      </c>
-      <c r="G44" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="H44" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="I44" s="34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="97"/>
-      <c r="B45" s="97"/>
-      <c r="C45" s="34">
-        <v>14.11</v>
-      </c>
-      <c r="D45" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E45" s="35" t="s">
-        <v>211</v>
-      </c>
-      <c r="F45" s="35" t="s">
-        <v>270</v>
-      </c>
-      <c r="G45" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="H45" s="34" t="s">
-        <v>73</v>
-      </c>
-      <c r="I45" s="34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A46" s="95">
-        <v>15</v>
-      </c>
-      <c r="B46" s="95" t="s">
-        <v>74</v>
-      </c>
-      <c r="C46" s="37">
-        <v>15.1</v>
-      </c>
-      <c r="D46" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E46" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="F46" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="G46" s="38" t="s">
-        <v>150</v>
-      </c>
-      <c r="H46" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="I46" s="37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A47" s="75"/>
-      <c r="B47" s="75"/>
-      <c r="C47" s="37">
-        <v>15.2</v>
-      </c>
-      <c r="D47" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E47" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="G47" s="38" t="s">
-        <v>151</v>
-      </c>
-      <c r="H47" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="I47" s="37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A48" s="75"/>
-      <c r="B48" s="75"/>
-      <c r="C48" s="37">
-        <v>15.3</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="F48" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="G48" s="38" t="s">
-        <v>152</v>
-      </c>
-      <c r="H48" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="I48" s="37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="75"/>
-      <c r="B49" s="75"/>
-      <c r="C49" s="37">
-        <v>15.4</v>
-      </c>
-      <c r="D49" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E49" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="F49" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="G49" s="38" t="s">
-        <v>251</v>
-      </c>
-      <c r="H49" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="I49" s="37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A50" s="75"/>
-      <c r="B50" s="75"/>
-      <c r="C50" s="37">
-        <v>15.5</v>
-      </c>
-      <c r="D50" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E50" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="F50" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="G50" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="H50" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="I50" s="37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A51" s="75"/>
-      <c r="B51" s="75"/>
-      <c r="C51" s="37">
-        <v>15.6</v>
-      </c>
-      <c r="D51" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E51" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="F51" s="37" t="s">
-        <v>252</v>
-      </c>
-      <c r="G51" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="H51" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="I51" s="37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="75"/>
-      <c r="B52" s="75"/>
-      <c r="C52" s="37">
-        <v>15.7</v>
-      </c>
-      <c r="D52" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E52" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="F52" s="37" t="s">
-        <v>253</v>
-      </c>
-      <c r="G52" s="38" t="s">
-        <v>273</v>
-      </c>
-      <c r="H52" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="I52" s="37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A53" s="75"/>
-      <c r="B53" s="75"/>
-      <c r="C53" s="37">
-        <v>15.8</v>
-      </c>
-      <c r="D53" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="E53" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="F53" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="G53" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="H53" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="I53" s="37" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="74">
-        <v>16</v>
-      </c>
-      <c r="B54" s="74" t="s">
-        <v>89</v>
-      </c>
-      <c r="C54" s="39">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="D54" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E54" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="F54" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="G54" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="H54" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="I54" s="40" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A55" s="74"/>
-      <c r="B55" s="74"/>
-      <c r="C55" s="39">
-        <v>16.2</v>
-      </c>
-      <c r="D55" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E55" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="F55" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="G55" s="41" t="s">
-        <v>156</v>
-      </c>
-      <c r="H55" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="I55" s="40" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="74"/>
-      <c r="B56" s="74"/>
-      <c r="C56" s="39">
-        <v>16.3</v>
-      </c>
-      <c r="D56" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E56" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="F56" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="G56" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="H56" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="I56" s="40" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A57" s="74"/>
-      <c r="B57" s="74"/>
-      <c r="C57" s="39">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="D57" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E57" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="F57" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="G57" s="41" t="s">
-        <v>158</v>
-      </c>
-      <c r="H57" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="I57" s="40" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A58" s="74"/>
-      <c r="B58" s="74"/>
-      <c r="C58" s="39">
-        <v>16.5</v>
-      </c>
-      <c r="D58" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E58" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="F58" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="G58" s="41" t="s">
-        <v>159</v>
-      </c>
-      <c r="H58" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="I58" s="40" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A59" s="75"/>
-      <c r="B59" s="75"/>
-      <c r="C59" s="39">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="D59" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E59" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="F59" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="G59" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="H59" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="I59" s="40" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="76">
-        <v>17</v>
-      </c>
-      <c r="B60" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="C60" s="42">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="D60" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="E60" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="F60" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="G60" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="H60" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="I60" s="42" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="77"/>
-      <c r="B61" s="79"/>
-      <c r="C61" s="42">
-        <v>17.2</v>
-      </c>
-      <c r="D61" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="E61" s="42" t="s">
-        <v>110</v>
-      </c>
-      <c r="F61" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="G61" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="H61" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="I61" s="42" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A62" s="77"/>
-      <c r="B62" s="79"/>
-      <c r="C62" s="42">
-        <v>17.3</v>
-      </c>
-      <c r="D62" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="E62" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="F62" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="G62" s="43" t="s">
-        <v>163</v>
-      </c>
-      <c r="H62" s="42" t="s">
-        <v>93</v>
-      </c>
-      <c r="I62" s="42" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="77"/>
-      <c r="B63" s="79"/>
-      <c r="C63" s="42">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="D63" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="E63" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="F63" s="42" t="s">
-        <v>115</v>
-      </c>
-      <c r="G63" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="H63" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="I63" s="42" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A64" s="78"/>
-      <c r="B64" s="79"/>
-      <c r="C64" s="42">
-        <v>17.5</v>
-      </c>
-      <c r="D64" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="E64" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="F64" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="G64" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="H64" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="I64" s="42" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A65" s="80">
-        <v>18</v>
-      </c>
-      <c r="B65" s="81" t="s">
-        <v>279</v>
-      </c>
-      <c r="C65" s="18">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="D65" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E65" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="F65" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="G65" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="H65" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I65" s="18" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" s="6" customFormat="1" ht="250.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="75"/>
-      <c r="B66" s="82"/>
-      <c r="C66" s="18">
-        <v>18.2</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="F66" s="18" t="s">
-        <v>284</v>
-      </c>
-      <c r="G66" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="H66" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I66" s="18" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="75"/>
-      <c r="B67" s="82"/>
-      <c r="C67" s="18">
-        <v>18.3</v>
-      </c>
-      <c r="D67" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="F67" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="G67" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="H67" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I67" s="18" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" s="6" customFormat="1" ht="246.5" x14ac:dyDescent="0.35">
-      <c r="A68" s="75"/>
-      <c r="B68" s="82"/>
-      <c r="C68" s="18">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="F68" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="G68" s="19" t="s">
-        <v>304</v>
-      </c>
-      <c r="H68" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="I68" s="18" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" s="6" customFormat="1" ht="216" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="48"/>
-      <c r="B69" s="83"/>
-      <c r="C69" s="18">
-        <v>18.5</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="F69" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="G69" s="19" t="s">
-        <v>305</v>
-      </c>
-      <c r="H69" s="18"/>
-      <c r="I69" s="18"/>
-    </row>
-    <row r="70" spans="1:12" s="6" customFormat="1" ht="87" x14ac:dyDescent="0.35">
-      <c r="A70" s="68">
-        <v>19</v>
-      </c>
-      <c r="B70" s="71" t="s">
-        <v>120</v>
-      </c>
-      <c r="C70" s="44">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="D70" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="E70" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="F70" s="45" t="s">
-        <v>223</v>
-      </c>
-      <c r="G70" s="46" t="s">
-        <v>225</v>
-      </c>
-      <c r="H70" s="44"/>
-      <c r="I70" s="47"/>
-    </row>
-    <row r="71" spans="1:12" s="6" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="69"/>
-      <c r="B71" s="72"/>
-      <c r="C71" s="15">
-        <v>19.2</v>
-      </c>
-      <c r="D71" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="E71" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="F71" s="45" t="s">
-        <v>219</v>
-      </c>
-      <c r="G71" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="H71" s="44"/>
-      <c r="I71" s="47"/>
-    </row>
-    <row r="72" spans="1:12" s="6" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="70"/>
-      <c r="B72" s="73"/>
-      <c r="C72" s="53">
-        <v>19.3</v>
-      </c>
-      <c r="D72" s="54" t="s">
-        <v>121</v>
-      </c>
-      <c r="E72" s="54" t="s">
-        <v>307</v>
-      </c>
-      <c r="F72" s="54" t="s">
-        <v>308</v>
-      </c>
-      <c r="G72" s="55" t="s">
-        <v>331</v>
-      </c>
-      <c r="H72" s="56"/>
-      <c r="I72" s="57" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" s="6" customFormat="1" ht="203" x14ac:dyDescent="0.35">
-      <c r="A73" s="68">
-        <v>20</v>
-      </c>
-      <c r="B73" s="71" t="s">
-        <v>126</v>
-      </c>
-      <c r="C73" s="44">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="D73" s="45" t="s">
-        <v>127</v>
-      </c>
-      <c r="E73" s="45" t="s">
-        <v>236</v>
-      </c>
-      <c r="F73" s="45" t="s">
-        <v>237</v>
-      </c>
-      <c r="G73" s="46" t="s">
-        <v>238</v>
-      </c>
-      <c r="H73" s="44"/>
-      <c r="I73" s="47"/>
-    </row>
-    <row r="74" spans="1:12" s="6" customFormat="1" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A74" s="69"/>
-      <c r="B74" s="72"/>
-      <c r="C74" s="15">
+      <c r="H73" s="41"/>
+      <c r="I73" s="44"/>
+    </row>
+    <row r="74" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A74" s="82"/>
+      <c r="B74" s="85"/>
+      <c r="C74" s="12">
         <v>20.2</v>
       </c>
-      <c r="D74" s="45" t="s">
+      <c r="D74" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="E74" s="45" t="s">
-        <v>226</v>
-      </c>
-      <c r="F74" s="45" t="s">
-        <v>219</v>
-      </c>
-      <c r="G74" s="46" t="s">
-        <v>227</v>
-      </c>
-      <c r="H74" s="44"/>
-      <c r="I74" s="47"/>
+      <c r="E74" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="F74" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="G74" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="H74" s="41"/>
+      <c r="I74" s="44"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
     </row>
-    <row r="75" spans="1:12" s="6" customFormat="1" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A75" s="70"/>
-      <c r="B75" s="72"/>
-      <c r="C75" s="56">
+    <row r="75" spans="1:12" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="83"/>
+      <c r="B75" s="85"/>
+      <c r="C75" s="53">
         <v>20.3</v>
       </c>
-      <c r="D75" s="54" t="s">
+      <c r="D75" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="E75" s="54" t="s">
-        <v>309</v>
-      </c>
-      <c r="F75" s="54" t="s">
-        <v>312</v>
-      </c>
-      <c r="G75" s="55" t="s">
-        <v>330</v>
-      </c>
-      <c r="H75" s="56"/>
-      <c r="I75" s="57" t="s">
-        <v>313</v>
+      <c r="E75" s="51" t="s">
+        <v>274</v>
+      </c>
+      <c r="F75" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="G75" s="52" t="s">
+        <v>295</v>
+      </c>
+      <c r="H75" s="53"/>
+      <c r="I75" s="54" t="s">
+        <v>278</v>
       </c>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
     </row>
-    <row r="76" spans="1:12" s="6" customFormat="1" ht="333.5" x14ac:dyDescent="0.35">
-      <c r="A76" s="49"/>
-      <c r="B76" s="73"/>
-      <c r="C76" s="56">
+    <row r="76" spans="1:12" s="6" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
+      <c r="A76" s="46"/>
+      <c r="B76" s="86"/>
+      <c r="C76" s="53">
         <v>20.399999999999999</v>
       </c>
-      <c r="D76" s="54" t="s">
+      <c r="D76" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="E76" s="54" t="s">
-        <v>310</v>
-      </c>
-      <c r="F76" s="54" t="s">
-        <v>311</v>
-      </c>
-      <c r="G76" s="55" t="s">
-        <v>329</v>
-      </c>
-      <c r="H76" s="56"/>
-      <c r="I76" s="57" t="s">
-        <v>313</v>
+      <c r="E76" s="51" t="s">
+        <v>275</v>
+      </c>
+      <c r="F76" s="51" t="s">
+        <v>276</v>
+      </c>
+      <c r="G76" s="52" t="s">
+        <v>294</v>
+      </c>
+      <c r="H76" s="53"/>
+      <c r="I76" s="54" t="s">
+        <v>278</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
     </row>
-    <row r="77" spans="1:12" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A77" s="68">
+    <row r="77" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A77" s="81">
         <v>21</v>
       </c>
-      <c r="B77" s="71" t="s">
+      <c r="B77" s="84" t="s">
         <v>129</v>
       </c>
-      <c r="C77" s="44">
+      <c r="C77" s="41">
         <v>21.1</v>
       </c>
-      <c r="D77" s="45" t="s">
+      <c r="D77" s="42" t="s">
         <v>130</v>
       </c>
-      <c r="E77" s="45" t="s">
-        <v>228</v>
-      </c>
-      <c r="F77" s="45" t="s">
-        <v>229</v>
-      </c>
-      <c r="G77" s="46" t="s">
-        <v>230</v>
-      </c>
-      <c r="H77" s="44"/>
-      <c r="I77" s="47"/>
-    </row>
-    <row r="78" spans="1:12" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A78" s="69"/>
-      <c r="B78" s="72"/>
-      <c r="C78" s="15">
+      <c r="E77" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="F77" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="G77" s="43" t="s">
+        <v>195</v>
+      </c>
+      <c r="H77" s="41"/>
+      <c r="I77" s="44"/>
+    </row>
+    <row r="78" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="82"/>
+      <c r="B78" s="85"/>
+      <c r="C78" s="12">
         <v>21.2</v>
       </c>
-      <c r="D78" s="45" t="s">
+      <c r="D78" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="E78" s="45" t="s">
-        <v>218</v>
-      </c>
-      <c r="F78" s="45" t="s">
-        <v>219</v>
-      </c>
-      <c r="G78" s="46" t="s">
+      <c r="E78" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="F78" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="G78" s="43" t="s">
         <v>132</v>
       </c>
-      <c r="H78" s="44"/>
-      <c r="I78" s="47"/>
-    </row>
-    <row r="79" spans="1:12" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="70"/>
-      <c r="B79" s="73"/>
-      <c r="C79" s="32">
+      <c r="H78" s="41"/>
+      <c r="I78" s="44"/>
+    </row>
+    <row r="79" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A79" s="83"/>
+      <c r="B79" s="86"/>
+      <c r="C79" s="29">
         <v>21.3</v>
       </c>
-      <c r="D79" s="16" t="s">
+      <c r="D79" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="E79" s="16" t="s">
+      <c r="E79" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="F79" s="16"/>
-      <c r="G79" s="17"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="33"/>
-    </row>
-    <row r="80" spans="1:12" ht="261" x14ac:dyDescent="0.35">
-      <c r="A80" s="68">
+      <c r="F79" s="13"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="29"/>
+      <c r="I79" s="30"/>
+    </row>
+    <row r="80" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A80" s="81">
         <v>22</v>
       </c>
-      <c r="B80" s="71" t="s">
+      <c r="B80" s="84" t="s">
         <v>133</v>
       </c>
-      <c r="C80" s="44">
+      <c r="C80" s="41">
         <v>22.1</v>
       </c>
-      <c r="D80" s="45" t="s">
+      <c r="D80" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="E80" s="45" t="s">
-        <v>233</v>
-      </c>
-      <c r="F80" s="45" t="s">
-        <v>234</v>
-      </c>
-      <c r="G80" s="46" t="s">
-        <v>235</v>
-      </c>
-      <c r="H80" s="44"/>
-      <c r="I80" s="47"/>
-    </row>
-    <row r="81" spans="1:9" ht="261" x14ac:dyDescent="0.35">
-      <c r="A81" s="69"/>
-      <c r="B81" s="72"/>
-      <c r="C81" s="15">
+      <c r="E80" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="F80" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="G80" s="43" t="s">
+        <v>200</v>
+      </c>
+      <c r="H80" s="41"/>
+      <c r="I80" s="44"/>
+    </row>
+    <row r="81" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A81" s="82"/>
+      <c r="B81" s="85"/>
+      <c r="C81" s="12">
         <v>22.2</v>
       </c>
-      <c r="D81" s="45" t="s">
-        <v>217</v>
-      </c>
-      <c r="E81" s="44" t="s">
-        <v>231</v>
-      </c>
-      <c r="F81" s="45" t="s">
-        <v>219</v>
-      </c>
-      <c r="G81" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="H81" s="44"/>
-      <c r="I81" s="47"/>
-    </row>
-    <row r="82" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A82" s="70"/>
-      <c r="B82" s="73"/>
-      <c r="C82" s="32">
+      <c r="D81" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="E81" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="F81" s="42" t="s">
+        <v>184</v>
+      </c>
+      <c r="G81" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="H81" s="41"/>
+      <c r="I81" s="44"/>
+    </row>
+    <row r="82" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A82" s="83"/>
+      <c r="B82" s="86"/>
+      <c r="C82" s="29">
         <v>22.3</v>
       </c>
-      <c r="D82" s="16" t="s">
+      <c r="D82" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="E82" s="32" t="s">
+      <c r="E82" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="F82" s="16"/>
-      <c r="G82" s="17"/>
-      <c r="H82" s="32"/>
-      <c r="I82" s="33"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F82" s="13"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="29"/>
+      <c r="I82" s="30"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
-      <c r="E83" s="11"/>
+      <c r="E83" s="10"/>
       <c r="H83" s="3"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="I84" s="2"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="I85" s="2"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
@@ -9896,100 +8634,77 @@
       <c r="H86" s="7"/>
       <c r="I86" s="7"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
-      <c r="D87" s="10"/>
-      <c r="E87" s="10"/>
-      <c r="F87" s="10"/>
+      <c r="D87" s="9"/>
+      <c r="E87" s="9"/>
+      <c r="F87" s="9"/>
       <c r="G87" s="8"/>
-      <c r="H87" s="10"/>
-      <c r="I87" s="10"/>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D88" s="10"/>
-      <c r="E88" s="10"/>
-      <c r="F88" s="10"/>
+      <c r="H87" s="9"/>
+      <c r="I87" s="9"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9"/>
       <c r="G88" s="8"/>
-      <c r="H88" s="10"/>
-      <c r="I88" s="10"/>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H88" s="9"/>
+      <c r="I88" s="9"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B89" s="3"/>
-      <c r="D89" s="10"/>
-      <c r="E89" s="10"/>
-      <c r="F89" s="10"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9"/>
       <c r="G89" s="8"/>
-      <c r="H89" s="10"/>
-      <c r="I89" s="10"/>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D90" s="10"/>
-      <c r="E90" s="10"/>
-      <c r="F90" s="10"/>
+      <c r="H89" s="9"/>
+      <c r="I89" s="9"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9"/>
       <c r="G90" s="8"/>
-      <c r="H90" s="10"/>
-      <c r="I90" s="10"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D91" s="10"/>
-      <c r="E91" s="10"/>
-      <c r="F91" s="10"/>
+      <c r="H90" s="9"/>
+      <c r="I90" s="9"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9"/>
       <c r="G91" s="8"/>
-      <c r="H91" s="10"/>
-      <c r="I91" s="10"/>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D92" s="10"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
+      <c r="H91" s="9"/>
+      <c r="I91" s="9"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D92" s="9"/>
+      <c r="E92" s="9"/>
+      <c r="F92" s="9"/>
       <c r="G92" s="8"/>
-      <c r="H92" s="10"/>
-      <c r="I92" s="10"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D93" s="10"/>
-      <c r="E93" s="10"/>
-      <c r="F93" s="10"/>
+      <c r="H92" s="9"/>
+      <c r="I92" s="9"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D93" s="9"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9"/>
       <c r="G93" s="8"/>
-      <c r="H93" s="10"/>
-      <c r="I93" s="10"/>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D94" s="10"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="10"/>
+      <c r="H93" s="9"/>
+      <c r="I93" s="9"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D94" s="9"/>
+      <c r="E94" s="9"/>
+      <c r="F94" s="9"/>
       <c r="G94" s="8"/>
-      <c r="H94" s="10"/>
-      <c r="I94" s="10"/>
+      <c r="H94" s="9"/>
+      <c r="I94" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="I1:I32" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A46:A53"/>
-    <mergeCell ref="B46:B53"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="A35:A45"/>
-    <mergeCell ref="B35:B45"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B10"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="A80:A82"/>
@@ -10004,6 +8719,29 @@
     <mergeCell ref="A73:A75"/>
     <mergeCell ref="B73:B76"/>
     <mergeCell ref="B65:B69"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B10"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A46:A53"/>
+    <mergeCell ref="B46:B53"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="A35:A45"/>
+    <mergeCell ref="B35:B45"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="B22:B26"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10013,810 +8751,202 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0802363A-09BC-4F89-B136-783D2DDEAFD1}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="18.1796875" customWidth="1"/>
-    <col min="5" max="5" width="24.90625" customWidth="1"/>
-    <col min="6" max="6" width="27.36328125" customWidth="1"/>
-    <col min="7" max="7" width="36.1796875" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" style="96" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" customWidth="1"/>
+    <col min="3" max="3" width="55.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="89.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="9"/>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-    </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="I3" s="12" t="s">
+    <row r="1" spans="1:5" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="94" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>298</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>299</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="9"/>
-    </row>
-    <row r="4" spans="1:10" ht="348" x14ac:dyDescent="0.35">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="13">
-        <v>14.1</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="J4" s="9"/>
-    </row>
-    <row r="5" spans="1:10" ht="362.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="13">
-        <v>14.2</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="J5" s="9"/>
-    </row>
-    <row r="6" spans="1:10" ht="348" x14ac:dyDescent="0.35">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="13">
-        <v>14.3</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="J6" s="9"/>
-    </row>
-    <row r="7" spans="1:10" ht="406" x14ac:dyDescent="0.35">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="13">
-        <v>14.4</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="J7" s="9"/>
-    </row>
-    <row r="8" spans="1:10" ht="333.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="13">
-        <v>14.5</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="13">
-        <v>14.6</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" spans="1:10" ht="348" x14ac:dyDescent="0.35">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" s="13">
-        <v>14.7</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" spans="1:10" ht="319" x14ac:dyDescent="0.35">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E11" s="13">
-        <v>14.8</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" spans="1:10" ht="304.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="13">
-        <v>14.9</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="J12" s="9"/>
-    </row>
-    <row r="13" spans="1:10" ht="391.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="J13" s="9"/>
-    </row>
-    <row r="14" spans="1:10" ht="290" x14ac:dyDescent="0.35">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="13">
-        <v>14.11</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="J14" s="9"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0802363A-09BC-4F89-B136-783D2DDEAFD1}">
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="21.81640625" customWidth="1"/>
-    <col min="2" max="2" width="43.54296875" customWidth="1"/>
-    <col min="3" max="3" width="55.1796875" customWidth="1"/>
-    <col min="4" max="4" width="70.1796875" customWidth="1"/>
-    <col min="5" max="5" width="89.81640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="37.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="95" t="s">
+        <v>334</v>
+      </c>
+      <c r="B2" s="93" t="s">
+        <v>337</v>
+      </c>
+      <c r="C2" s="93" t="s">
+        <v>338</v>
+      </c>
+      <c r="D2" s="93" t="s">
+        <v>335</v>
+      </c>
+      <c r="E2" s="57" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A3" s="95">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B3" s="93" t="s">
+        <v>333</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>320</v>
+      </c>
+      <c r="D3" s="56" t="s">
+        <v>321</v>
+      </c>
+      <c r="E3" s="55" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A4" s="95">
+        <v>5.2</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>301</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>302</v>
+      </c>
+      <c r="D4" s="56" t="s">
+        <v>303</v>
+      </c>
+      <c r="E4" s="57" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="95">
+        <v>5.3</v>
+      </c>
+      <c r="B5" s="56" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" s="56" t="s">
+        <v>305</v>
+      </c>
+      <c r="D5" s="56" t="s">
+        <v>306</v>
+      </c>
+      <c r="E5" s="57" t="s">
         <v>332</v>
       </c>
-      <c r="B1" s="67" t="s">
-        <v>333</v>
-      </c>
-      <c r="C1" s="67" t="s">
-        <v>334</v>
-      </c>
-      <c r="D1" s="67" t="s">
-        <v>335</v>
-      </c>
-      <c r="E1" s="67" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="145" x14ac:dyDescent="0.35">
-      <c r="A2" s="58">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B2" s="59" t="s">
-        <v>336</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>337</v>
-      </c>
-      <c r="D2" s="59" t="s">
-        <v>338</v>
-      </c>
-      <c r="E2" s="60" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="58">
-        <v>5.2</v>
-      </c>
-      <c r="B3" s="59" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="95">
+        <v>5.4</v>
+      </c>
+      <c r="B6" s="56" t="s">
+        <v>301</v>
+      </c>
+      <c r="C6" s="56" t="s">
+        <v>307</v>
+      </c>
+      <c r="D6" s="56" t="s">
+        <v>308</v>
+      </c>
+      <c r="E6" s="55" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="101">
+        <v>5.5</v>
+      </c>
+      <c r="B7" s="102" t="s">
+        <v>309</v>
+      </c>
+      <c r="C7" s="102" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" s="102" t="s">
+        <v>311</v>
+      </c>
+      <c r="E7" s="103" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="95">
+        <v>5.6</v>
+      </c>
+      <c r="B8" s="56" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8" s="56" t="s">
+        <v>313</v>
+      </c>
+      <c r="D8" s="56" t="s">
+        <v>314</v>
+      </c>
+      <c r="E8" s="57" t="s">
         <v>339</v>
       </c>
-      <c r="C3" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="D3" s="59" t="s">
-        <v>341</v>
-      </c>
-      <c r="E3" s="60" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="116" x14ac:dyDescent="0.35">
-      <c r="A4" s="58">
-        <v>5.3</v>
-      </c>
-      <c r="B4" s="59" t="s">
-        <v>336</v>
-      </c>
-      <c r="C4" s="59" t="s">
-        <v>342</v>
-      </c>
-      <c r="D4" s="59" t="s">
-        <v>343</v>
-      </c>
-      <c r="E4" s="60" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="58">
-        <v>5.4</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>336</v>
-      </c>
-      <c r="C5" s="59" t="s">
-        <v>344</v>
-      </c>
-      <c r="D5" s="59" t="s">
-        <v>345</v>
-      </c>
-      <c r="E5" s="58" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="116" x14ac:dyDescent="0.35">
-      <c r="A6" s="61">
-        <v>5.5</v>
-      </c>
-      <c r="B6" s="62" t="s">
-        <v>346</v>
-      </c>
-      <c r="C6" s="62" t="s">
-        <v>347</v>
-      </c>
-      <c r="D6" s="62" t="s">
-        <v>348</v>
-      </c>
-      <c r="E6" s="102" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="116" x14ac:dyDescent="0.35">
-      <c r="A7" s="58">
-        <v>5.6</v>
-      </c>
-      <c r="B7" s="59" t="s">
-        <v>349</v>
-      </c>
-      <c r="C7" s="59" t="s">
-        <v>350</v>
-      </c>
-      <c r="D7" s="59" t="s">
-        <v>351</v>
-      </c>
-      <c r="E7" s="60" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="145" x14ac:dyDescent="0.35">
-      <c r="A8" s="63">
+    </row>
+    <row r="9" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="100">
         <v>5.7</v>
       </c>
-      <c r="B8" s="64" t="s">
-        <v>352</v>
-      </c>
-      <c r="C8" s="64" t="s">
-        <v>353</v>
-      </c>
-      <c r="D8" s="65" t="s">
-        <v>371</v>
-      </c>
-      <c r="E8" s="63" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="58">
+      <c r="B9" s="97" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" s="97" t="s">
+        <v>316</v>
+      </c>
+      <c r="D9" s="98" t="s">
+        <v>326</v>
+      </c>
+      <c r="E9" s="99" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="95">
         <v>5.8</v>
       </c>
-      <c r="B9" s="59" t="s">
-        <v>354</v>
-      </c>
-      <c r="C9" s="59" t="s">
-        <v>355</v>
-      </c>
-      <c r="D9" s="59" t="s">
-        <v>356</v>
-      </c>
-      <c r="E9" s="58" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="58">
+      <c r="B10" s="56" t="s">
+        <v>317</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>318</v>
+      </c>
+      <c r="D10" s="56" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" s="55" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="95">
         <v>5.9</v>
       </c>
-      <c r="B10" s="59" t="s">
-        <v>357</v>
-      </c>
-      <c r="C10" s="59" t="s">
-        <v>358</v>
-      </c>
-      <c r="D10" s="59" t="s">
-        <v>359</v>
-      </c>
-      <c r="E10" s="58" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="145" x14ac:dyDescent="0.35">
-      <c r="A11" s="66">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="B11" s="59" t="s">
-        <v>360</v>
-      </c>
-      <c r="C11" s="59" t="s">
-        <v>361</v>
-      </c>
-      <c r="D11" s="59" t="s">
-        <v>362</v>
-      </c>
-      <c r="E11" s="58" t="s">
-        <v>367</v>
+      <c r="B11" s="93" t="s">
+        <v>330</v>
+      </c>
+      <c r="C11" s="93" t="s">
+        <v>328</v>
+      </c>
+      <c r="D11" s="93" t="s">
+        <v>329</v>
+      </c>
+      <c r="E11" s="57" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/Business Analysis/checkupp_product_backlog.xlsx
+++ b/Business Analysis/checkupp_product_backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8CB6421-DABA-4057-AC9D-672152928404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8404C94-CBC7-4AE4-91FD-931273E72FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5136,6 +5136,464 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Logged-in user navigating the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Screenings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">tap on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vaccine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab located at the top</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> must be displayed separately from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommended for You</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cards within </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> must follow their defined frontend visibility rules.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Travel must be available to all users.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Children (0–4 years) must follow the 16+ visibility rule</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. (Must be obscured in MVP)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Age/life-stage categories shown for general browsing must appear in the order specified by the approved wireframe.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Changes to the configured test/user profile must result in the appropriate category visibility changes when the screen is re-rendered.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Children (0–4 years)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> card must be displayed under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when the configured user's age is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16 years or older</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The Children card must not be displayed when the configured user's age is below 16.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The boundary value of exactly 16 years must result in the Children card being displayed.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Visibility of the Children card must not depend on gender or pregnancy status.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting the card must display the vaccination information configured for children aged 0–4 years.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Must be obscured in MVP.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -5146,7 +5604,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Screenings bottom nav tab's screen must display 3 top tabs in the following order:</t>
+      <t>Screenings bottom navigation tab's screen must display 3 top tabs in the following order:</t>
     </r>
     <r>
       <rPr>
@@ -5229,23 +5687,124 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> screen.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Logged-in user navigating the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Screenings</t>
+      <t xml:space="preserve"> screen, rendered under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vaccine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tapping </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Immunisation Checkups</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Home</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottom navigation tab must navigate the user to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Immunisation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen, rendered under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vaccine</t>
     </r>
     <r>
       <rPr>
@@ -5256,438 +5815,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> tab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Vaccine</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab located at the top</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Categories</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> must be displayed separately from </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Recommended for You</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Cards within </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Categories</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> must follow their defined frontend visibility rules.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Travel must be available to all users.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Children (0–4 years) must follow the 16+ visibility rule</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. (Must be obscured in MVP)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Age/life-stage categories shown for general browsing must appear in the order specified by the approved wireframe.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Changes to the configured test/user profile must result in the appropriate category visibility changes when the screen is re-rendered.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Children (0–4 years)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> card must be displayed under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Categories</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> when the configured user's age is </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>16 years or older</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The Children card must not be displayed when the configured user's age is below 16.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The boundary value of exactly 16 years must result in the Children card being displayed.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Visibility of the Children card must not depend on gender or pregnancy status.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Selecting the card must display the vaccination information configured for children aged 0–4 years.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Must be obscured in MVP.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
     </r>
   </si>
 </sst>
@@ -5695,11 +5822,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -6081,7 +6215,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -6094,10 +6228,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -6112,287 +6246,287 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6632,34 +6766,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="72" t="s">
+      <c r="B1" s="86" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="72" t="s">
+      <c r="C1" s="86" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="72" t="s">
+      <c r="D1" s="86" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="76" t="s">
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="72" t="s">
+      <c r="H1" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="72" t="s">
+      <c r="I1" s="86" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="65"/>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -6669,15 +6803,15 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="76"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
+      <c r="G2" s="87"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="3" spans="1:9" s="5" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="77">
+      <c r="A3" s="88">
         <v>1</v>
       </c>
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="89" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="13">
@@ -6703,8 +6837,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="6" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="77"/>
-      <c r="B4" s="79"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="90"/>
       <c r="C4" s="13">
         <v>1.2</v>
       </c>
@@ -6724,8 +6858,8 @@
       <c r="I4" s="13"/>
     </row>
     <row r="5" spans="1:9" s="6" customFormat="1" ht="160.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="77"/>
-      <c r="B5" s="79"/>
+      <c r="A5" s="88"/>
+      <c r="B5" s="90"/>
       <c r="C5" s="13">
         <v>1.3</v>
       </c>
@@ -6745,8 +6879,8 @@
       <c r="I5" s="13"/>
     </row>
     <row r="6" spans="1:9" s="6" customFormat="1" ht="154.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="77"/>
-      <c r="B6" s="79"/>
+      <c r="A6" s="88"/>
+      <c r="B6" s="90"/>
       <c r="C6" s="13">
         <v>1.4</v>
       </c>
@@ -6766,8 +6900,8 @@
       <c r="I6" s="13"/>
     </row>
     <row r="7" spans="1:9" s="6" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="77"/>
-      <c r="B7" s="79"/>
+      <c r="A7" s="88"/>
+      <c r="B7" s="90"/>
       <c r="C7" s="13">
         <v>1.5</v>
       </c>
@@ -6788,7 +6922,7 @@
     </row>
     <row r="8" spans="1:9" s="6" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="47"/>
-      <c r="B8" s="79"/>
+      <c r="B8" s="90"/>
       <c r="C8" s="13">
         <v>1.6</v>
       </c>
@@ -6809,7 +6943,7 @@
     </row>
     <row r="9" spans="1:9" s="6" customFormat="1" ht="152.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="47"/>
-      <c r="B9" s="79"/>
+      <c r="B9" s="90"/>
       <c r="C9" s="13">
         <v>1.7</v>
       </c>
@@ -6830,7 +6964,7 @@
     </row>
     <row r="10" spans="1:9" s="6" customFormat="1" ht="295.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="47"/>
-      <c r="B10" s="80"/>
+      <c r="B10" s="91"/>
       <c r="C10" s="13">
         <v>1.8</v>
       </c>
@@ -6850,10 +6984,10 @@
       <c r="I10" s="48"/>
     </row>
     <row r="11" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="73">
+      <c r="A11" s="83">
         <v>5</v>
       </c>
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="83" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="15">
@@ -6879,8 +7013,8 @@
       </c>
     </row>
     <row r="12" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="74"/>
-      <c r="B12" s="74"/>
+      <c r="A12" s="84"/>
+      <c r="B12" s="84"/>
       <c r="C12" s="15">
         <v>5.2</v>
       </c>
@@ -6900,8 +7034,8 @@
       <c r="I12" s="15"/>
     </row>
     <row r="13" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="74"/>
-      <c r="B13" s="74"/>
+      <c r="A13" s="84"/>
+      <c r="B13" s="84"/>
       <c r="C13" s="15">
         <v>5.3</v>
       </c>
@@ -6921,8 +7055,8 @@
       <c r="I13" s="15"/>
     </row>
     <row r="14" spans="1:9" s="11" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="74"/>
-      <c r="B14" s="74"/>
+      <c r="A14" s="84"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="18">
         <v>5.4</v>
       </c>
@@ -6942,8 +7076,8 @@
       <c r="I14" s="18"/>
     </row>
     <row r="15" spans="1:9" s="11" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="75"/>
-      <c r="B15" s="75"/>
+      <c r="A15" s="85"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="18">
         <v>5.5</v>
       </c>
@@ -6963,10 +7097,10 @@
       <c r="I15" s="18"/>
     </row>
     <row r="16" spans="1:9" s="11" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="59">
+      <c r="A16" s="92">
         <v>6</v>
       </c>
-      <c r="B16" s="59" t="s">
+      <c r="B16" s="92" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="21">
@@ -6992,8 +7126,8 @@
       </c>
     </row>
     <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="60"/>
-      <c r="B17" s="60"/>
+      <c r="A17" s="93"/>
+      <c r="B17" s="93"/>
       <c r="C17" s="21">
         <v>6.2</v>
       </c>
@@ -7013,8 +7147,8 @@
       <c r="I17" s="21"/>
     </row>
     <row r="18" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="60"/>
-      <c r="B18" s="60"/>
+      <c r="A18" s="93"/>
+      <c r="B18" s="93"/>
       <c r="C18" s="21">
         <v>6.3</v>
       </c>
@@ -7034,8 +7168,8 @@
       <c r="I18" s="21"/>
     </row>
     <row r="19" spans="1:9" s="6" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="60"/>
-      <c r="B19" s="60"/>
+      <c r="A19" s="93"/>
+      <c r="B19" s="93"/>
       <c r="C19" s="24">
         <v>6.4</v>
       </c>
@@ -7060,7 +7194,7 @@
     </row>
     <row r="20" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A20" s="49"/>
-      <c r="B20" s="60"/>
+      <c r="B20" s="93"/>
       <c r="C20" s="21">
         <v>6.5</v>
       </c>
@@ -7081,7 +7215,7 @@
     </row>
     <row r="21" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="49"/>
-      <c r="B21" s="71"/>
+      <c r="B21" s="103"/>
       <c r="C21" s="21">
         <v>6.6</v>
       </c>
@@ -7101,10 +7235,10 @@
       <c r="I21" s="21"/>
     </row>
     <row r="22" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A22" s="61">
+      <c r="A22" s="94">
         <v>7</v>
       </c>
-      <c r="B22" s="59" t="s">
+      <c r="B22" s="92" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="21">
@@ -7130,8 +7264,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A23" s="62"/>
-      <c r="B23" s="60"/>
+      <c r="A23" s="95"/>
+      <c r="B23" s="93"/>
       <c r="C23" s="21">
         <v>7.2</v>
       </c>
@@ -7153,8 +7287,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="62"/>
-      <c r="B24" s="60"/>
+      <c r="A24" s="95"/>
+      <c r="B24" s="93"/>
       <c r="C24" s="21">
         <v>7.3</v>
       </c>
@@ -7174,8 +7308,8 @@
       <c r="I24" s="21"/>
     </row>
     <row r="25" spans="1:9" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="63"/>
-      <c r="B25" s="60"/>
+      <c r="A25" s="96"/>
+      <c r="B25" s="93"/>
       <c r="C25" s="21">
         <v>7.4</v>
       </c>
@@ -7196,7 +7330,7 @@
     </row>
     <row r="26" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A26" s="49"/>
-      <c r="B26" s="71"/>
+      <c r="B26" s="103"/>
       <c r="C26" s="21">
         <v>7.5</v>
       </c>
@@ -7216,10 +7350,10 @@
       <c r="I26" s="21"/>
     </row>
     <row r="27" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="68">
+      <c r="A27" s="100">
         <v>8</v>
       </c>
-      <c r="B27" s="68" t="s">
+      <c r="B27" s="100" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="25">
@@ -7243,8 +7377,8 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="69"/>
-      <c r="B28" s="69"/>
+      <c r="A28" s="101"/>
+      <c r="B28" s="101"/>
       <c r="C28" s="25">
         <v>9.3000000000000007</v>
       </c>
@@ -7266,8 +7400,8 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="70"/>
-      <c r="B29" s="70"/>
+      <c r="A29" s="102"/>
+      <c r="B29" s="102"/>
       <c r="C29" s="25">
         <v>9.4</v>
       </c>
@@ -7289,10 +7423,10 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="66">
+      <c r="A30" s="98">
         <v>12</v>
       </c>
-      <c r="B30" s="66" t="s">
+      <c r="B30" s="98" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="27">
@@ -7318,8 +7452,8 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="66"/>
-      <c r="B31" s="66"/>
+      <c r="A31" s="98"/>
+      <c r="B31" s="98"/>
       <c r="C31" s="27">
         <v>12.2</v>
       </c>
@@ -7343,8 +7477,8 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="66"/>
-      <c r="B32" s="66"/>
+      <c r="A32" s="98"/>
+      <c r="B32" s="98"/>
       <c r="C32" s="27">
         <v>12.3</v>
       </c>
@@ -7368,8 +7502,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="66"/>
-      <c r="B33" s="66"/>
+      <c r="A33" s="98"/>
+      <c r="B33" s="98"/>
       <c r="C33" s="27">
         <v>12.4</v>
       </c>
@@ -7393,8 +7527,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="66"/>
-      <c r="B34" s="66"/>
+      <c r="A34" s="98"/>
+      <c r="B34" s="98"/>
       <c r="C34" s="27">
         <v>12.5</v>
       </c>
@@ -7418,10 +7552,10 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="67">
+      <c r="A35" s="99">
         <v>14</v>
       </c>
-      <c r="B35" s="67" t="s">
+      <c r="B35" s="99" t="s">
         <v>70</v>
       </c>
       <c r="C35" s="31">
@@ -7447,8 +7581,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="67"/>
-      <c r="B36" s="67"/>
+      <c r="A36" s="99"/>
+      <c r="B36" s="99"/>
       <c r="C36" s="31">
         <v>14.2</v>
       </c>
@@ -7472,8 +7606,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="67"/>
-      <c r="B37" s="67"/>
+      <c r="A37" s="99"/>
+      <c r="B37" s="99"/>
       <c r="C37" s="31">
         <v>14.3</v>
       </c>
@@ -7497,8 +7631,8 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="67"/>
-      <c r="B38" s="67"/>
+      <c r="A38" s="99"/>
+      <c r="B38" s="99"/>
       <c r="C38" s="31">
         <v>14.4</v>
       </c>
@@ -7522,8 +7656,8 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="67"/>
-      <c r="B39" s="67"/>
+      <c r="A39" s="99"/>
+      <c r="B39" s="99"/>
       <c r="C39" s="31">
         <v>14.5</v>
       </c>
@@ -7547,8 +7681,8 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="67"/>
-      <c r="B40" s="67"/>
+      <c r="A40" s="99"/>
+      <c r="B40" s="99"/>
       <c r="C40" s="31">
         <v>14.6</v>
       </c>
@@ -7572,8 +7706,8 @@
       </c>
     </row>
     <row r="41" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="67"/>
-      <c r="B41" s="67"/>
+      <c r="A41" s="99"/>
+      <c r="B41" s="99"/>
       <c r="C41" s="31">
         <v>14.7</v>
       </c>
@@ -7597,8 +7731,8 @@
       </c>
     </row>
     <row r="42" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="67"/>
-      <c r="B42" s="67"/>
+      <c r="A42" s="99"/>
+      <c r="B42" s="99"/>
       <c r="C42" s="31">
         <v>14.8</v>
       </c>
@@ -7622,8 +7756,8 @@
       </c>
     </row>
     <row r="43" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="67"/>
-      <c r="B43" s="67"/>
+      <c r="A43" s="99"/>
+      <c r="B43" s="99"/>
       <c r="C43" s="31">
         <v>14.9</v>
       </c>
@@ -7647,8 +7781,8 @@
       </c>
     </row>
     <row r="44" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="67"/>
-      <c r="B44" s="67"/>
+      <c r="A44" s="99"/>
+      <c r="B44" s="99"/>
       <c r="C44" s="31">
         <v>14.1</v>
       </c>
@@ -7672,8 +7806,8 @@
       </c>
     </row>
     <row r="45" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="67"/>
-      <c r="B45" s="67"/>
+      <c r="A45" s="99"/>
+      <c r="B45" s="99"/>
       <c r="C45" s="31">
         <v>14.11</v>
       </c>
@@ -7697,10 +7831,10 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="64">
+      <c r="A46" s="97">
         <v>15</v>
       </c>
-      <c r="B46" s="64" t="s">
+      <c r="B46" s="97" t="s">
         <v>74</v>
       </c>
       <c r="C46" s="34">
@@ -7726,8 +7860,8 @@
       </c>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="65"/>
-      <c r="B47" s="65"/>
+      <c r="A47" s="77"/>
+      <c r="B47" s="77"/>
       <c r="C47" s="34">
         <v>15.2</v>
       </c>
@@ -7751,8 +7885,8 @@
       </c>
     </row>
     <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="65"/>
-      <c r="B48" s="65"/>
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
       <c r="C48" s="34">
         <v>15.3</v>
       </c>
@@ -7776,8 +7910,8 @@
       </c>
     </row>
     <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="65"/>
-      <c r="B49" s="65"/>
+      <c r="A49" s="77"/>
+      <c r="B49" s="77"/>
       <c r="C49" s="34">
         <v>15.4</v>
       </c>
@@ -7801,8 +7935,8 @@
       </c>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="65"/>
-      <c r="B50" s="65"/>
+      <c r="A50" s="77"/>
+      <c r="B50" s="77"/>
       <c r="C50" s="34">
         <v>15.5</v>
       </c>
@@ -7826,8 +7960,8 @@
       </c>
     </row>
     <row r="51" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="65"/>
-      <c r="B51" s="65"/>
+      <c r="A51" s="77"/>
+      <c r="B51" s="77"/>
       <c r="C51" s="34">
         <v>15.6</v>
       </c>
@@ -7851,8 +7985,8 @@
       </c>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="65"/>
-      <c r="B52" s="65"/>
+      <c r="A52" s="77"/>
+      <c r="B52" s="77"/>
       <c r="C52" s="34">
         <v>15.7</v>
       </c>
@@ -7876,8 +8010,8 @@
       </c>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="65"/>
-      <c r="B53" s="65"/>
+      <c r="A53" s="77"/>
+      <c r="B53" s="77"/>
       <c r="C53" s="34">
         <v>15.8</v>
       </c>
@@ -7901,10 +8035,10 @@
       </c>
     </row>
     <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="87">
+      <c r="A54" s="76">
         <v>16</v>
       </c>
-      <c r="B54" s="87" t="s">
+      <c r="B54" s="76" t="s">
         <v>89</v>
       </c>
       <c r="C54" s="36">
@@ -7930,8 +8064,8 @@
       </c>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="87"/>
-      <c r="B55" s="87"/>
+      <c r="A55" s="76"/>
+      <c r="B55" s="76"/>
       <c r="C55" s="36">
         <v>16.2</v>
       </c>
@@ -7955,8 +8089,8 @@
       </c>
     </row>
     <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="87"/>
-      <c r="B56" s="87"/>
+      <c r="A56" s="76"/>
+      <c r="B56" s="76"/>
       <c r="C56" s="36">
         <v>16.3</v>
       </c>
@@ -7980,8 +8114,8 @@
       </c>
     </row>
     <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="87"/>
-      <c r="B57" s="87"/>
+      <c r="A57" s="76"/>
+      <c r="B57" s="76"/>
       <c r="C57" s="36">
         <v>16.399999999999999</v>
       </c>
@@ -8005,8 +8139,8 @@
       </c>
     </row>
     <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="87"/>
-      <c r="B58" s="87"/>
+      <c r="A58" s="76"/>
+      <c r="B58" s="76"/>
       <c r="C58" s="36">
         <v>16.5</v>
       </c>
@@ -8030,8 +8164,8 @@
       </c>
     </row>
     <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="65"/>
-      <c r="B59" s="65"/>
+      <c r="A59" s="77"/>
+      <c r="B59" s="77"/>
       <c r="C59" s="36">
         <v>16.600000000000001</v>
       </c>
@@ -8055,10 +8189,10 @@
       </c>
     </row>
     <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="88">
+      <c r="A60" s="78">
         <v>17</v>
       </c>
-      <c r="B60" s="91" t="s">
+      <c r="B60" s="81" t="s">
         <v>105</v>
       </c>
       <c r="C60" s="39">
@@ -8084,8 +8218,8 @@
       </c>
     </row>
     <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="89"/>
-      <c r="B61" s="91"/>
+      <c r="A61" s="79"/>
+      <c r="B61" s="81"/>
       <c r="C61" s="39">
         <v>17.2</v>
       </c>
@@ -8109,8 +8243,8 @@
       </c>
     </row>
     <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="89"/>
-      <c r="B62" s="91"/>
+      <c r="A62" s="79"/>
+      <c r="B62" s="81"/>
       <c r="C62" s="39">
         <v>17.3</v>
       </c>
@@ -8134,8 +8268,8 @@
       </c>
     </row>
     <row r="63" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="89"/>
-      <c r="B63" s="91"/>
+      <c r="A63" s="79"/>
+      <c r="B63" s="81"/>
       <c r="C63" s="39">
         <v>17.399999999999999</v>
       </c>
@@ -8159,8 +8293,8 @@
       </c>
     </row>
     <row r="64" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="90"/>
-      <c r="B64" s="91"/>
+      <c r="A64" s="80"/>
+      <c r="B64" s="81"/>
       <c r="C64" s="39">
         <v>17.5</v>
       </c>
@@ -8184,10 +8318,10 @@
       </c>
     </row>
     <row r="65" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="92">
+      <c r="A65" s="82">
         <v>18</v>
       </c>
-      <c r="B65" s="73" t="s">
+      <c r="B65" s="83" t="s">
         <v>244</v>
       </c>
       <c r="C65" s="15">
@@ -8213,8 +8347,8 @@
       </c>
     </row>
     <row r="66" spans="1:12" s="6" customFormat="1" ht="250.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="65"/>
-      <c r="B66" s="74"/>
+      <c r="A66" s="77"/>
+      <c r="B66" s="84"/>
       <c r="C66" s="15">
         <v>18.2</v>
       </c>
@@ -8238,8 +8372,8 @@
       </c>
     </row>
     <row r="67" spans="1:12" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="65"/>
-      <c r="B67" s="74"/>
+      <c r="A67" s="77"/>
+      <c r="B67" s="84"/>
       <c r="C67" s="15">
         <v>18.3</v>
       </c>
@@ -8263,8 +8397,8 @@
       </c>
     </row>
     <row r="68" spans="1:12" s="6" customFormat="1" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="65"/>
-      <c r="B68" s="74"/>
+      <c r="A68" s="77"/>
+      <c r="B68" s="84"/>
       <c r="C68" s="15">
         <v>18.399999999999999</v>
       </c>
@@ -8289,7 +8423,7 @@
     </row>
     <row r="69" spans="1:12" s="6" customFormat="1" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="45"/>
-      <c r="B69" s="75"/>
+      <c r="B69" s="85"/>
       <c r="C69" s="15">
         <v>18.5</v>
       </c>
@@ -8309,10 +8443,10 @@
       <c r="I69" s="15"/>
     </row>
     <row r="70" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="81">
+      <c r="A70" s="70">
         <v>19</v>
       </c>
-      <c r="B70" s="84" t="s">
+      <c r="B70" s="73" t="s">
         <v>120</v>
       </c>
       <c r="C70" s="41">
@@ -8334,8 +8468,8 @@
       <c r="I70" s="44"/>
     </row>
     <row r="71" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="82"/>
-      <c r="B71" s="85"/>
+      <c r="A71" s="71"/>
+      <c r="B71" s="74"/>
       <c r="C71" s="12">
         <v>19.2</v>
       </c>
@@ -8355,8 +8489,8 @@
       <c r="I71" s="44"/>
     </row>
     <row r="72" spans="1:12" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="83"/>
-      <c r="B72" s="86"/>
+      <c r="A72" s="72"/>
+      <c r="B72" s="75"/>
       <c r="C72" s="50">
         <v>19.3</v>
       </c>
@@ -8378,10 +8512,10 @@
       </c>
     </row>
     <row r="73" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="81">
+      <c r="A73" s="70">
         <v>20</v>
       </c>
-      <c r="B73" s="84" t="s">
+      <c r="B73" s="73" t="s">
         <v>126</v>
       </c>
       <c r="C73" s="41">
@@ -8403,8 +8537,8 @@
       <c r="I73" s="44"/>
     </row>
     <row r="74" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A74" s="82"/>
-      <c r="B74" s="85"/>
+      <c r="A74" s="71"/>
+      <c r="B74" s="74"/>
       <c r="C74" s="12">
         <v>20.2</v>
       </c>
@@ -8427,8 +8561,8 @@
       <c r="L74" s="1"/>
     </row>
     <row r="75" spans="1:12" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="83"/>
-      <c r="B75" s="85"/>
+      <c r="A75" s="72"/>
+      <c r="B75" s="74"/>
       <c r="C75" s="53">
         <v>20.3</v>
       </c>
@@ -8454,7 +8588,7 @@
     </row>
     <row r="76" spans="1:12" s="6" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A76" s="46"/>
-      <c r="B76" s="86"/>
+      <c r="B76" s="75"/>
       <c r="C76" s="53">
         <v>20.399999999999999</v>
       </c>
@@ -8479,10 +8613,10 @@
       <c r="L76" s="1"/>
     </row>
     <row r="77" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="81">
+      <c r="A77" s="70">
         <v>21</v>
       </c>
-      <c r="B77" s="84" t="s">
+      <c r="B77" s="73" t="s">
         <v>129</v>
       </c>
       <c r="C77" s="41">
@@ -8504,8 +8638,8 @@
       <c r="I77" s="44"/>
     </row>
     <row r="78" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="82"/>
-      <c r="B78" s="85"/>
+      <c r="A78" s="71"/>
+      <c r="B78" s="74"/>
       <c r="C78" s="12">
         <v>21.2</v>
       </c>
@@ -8525,8 +8659,8 @@
       <c r="I78" s="44"/>
     </row>
     <row r="79" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A79" s="83"/>
-      <c r="B79" s="86"/>
+      <c r="A79" s="72"/>
+      <c r="B79" s="75"/>
       <c r="C79" s="29">
         <v>21.3</v>
       </c>
@@ -8542,10 +8676,10 @@
       <c r="I79" s="30"/>
     </row>
     <row r="80" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="81">
+      <c r="A80" s="70">
         <v>22</v>
       </c>
-      <c r="B80" s="84" t="s">
+      <c r="B80" s="73" t="s">
         <v>133</v>
       </c>
       <c r="C80" s="41">
@@ -8567,8 +8701,8 @@
       <c r="I80" s="44"/>
     </row>
     <row r="81" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A81" s="82"/>
-      <c r="B81" s="85"/>
+      <c r="A81" s="71"/>
+      <c r="B81" s="74"/>
       <c r="C81" s="12">
         <v>22.2</v>
       </c>
@@ -8588,8 +8722,8 @@
       <c r="I81" s="44"/>
     </row>
     <row r="82" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A82" s="83"/>
-      <c r="B82" s="86"/>
+      <c r="A82" s="72"/>
+      <c r="B82" s="75"/>
       <c r="C82" s="29">
         <v>22.3</v>
       </c>
@@ -8705,6 +8839,29 @@
   </sheetData>
   <autoFilter ref="I1:I32" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A46:A53"/>
+    <mergeCell ref="B46:B53"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="A35:A45"/>
+    <mergeCell ref="B35:B45"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B10"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="A80:A82"/>
@@ -8719,31 +8876,8 @@
     <mergeCell ref="A73:A75"/>
     <mergeCell ref="B73:B76"/>
     <mergeCell ref="B65:B69"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B10"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A46:A53"/>
-    <mergeCell ref="B46:B53"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="A35:A45"/>
-    <mergeCell ref="B35:B45"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="B22:B26"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -8755,7 +8889,7 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" style="96" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" style="62" customWidth="1"/>
     <col min="2" max="2" width="43.5546875" customWidth="1"/>
     <col min="3" max="3" width="55.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="62" bestFit="1" customWidth="1"/>
@@ -8763,7 +8897,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="60" t="s">
         <v>297</v>
       </c>
       <c r="B1" s="58" t="s">
@@ -8779,28 +8913,28 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="95" t="s">
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="61" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="59" t="s">
+        <v>336</v>
+      </c>
+      <c r="C2" s="59" t="s">
         <v>337</v>
       </c>
-      <c r="C2" s="93" t="s">
-        <v>338</v>
-      </c>
-      <c r="D2" s="93" t="s">
+      <c r="D2" s="59" t="s">
         <v>335</v>
       </c>
       <c r="E2" s="57" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="144" x14ac:dyDescent="0.3">
-      <c r="A3" s="95">
+      <c r="A3" s="61">
         <v>5.0999999999999996</v>
       </c>
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="59" t="s">
         <v>333</v>
       </c>
       <c r="C3" s="56" t="s">
@@ -8814,7 +8948,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="144" x14ac:dyDescent="0.3">
-      <c r="A4" s="95">
+      <c r="A4" s="61">
         <v>5.2</v>
       </c>
       <c r="B4" s="56" t="s">
@@ -8831,7 +8965,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="95">
+      <c r="A5" s="61">
         <v>5.3</v>
       </c>
       <c r="B5" s="56" t="s">
@@ -8848,7 +8982,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="95">
+      <c r="A6" s="61">
         <v>5.4</v>
       </c>
       <c r="B6" s="56" t="s">
@@ -8865,24 +8999,24 @@
       </c>
     </row>
     <row r="7" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="101">
+      <c r="A7" s="67">
         <v>5.5</v>
       </c>
-      <c r="B7" s="102" t="s">
+      <c r="B7" s="68" t="s">
         <v>309</v>
       </c>
-      <c r="C7" s="102" t="s">
+      <c r="C7" s="68" t="s">
         <v>310</v>
       </c>
-      <c r="D7" s="102" t="s">
+      <c r="D7" s="68" t="s">
         <v>311</v>
       </c>
-      <c r="E7" s="103" t="s">
-        <v>340</v>
+      <c r="E7" s="69" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="95">
+      <c r="A8" s="61">
         <v>5.6</v>
       </c>
       <c r="B8" s="56" t="s">
@@ -8895,28 +9029,28 @@
         <v>314</v>
       </c>
       <c r="E8" s="57" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="100">
+      <c r="A9" s="66">
         <v>5.7</v>
       </c>
-      <c r="B9" s="97" t="s">
+      <c r="B9" s="63" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="97" t="s">
+      <c r="C9" s="63" t="s">
         <v>316</v>
       </c>
-      <c r="D9" s="98" t="s">
+      <c r="D9" s="64" t="s">
         <v>326</v>
       </c>
-      <c r="E9" s="99" t="s">
+      <c r="E9" s="65" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="95">
+      <c r="A10" s="61">
         <v>5.8</v>
       </c>
       <c r="B10" s="56" t="s">
@@ -8933,16 +9067,16 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="95">
+      <c r="A11" s="61">
         <v>5.9</v>
       </c>
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="59" t="s">
         <v>330</v>
       </c>
-      <c r="C11" s="93" t="s">
+      <c r="C11" s="59" t="s">
         <v>328</v>
       </c>
-      <c r="D11" s="93" t="s">
+      <c r="D11" s="59" t="s">
         <v>329</v>
       </c>
       <c r="E11" s="57" t="s">

--- a/Business Analysis/checkupp_product_backlog.xlsx
+++ b/Business Analysis/checkupp_product_backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8404C94-CBC7-4AE4-91FD-931273E72FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B3E76B-44D9-4556-ABC2-491024BE004E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4890,6 +4890,850 @@
         <rFont val="Calibri"/>
         <scheme val="minor"/>
       </rPr>
+      <t xml:space="preserve"> The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pregnancy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> card must be displayed when the configured user profile indicates both "female gender" </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "confirmed pregnancy in the app" (calculated LMP date).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The Pregnancy card must not be displayed as a personalised recommendation when either condition is not satisfied.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pregnancy recommendations must appear alongside any applicable age-based recommendation rather than replacing it, under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommended for You</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting the Pregnancy card must display the vaccination information configured for the pregnancy life stage.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The displayed Pregnancy card must follow the approved wireframe styling and interaction behaviour.</t>
+    </r>
+  </si>
+  <si>
+    <t>Logged-in user navigating the Immunisations screen</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>I can access the Immunisations tracking and listing feature of the app</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Logged-in user navigating the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Screenings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">tap on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vaccine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab located at the top</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> must be displayed separately from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Recommended for You</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cards within </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> must follow their defined frontend visibility rules.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Travel must be available to all users.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Children (0–4 years) must follow the 16+ visibility rule</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. (Must be obscured in MVP)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Age/life-stage categories shown for general browsing must appear in the order specified by the approved wireframe.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Changes to the configured test/user profile must result in the appropriate category visibility changes when the screen is re-rendered.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Children (0–4 years)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> card must be displayed under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Categories</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when the configured user's age is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>16 years or older</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The Children card must not be displayed when the configured user's age is below 16.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The boundary value of exactly 16 years must result in the Children card being displayed.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Visibility of the Children card must not depend on gender or pregnancy status.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Selecting the card must display the vaccination information configured for children aged 0–4 years.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Must be obscured in MVP.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Screenings bottom navigation tab's screen must display 3 top tabs in the following order:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> General, Cancer, Vaccine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Tapping the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vaccine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab must navigate the user to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Immunisation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen, rendered under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vaccine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tapping </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Immunisation Checkups</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Home</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bottom navigation tab must navigate the user to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Immunisation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen, rendered under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vaccine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve"> Missing/invalid age data must not result in an arbitrary age-specific recommendation being shown.
 </t>
     </r>
@@ -4931,37 +5775,17 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> General categories that do not depend on missing information, such as Travel, must remain accessible.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The frontend must display the defined fallback/empty state where personalised recommendations cannot be determined: A link to profile page that gives a gentle nudge to set age.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
+4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
     </r>
     <r>
       <rPr>
@@ -4971,850 +5795,6 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> The screen must remain functional and must not crash because profile values are null, undefined, malformed, or otherwise unavailable.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Pregnancy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> card must be displayed when the configured user profile indicates both "female gender" </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>and</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> "confirmed pregnancy in the app" (calculated LMP date).
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The Pregnancy card must not be displayed as a personalised recommendation when either condition is not satisfied.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pregnancy recommendations must appear alongside any applicable age-based recommendation rather than replacing it, under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Recommended for You</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Selecting the Pregnancy card must display the vaccination information configured for the pregnancy life stage.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The displayed Pregnancy card must follow the approved wireframe styling and interaction behaviour.</t>
-    </r>
-  </si>
-  <si>
-    <t>Logged-in user navigating the Immunisations screen</t>
-  </si>
-  <si>
-    <t>5.0</t>
-  </si>
-  <si>
-    <t>I can access the Immunisations tracking and listing feature of the app</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Logged-in user navigating the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Screenings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Vaccine</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab located at the top</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Categories</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> must be displayed separately from </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Recommended for You</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Cards within </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Categories</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> must follow their defined frontend visibility rules.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Travel must be available to all users.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Children (0–4 years) must follow the 16+ visibility rule</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. (Must be obscured in MVP)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Age/life-stage categories shown for general browsing must appear in the order specified by the approved wireframe.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFFC000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Changes to the configured test/user profile must result in the appropriate category visibility changes when the screen is re-rendered.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Children (0–4 years)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> card must be displayed under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Categories</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> when the configured user's age is </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>16 years or older</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The Children card must not be displayed when the configured user's age is below 16.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> The boundary value of exactly 16 years must result in the Children card being displayed.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Visibility of the Children card must not depend on gender or pregnancy status.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Selecting the card must display the vaccination information configured for children aged 0–4 years.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Must be obscured in MVP.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="2" tint="-9.9978637043366805E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Screenings bottom navigation tab's screen must display 3 top tabs in the following order:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> General, Cancer, Vaccine</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Tapping the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Vaccine</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab must navigate the user to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Immunisation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen, rendered under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Vaccine</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Tapping </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Immunisation Checkups</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Home</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> bottom navigation tab must navigate the user to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Immunisation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen, rendered under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Vaccine</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab</t>
     </r>
   </si>
 </sst>
@@ -6426,6 +6406,72 @@
     <xf numFmtId="0" fontId="26" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6447,9 +6493,6 @@
     <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6463,69 +6506,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6766,34 +6746,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="86" t="s">
+      <c r="B1" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="86" t="s">
+      <c r="C1" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="86" t="s">
+      <c r="D1" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
       <c r="G1" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="86" t="s">
+      <c r="H1" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="86" t="s">
+      <c r="I1" s="83" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -6804,8 +6784,8 @@
         <v>9</v>
       </c>
       <c r="G2" s="87"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
     </row>
     <row r="3" spans="1:9" s="5" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="88">
@@ -6984,10 +6964,10 @@
       <c r="I10" s="48"/>
     </row>
     <row r="11" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="83">
+      <c r="A11" s="84">
         <v>5</v>
       </c>
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="84" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="15">
@@ -7013,8 +6993,8 @@
       </c>
     </row>
     <row r="12" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="84"/>
-      <c r="B12" s="84"/>
+      <c r="A12" s="85"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="15">
         <v>5.2</v>
       </c>
@@ -7034,8 +7014,8 @@
       <c r="I12" s="15"/>
     </row>
     <row r="13" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="84"/>
-      <c r="B13" s="84"/>
+      <c r="A13" s="85"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="15">
         <v>5.3</v>
       </c>
@@ -7055,8 +7035,8 @@
       <c r="I13" s="15"/>
     </row>
     <row r="14" spans="1:9" s="11" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="84"/>
-      <c r="B14" s="84"/>
+      <c r="A14" s="85"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="18">
         <v>5.4</v>
       </c>
@@ -7076,8 +7056,8 @@
       <c r="I14" s="18"/>
     </row>
     <row r="15" spans="1:9" s="11" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="85"/>
-      <c r="B15" s="85"/>
+      <c r="A15" s="86"/>
+      <c r="B15" s="86"/>
       <c r="C15" s="18">
         <v>5.5</v>
       </c>
@@ -7097,10 +7077,10 @@
       <c r="I15" s="18"/>
     </row>
     <row r="16" spans="1:9" s="11" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="92">
+      <c r="A16" s="70">
         <v>6</v>
       </c>
-      <c r="B16" s="92" t="s">
+      <c r="B16" s="70" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="21">
@@ -7126,8 +7106,8 @@
       </c>
     </row>
     <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="93"/>
-      <c r="B17" s="93"/>
+      <c r="A17" s="71"/>
+      <c r="B17" s="71"/>
       <c r="C17" s="21">
         <v>6.2</v>
       </c>
@@ -7147,8 +7127,8 @@
       <c r="I17" s="21"/>
     </row>
     <row r="18" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="93"/>
-      <c r="B18" s="93"/>
+      <c r="A18" s="71"/>
+      <c r="B18" s="71"/>
       <c r="C18" s="21">
         <v>6.3</v>
       </c>
@@ -7168,8 +7148,8 @@
       <c r="I18" s="21"/>
     </row>
     <row r="19" spans="1:9" s="6" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="93"/>
-      <c r="B19" s="93"/>
+      <c r="A19" s="71"/>
+      <c r="B19" s="71"/>
       <c r="C19" s="24">
         <v>6.4</v>
       </c>
@@ -7194,7 +7174,7 @@
     </row>
     <row r="20" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A20" s="49"/>
-      <c r="B20" s="93"/>
+      <c r="B20" s="71"/>
       <c r="C20" s="21">
         <v>6.5</v>
       </c>
@@ -7215,7 +7195,7 @@
     </row>
     <row r="21" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="49"/>
-      <c r="B21" s="103"/>
+      <c r="B21" s="82"/>
       <c r="C21" s="21">
         <v>6.6</v>
       </c>
@@ -7235,10 +7215,10 @@
       <c r="I21" s="21"/>
     </row>
     <row r="22" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A22" s="94">
+      <c r="A22" s="72">
         <v>7</v>
       </c>
-      <c r="B22" s="92" t="s">
+      <c r="B22" s="70" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="21">
@@ -7264,8 +7244,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A23" s="95"/>
-      <c r="B23" s="93"/>
+      <c r="A23" s="73"/>
+      <c r="B23" s="71"/>
       <c r="C23" s="21">
         <v>7.2</v>
       </c>
@@ -7287,8 +7267,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="95"/>
-      <c r="B24" s="93"/>
+      <c r="A24" s="73"/>
+      <c r="B24" s="71"/>
       <c r="C24" s="21">
         <v>7.3</v>
       </c>
@@ -7308,8 +7288,8 @@
       <c r="I24" s="21"/>
     </row>
     <row r="25" spans="1:9" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="96"/>
-      <c r="B25" s="93"/>
+      <c r="A25" s="74"/>
+      <c r="B25" s="71"/>
       <c r="C25" s="21">
         <v>7.4</v>
       </c>
@@ -7330,7 +7310,7 @@
     </row>
     <row r="26" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A26" s="49"/>
-      <c r="B26" s="103"/>
+      <c r="B26" s="82"/>
       <c r="C26" s="21">
         <v>7.5</v>
       </c>
@@ -7350,10 +7330,10 @@
       <c r="I26" s="21"/>
     </row>
     <row r="27" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="100">
+      <c r="A27" s="79">
         <v>8</v>
       </c>
-      <c r="B27" s="100" t="s">
+      <c r="B27" s="79" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="25">
@@ -7377,8 +7357,8 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="101"/>
-      <c r="B28" s="101"/>
+      <c r="A28" s="80"/>
+      <c r="B28" s="80"/>
       <c r="C28" s="25">
         <v>9.3000000000000007</v>
       </c>
@@ -7400,8 +7380,8 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="102"/>
-      <c r="B29" s="102"/>
+      <c r="A29" s="81"/>
+      <c r="B29" s="81"/>
       <c r="C29" s="25">
         <v>9.4</v>
       </c>
@@ -7423,10 +7403,10 @@
       </c>
     </row>
     <row r="30" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="98">
+      <c r="A30" s="77">
         <v>12</v>
       </c>
-      <c r="B30" s="98" t="s">
+      <c r="B30" s="77" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="27">
@@ -7452,8 +7432,8 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="98"/>
-      <c r="B31" s="98"/>
+      <c r="A31" s="77"/>
+      <c r="B31" s="77"/>
       <c r="C31" s="27">
         <v>12.2</v>
       </c>
@@ -7477,8 +7457,8 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="98"/>
-      <c r="B32" s="98"/>
+      <c r="A32" s="77"/>
+      <c r="B32" s="77"/>
       <c r="C32" s="27">
         <v>12.3</v>
       </c>
@@ -7502,8 +7482,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="98"/>
-      <c r="B33" s="98"/>
+      <c r="A33" s="77"/>
+      <c r="B33" s="77"/>
       <c r="C33" s="27">
         <v>12.4</v>
       </c>
@@ -7527,8 +7507,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="98"/>
-      <c r="B34" s="98"/>
+      <c r="A34" s="77"/>
+      <c r="B34" s="77"/>
       <c r="C34" s="27">
         <v>12.5</v>
       </c>
@@ -7552,10 +7532,10 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="99">
+      <c r="A35" s="78">
         <v>14</v>
       </c>
-      <c r="B35" s="99" t="s">
+      <c r="B35" s="78" t="s">
         <v>70</v>
       </c>
       <c r="C35" s="31">
@@ -7581,8 +7561,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="99"/>
-      <c r="B36" s="99"/>
+      <c r="A36" s="78"/>
+      <c r="B36" s="78"/>
       <c r="C36" s="31">
         <v>14.2</v>
       </c>
@@ -7606,8 +7586,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="99"/>
-      <c r="B37" s="99"/>
+      <c r="A37" s="78"/>
+      <c r="B37" s="78"/>
       <c r="C37" s="31">
         <v>14.3</v>
       </c>
@@ -7631,8 +7611,8 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="99"/>
-      <c r="B38" s="99"/>
+      <c r="A38" s="78"/>
+      <c r="B38" s="78"/>
       <c r="C38" s="31">
         <v>14.4</v>
       </c>
@@ -7656,8 +7636,8 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="99"/>
-      <c r="B39" s="99"/>
+      <c r="A39" s="78"/>
+      <c r="B39" s="78"/>
       <c r="C39" s="31">
         <v>14.5</v>
       </c>
@@ -7681,8 +7661,8 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="99"/>
-      <c r="B40" s="99"/>
+      <c r="A40" s="78"/>
+      <c r="B40" s="78"/>
       <c r="C40" s="31">
         <v>14.6</v>
       </c>
@@ -7706,8 +7686,8 @@
       </c>
     </row>
     <row r="41" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="99"/>
-      <c r="B41" s="99"/>
+      <c r="A41" s="78"/>
+      <c r="B41" s="78"/>
       <c r="C41" s="31">
         <v>14.7</v>
       </c>
@@ -7731,8 +7711,8 @@
       </c>
     </row>
     <row r="42" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="99"/>
-      <c r="B42" s="99"/>
+      <c r="A42" s="78"/>
+      <c r="B42" s="78"/>
       <c r="C42" s="31">
         <v>14.8</v>
       </c>
@@ -7756,8 +7736,8 @@
       </c>
     </row>
     <row r="43" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="99"/>
-      <c r="B43" s="99"/>
+      <c r="A43" s="78"/>
+      <c r="B43" s="78"/>
       <c r="C43" s="31">
         <v>14.9</v>
       </c>
@@ -7781,8 +7761,8 @@
       </c>
     </row>
     <row r="44" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="99"/>
-      <c r="B44" s="99"/>
+      <c r="A44" s="78"/>
+      <c r="B44" s="78"/>
       <c r="C44" s="31">
         <v>14.1</v>
       </c>
@@ -7806,8 +7786,8 @@
       </c>
     </row>
     <row r="45" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="99"/>
-      <c r="B45" s="99"/>
+      <c r="A45" s="78"/>
+      <c r="B45" s="78"/>
       <c r="C45" s="31">
         <v>14.11</v>
       </c>
@@ -7831,10 +7811,10 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="97">
+      <c r="A46" s="75">
         <v>15</v>
       </c>
-      <c r="B46" s="97" t="s">
+      <c r="B46" s="75" t="s">
         <v>74</v>
       </c>
       <c r="C46" s="34">
@@ -7860,8 +7840,8 @@
       </c>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="77"/>
-      <c r="B47" s="77"/>
+      <c r="A47" s="76"/>
+      <c r="B47" s="76"/>
       <c r="C47" s="34">
         <v>15.2</v>
       </c>
@@ -7885,8 +7865,8 @@
       </c>
     </row>
     <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="77"/>
-      <c r="B48" s="77"/>
+      <c r="A48" s="76"/>
+      <c r="B48" s="76"/>
       <c r="C48" s="34">
         <v>15.3</v>
       </c>
@@ -7910,8 +7890,8 @@
       </c>
     </row>
     <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="77"/>
-      <c r="B49" s="77"/>
+      <c r="A49" s="76"/>
+      <c r="B49" s="76"/>
       <c r="C49" s="34">
         <v>15.4</v>
       </c>
@@ -7935,8 +7915,8 @@
       </c>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="77"/>
-      <c r="B50" s="77"/>
+      <c r="A50" s="76"/>
+      <c r="B50" s="76"/>
       <c r="C50" s="34">
         <v>15.5</v>
       </c>
@@ -7960,8 +7940,8 @@
       </c>
     </row>
     <row r="51" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="77"/>
-      <c r="B51" s="77"/>
+      <c r="A51" s="76"/>
+      <c r="B51" s="76"/>
       <c r="C51" s="34">
         <v>15.6</v>
       </c>
@@ -7985,8 +7965,8 @@
       </c>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="77"/>
-      <c r="B52" s="77"/>
+      <c r="A52" s="76"/>
+      <c r="B52" s="76"/>
       <c r="C52" s="34">
         <v>15.7</v>
       </c>
@@ -8010,8 +7990,8 @@
       </c>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="77"/>
-      <c r="B53" s="77"/>
+      <c r="A53" s="76"/>
+      <c r="B53" s="76"/>
       <c r="C53" s="34">
         <v>15.8</v>
       </c>
@@ -8035,10 +8015,10 @@
       </c>
     </row>
     <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="76">
+      <c r="A54" s="98">
         <v>16</v>
       </c>
-      <c r="B54" s="76" t="s">
+      <c r="B54" s="98" t="s">
         <v>89</v>
       </c>
       <c r="C54" s="36">
@@ -8064,8 +8044,8 @@
       </c>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="76"/>
-      <c r="B55" s="76"/>
+      <c r="A55" s="98"/>
+      <c r="B55" s="98"/>
       <c r="C55" s="36">
         <v>16.2</v>
       </c>
@@ -8089,8 +8069,8 @@
       </c>
     </row>
     <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="76"/>
-      <c r="B56" s="76"/>
+      <c r="A56" s="98"/>
+      <c r="B56" s="98"/>
       <c r="C56" s="36">
         <v>16.3</v>
       </c>
@@ -8114,8 +8094,8 @@
       </c>
     </row>
     <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="76"/>
-      <c r="B57" s="76"/>
+      <c r="A57" s="98"/>
+      <c r="B57" s="98"/>
       <c r="C57" s="36">
         <v>16.399999999999999</v>
       </c>
@@ -8139,8 +8119,8 @@
       </c>
     </row>
     <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="76"/>
-      <c r="B58" s="76"/>
+      <c r="A58" s="98"/>
+      <c r="B58" s="98"/>
       <c r="C58" s="36">
         <v>16.5</v>
       </c>
@@ -8164,8 +8144,8 @@
       </c>
     </row>
     <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="77"/>
-      <c r="B59" s="77"/>
+      <c r="A59" s="76"/>
+      <c r="B59" s="76"/>
       <c r="C59" s="36">
         <v>16.600000000000001</v>
       </c>
@@ -8189,10 +8169,10 @@
       </c>
     </row>
     <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="78">
+      <c r="A60" s="99">
         <v>17</v>
       </c>
-      <c r="B60" s="81" t="s">
+      <c r="B60" s="102" t="s">
         <v>105</v>
       </c>
       <c r="C60" s="39">
@@ -8218,8 +8198,8 @@
       </c>
     </row>
     <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="79"/>
-      <c r="B61" s="81"/>
+      <c r="A61" s="100"/>
+      <c r="B61" s="102"/>
       <c r="C61" s="39">
         <v>17.2</v>
       </c>
@@ -8243,8 +8223,8 @@
       </c>
     </row>
     <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="79"/>
-      <c r="B62" s="81"/>
+      <c r="A62" s="100"/>
+      <c r="B62" s="102"/>
       <c r="C62" s="39">
         <v>17.3</v>
       </c>
@@ -8268,8 +8248,8 @@
       </c>
     </row>
     <row r="63" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="79"/>
-      <c r="B63" s="81"/>
+      <c r="A63" s="100"/>
+      <c r="B63" s="102"/>
       <c r="C63" s="39">
         <v>17.399999999999999</v>
       </c>
@@ -8293,8 +8273,8 @@
       </c>
     </row>
     <row r="64" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="80"/>
-      <c r="B64" s="81"/>
+      <c r="A64" s="101"/>
+      <c r="B64" s="102"/>
       <c r="C64" s="39">
         <v>17.5</v>
       </c>
@@ -8318,10 +8298,10 @@
       </c>
     </row>
     <row r="65" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="82">
+      <c r="A65" s="103">
         <v>18</v>
       </c>
-      <c r="B65" s="83" t="s">
+      <c r="B65" s="84" t="s">
         <v>244</v>
       </c>
       <c r="C65" s="15">
@@ -8347,8 +8327,8 @@
       </c>
     </row>
     <row r="66" spans="1:12" s="6" customFormat="1" ht="250.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="77"/>
-      <c r="B66" s="84"/>
+      <c r="A66" s="76"/>
+      <c r="B66" s="85"/>
       <c r="C66" s="15">
         <v>18.2</v>
       </c>
@@ -8372,8 +8352,8 @@
       </c>
     </row>
     <row r="67" spans="1:12" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="77"/>
-      <c r="B67" s="84"/>
+      <c r="A67" s="76"/>
+      <c r="B67" s="85"/>
       <c r="C67" s="15">
         <v>18.3</v>
       </c>
@@ -8397,8 +8377,8 @@
       </c>
     </row>
     <row r="68" spans="1:12" s="6" customFormat="1" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="77"/>
-      <c r="B68" s="84"/>
+      <c r="A68" s="76"/>
+      <c r="B68" s="85"/>
       <c r="C68" s="15">
         <v>18.399999999999999</v>
       </c>
@@ -8423,7 +8403,7 @@
     </row>
     <row r="69" spans="1:12" s="6" customFormat="1" ht="216" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="45"/>
-      <c r="B69" s="85"/>
+      <c r="B69" s="86"/>
       <c r="C69" s="15">
         <v>18.5</v>
       </c>
@@ -8443,10 +8423,10 @@
       <c r="I69" s="15"/>
     </row>
     <row r="70" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="70">
+      <c r="A70" s="92">
         <v>19</v>
       </c>
-      <c r="B70" s="73" t="s">
+      <c r="B70" s="95" t="s">
         <v>120</v>
       </c>
       <c r="C70" s="41">
@@ -8468,8 +8448,8 @@
       <c r="I70" s="44"/>
     </row>
     <row r="71" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="71"/>
-      <c r="B71" s="74"/>
+      <c r="A71" s="93"/>
+      <c r="B71" s="96"/>
       <c r="C71" s="12">
         <v>19.2</v>
       </c>
@@ -8489,8 +8469,8 @@
       <c r="I71" s="44"/>
     </row>
     <row r="72" spans="1:12" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="72"/>
-      <c r="B72" s="75"/>
+      <c r="A72" s="94"/>
+      <c r="B72" s="97"/>
       <c r="C72" s="50">
         <v>19.3</v>
       </c>
@@ -8512,10 +8492,10 @@
       </c>
     </row>
     <row r="73" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="70">
+      <c r="A73" s="92">
         <v>20</v>
       </c>
-      <c r="B73" s="73" t="s">
+      <c r="B73" s="95" t="s">
         <v>126</v>
       </c>
       <c r="C73" s="41">
@@ -8537,8 +8517,8 @@
       <c r="I73" s="44"/>
     </row>
     <row r="74" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A74" s="71"/>
-      <c r="B74" s="74"/>
+      <c r="A74" s="93"/>
+      <c r="B74" s="96"/>
       <c r="C74" s="12">
         <v>20.2</v>
       </c>
@@ -8561,8 +8541,8 @@
       <c r="L74" s="1"/>
     </row>
     <row r="75" spans="1:12" s="6" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A75" s="72"/>
-      <c r="B75" s="74"/>
+      <c r="A75" s="94"/>
+      <c r="B75" s="96"/>
       <c r="C75" s="53">
         <v>20.3</v>
       </c>
@@ -8588,7 +8568,7 @@
     </row>
     <row r="76" spans="1:12" s="6" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A76" s="46"/>
-      <c r="B76" s="75"/>
+      <c r="B76" s="97"/>
       <c r="C76" s="53">
         <v>20.399999999999999</v>
       </c>
@@ -8613,10 +8593,10 @@
       <c r="L76" s="1"/>
     </row>
     <row r="77" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="70">
+      <c r="A77" s="92">
         <v>21</v>
       </c>
-      <c r="B77" s="73" t="s">
+      <c r="B77" s="95" t="s">
         <v>129</v>
       </c>
       <c r="C77" s="41">
@@ -8638,8 +8618,8 @@
       <c r="I77" s="44"/>
     </row>
     <row r="78" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A78" s="71"/>
-      <c r="B78" s="74"/>
+      <c r="A78" s="93"/>
+      <c r="B78" s="96"/>
       <c r="C78" s="12">
         <v>21.2</v>
       </c>
@@ -8659,8 +8639,8 @@
       <c r="I78" s="44"/>
     </row>
     <row r="79" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A79" s="72"/>
-      <c r="B79" s="75"/>
+      <c r="A79" s="94"/>
+      <c r="B79" s="97"/>
       <c r="C79" s="29">
         <v>21.3</v>
       </c>
@@ -8676,10 +8656,10 @@
       <c r="I79" s="30"/>
     </row>
     <row r="80" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="70">
+      <c r="A80" s="92">
         <v>22</v>
       </c>
-      <c r="B80" s="73" t="s">
+      <c r="B80" s="95" t="s">
         <v>133</v>
       </c>
       <c r="C80" s="41">
@@ -8701,8 +8681,8 @@
       <c r="I80" s="44"/>
     </row>
     <row r="81" spans="1:9" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A81" s="71"/>
-      <c r="B81" s="74"/>
+      <c r="A81" s="93"/>
+      <c r="B81" s="96"/>
       <c r="C81" s="12">
         <v>22.2</v>
       </c>
@@ -8722,8 +8702,8 @@
       <c r="I81" s="44"/>
     </row>
     <row r="82" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A82" s="72"/>
-      <c r="B82" s="75"/>
+      <c r="A82" s="94"/>
+      <c r="B82" s="97"/>
       <c r="C82" s="29">
         <v>22.3</v>
       </c>
@@ -8839,29 +8819,6 @@
   </sheetData>
   <autoFilter ref="I1:I32" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A46:A53"/>
-    <mergeCell ref="B46:B53"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="B30:B34"/>
-    <mergeCell ref="A35:A45"/>
-    <mergeCell ref="B35:B45"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A11:A15"/>
-    <mergeCell ref="B11:B15"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B10"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="A80:A82"/>
@@ -8876,6 +8833,29 @@
     <mergeCell ref="A73:A75"/>
     <mergeCell ref="B73:B76"/>
     <mergeCell ref="B65:B69"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="B11:B15"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B10"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A46:A53"/>
+    <mergeCell ref="B46:B53"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="B30:B34"/>
+    <mergeCell ref="A35:A45"/>
+    <mergeCell ref="B35:B45"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="B22:B26"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8915,19 +8895,19 @@
     </row>
     <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="61" t="s">
+        <v>333</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>336</v>
+      </c>
+      <c r="D2" s="59" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="59" t="s">
-        <v>336</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>337</v>
-      </c>
-      <c r="D2" s="59" t="s">
-        <v>335</v>
-      </c>
       <c r="E2" s="57" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="144" x14ac:dyDescent="0.3">
@@ -8935,7 +8915,7 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C3" s="56" t="s">
         <v>320</v>
@@ -8978,7 +8958,7 @@
         <v>306</v>
       </c>
       <c r="E5" s="57" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="72" x14ac:dyDescent="0.3">
@@ -9012,7 +8992,7 @@
         <v>311</v>
       </c>
       <c r="E7" s="69" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
@@ -9029,7 +9009,7 @@
         <v>314</v>
       </c>
       <c r="E8" s="57" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
@@ -9066,7 +9046,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="61">
         <v>5.9</v>
       </c>
@@ -9080,7 +9060,7 @@
         <v>329</v>
       </c>
       <c r="E11" s="57" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
